--- a/test/G14-G24.xlsx
+++ b/test/G14-G24.xlsx
@@ -8,14 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wolfgang\Documents\GitHub\SACOBRA_Py\test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4797BA3A-2794-4D45-BE25-DC0B75AFEB14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9997AEB9-44CE-45CF-A9FB-8A3C1B6387D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{6EF9DD2D-A48A-4E61-B7E9-B72FBCB815D4}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23016" windowHeight="12216" activeTab="2" xr2:uid="{6EF9DD2D-A48A-4E61-B7E9-B72FBCB815D4}"/>
   </bookViews>
   <sheets>
     <sheet name="Python, MIDPTS" sheetId="1" r:id="rId1"/>
-    <sheet name="Python, trueFunc OLD" sheetId="4" r:id="rId2"/>
-    <sheet name="Python, trueFunc" sheetId="3" r:id="rId3"/>
+    <sheet name="Python, MIDPTS EPS=0" sheetId="6" r:id="rId2"/>
+    <sheet name="Python, MIDPTS EPS" sheetId="7" r:id="rId3"/>
+    <sheet name="Python, trueFunc OLD" sheetId="4" r:id="rId4"/>
+    <sheet name="Python, trueFunc" sheetId="3" r:id="rId5"/>
+    <sheet name="Python, trueFunc EPS=0" sheetId="5" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="700" uniqueCount="51">
   <si>
     <t>SACOBRA_Py, 10 runs, mean(time), median(err)</t>
   </si>
@@ -72,9 +75,6 @@
   </si>
   <si>
     <t>conTol</t>
-  </si>
-  <si>
-    <t>conTol = 0.0</t>
   </si>
   <si>
     <t>gname</t>
@@ -219,6 +219,94 @@
   <si>
     <t>G22 with muFinal=1e-6 not better: median(err)=3.7, # infeasible runs: 4</t>
   </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>trueFuncForSurr = True</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, TGR=np.inf, muFinal=1e-7, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>p2.EPS=0.0</t>
+    </r>
+  </si>
+  <si>
+    <t>ISA.onlinePLOG = O_LOGIC.MIDPTS</t>
+  </si>
+  <si>
+    <t>muFinal=1e-7</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">TGR=np.inf, muFinal=1e-7, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>epsilonMax=0.0</t>
+    </r>
+  </si>
+  <si>
+    <t>NaN</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">TGR=np.inf, muFinal=1e-7, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>epsilonMax=None</t>
+    </r>
+  </si>
+  <si>
+    <t>n_infeasible</t>
+  </si>
+  <si>
+    <t>df2_conTol0.0-trueFunc-fe500-G14-G24.feather from 12.09.2025</t>
+  </si>
+  <si>
+    <t>df2_conTol0.0-MIDPTS-fe500-G14-G24-EPS0.feather from 17.09.2025</t>
+  </si>
+  <si>
+    <t>df2_conTol0.0-MIDPTS-fe500-G14-G24-EPSNone.feather from 18.09.2025</t>
+  </si>
 </sst>
 </file>
 
@@ -257,7 +345,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -291,6 +379,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -413,7 +507,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -491,6 +585,10 @@
     <xf numFmtId="11" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="11" fontId="0" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="11" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="1" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="11" fontId="0" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -805,7 +903,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{438B20B1-DE4E-4A79-B5E4-CEFFEB5E4BAC}">
-  <dimension ref="C1:U32"/>
+  <dimension ref="C1:U33"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="9.6640625" customWidth="1"/>
@@ -825,75 +923,64 @@
     </row>
     <row r="2" spans="3:20" x14ac:dyDescent="0.3">
       <c r="C2" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="3:20" x14ac:dyDescent="0.3">
+      <c r="C3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="M2" t="s">
+      <c r="M3" t="s">
         <v>2</v>
       </c>
-      <c r="N2" t="s">
+      <c r="N3" t="s">
         <v>3</v>
       </c>
-      <c r="O2" t="s">
+      <c r="O3" t="s">
         <v>4</v>
       </c>
-      <c r="P2" t="s">
+      <c r="P3" t="s">
         <v>5</v>
       </c>
-      <c r="Q2" t="s">
-        <v>23</v>
-      </c>
-      <c r="R2" t="s">
+      <c r="Q3" t="s">
+        <v>22</v>
+      </c>
+      <c r="R3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="3:20" x14ac:dyDescent="0.3">
-      <c r="C3" s="3"/>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
-      <c r="G3" s="4"/>
-      <c r="H3" s="4"/>
-      <c r="I3" s="4"/>
-      <c r="J3" s="5"/>
-      <c r="O3" t="s">
-        <v>14</v>
-      </c>
-      <c r="P3" t="s">
+    <row r="4" spans="3:20" x14ac:dyDescent="0.3">
+      <c r="C4" s="3"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
+      <c r="J4" s="5"/>
+      <c r="O4" t="s">
+        <v>13</v>
+      </c>
+      <c r="P4" t="s">
         <v>6</v>
       </c>
-      <c r="Q3" t="s">
+      <c r="Q4" t="s">
         <v>7</v>
       </c>
-      <c r="R3" t="s">
+      <c r="R4" t="s">
         <v>8</v>
       </c>
-      <c r="S3" t="s">
+      <c r="S4" t="s">
         <v>9</v>
       </c>
-      <c r="T3" s="6" t="s">
+      <c r="T4" s="6" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="4" spans="3:20" x14ac:dyDescent="0.3">
-      <c r="C4" s="7"/>
-      <c r="G4" s="44" t="s">
-        <v>11</v>
-      </c>
-      <c r="H4" s="45"/>
-      <c r="I4" s="44"/>
-      <c r="J4" s="45"/>
-      <c r="M4" t="s">
-        <v>12</v>
-      </c>
-      <c r="N4" t="s">
-        <v>13</v>
-      </c>
-      <c r="Q4" s="6"/>
     </row>
     <row r="5" spans="3:20" x14ac:dyDescent="0.3">
       <c r="C5" s="7"/>
       <c r="E5" s="10" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>9</v>
@@ -905,66 +992,49 @@
         <v>8</v>
       </c>
       <c r="I5" s="11" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J5" s="13"/>
       <c r="M5" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="N5" t="s">
-        <v>16</v>
-      </c>
-      <c r="O5">
-        <v>10</v>
-      </c>
-      <c r="P5">
-        <v>58.5</v>
-      </c>
-      <c r="Q5" s="6">
-        <v>3888.6478099999999</v>
-      </c>
-      <c r="R5" s="6">
-        <v>3.8567120000000003E-2</v>
-      </c>
-      <c r="S5">
-        <v>500</v>
-      </c>
-      <c r="T5">
-        <v>0</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="Q5" s="6"/>
     </row>
     <row r="6" spans="3:20" x14ac:dyDescent="0.3">
       <c r="C6" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6" s="15" t="s">
         <v>12</v>
-      </c>
-      <c r="D6" s="15" t="s">
-        <v>13</v>
       </c>
       <c r="E6" s="16"/>
       <c r="F6" s="17"/>
       <c r="G6" s="18" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H6" s="17"/>
       <c r="I6" s="18"/>
       <c r="J6" s="19"/>
       <c r="M6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="N6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O6">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="P6">
         <v>58.5</v>
       </c>
       <c r="Q6" s="6">
-        <v>2070.49449</v>
+        <v>3888.6478099999999</v>
       </c>
       <c r="R6" s="6">
-        <v>3.5015550000000002E-11</v>
+        <v>3.8567120000000003E-2</v>
       </c>
       <c r="S6">
         <v>500</v>
@@ -975,10 +1045,10 @@
     </row>
     <row r="7" spans="3:20" x14ac:dyDescent="0.3">
       <c r="C7" s="41" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D7" s="42" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E7" s="41">
         <v>13</v>
@@ -997,22 +1067,22 @@
       </c>
       <c r="J7" s="21"/>
       <c r="M7" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="N7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O7">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P7">
         <v>58.5</v>
       </c>
-      <c r="Q7">
-        <v>6199.09094</v>
+      <c r="Q7" s="6">
+        <v>2070.49449</v>
       </c>
       <c r="R7" s="6">
-        <v>4.7176989999999997E-3</v>
+        <v>3.5015550000000002E-11</v>
       </c>
       <c r="S7">
         <v>500</v>
@@ -1024,7 +1094,7 @@
     <row r="8" spans="3:20" x14ac:dyDescent="0.3">
       <c r="C8" s="16"/>
       <c r="D8" s="17" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E8" s="16">
         <v>13</v>
@@ -1037,22 +1107,22 @@
       <c r="I8" s="22"/>
       <c r="J8" s="25"/>
       <c r="M8" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="N8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P8">
         <v>58.5</v>
       </c>
-      <c r="Q8" s="6">
-        <v>2395.6140399999999</v>
+      <c r="Q8">
+        <v>6199.09094</v>
       </c>
       <c r="R8" s="6">
-        <v>0.61001050000000001</v>
+        <v>4.7176989999999997E-3</v>
       </c>
       <c r="S8">
         <v>500</v>
@@ -1063,10 +1133,10 @@
     </row>
     <row r="9" spans="3:20" x14ac:dyDescent="0.3">
       <c r="C9" s="7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D9" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E9" s="7">
         <v>2</v>
@@ -1085,22 +1155,22 @@
       </c>
       <c r="J9" s="21"/>
       <c r="M9" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="N9" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O9">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="P9">
         <v>58.5</v>
       </c>
-      <c r="Q9">
-        <v>1872.3066100000001</v>
+      <c r="Q9" s="6">
+        <v>2395.6140399999999</v>
       </c>
       <c r="R9" s="6">
-        <v>-2.034669E-4</v>
+        <v>0.61001050000000001</v>
       </c>
       <c r="S9">
         <v>500</v>
@@ -1112,7 +1182,7 @@
     <row r="10" spans="3:20" x14ac:dyDescent="0.3">
       <c r="C10" s="16"/>
       <c r="D10" s="17" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E10" s="16">
         <v>2</v>
@@ -1125,22 +1195,22 @@
       <c r="I10" s="22"/>
       <c r="J10" s="25"/>
       <c r="M10" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="N10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O10">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="P10">
         <v>58.5</v>
       </c>
-      <c r="Q10" s="6">
-        <v>1474.1254799999999</v>
+      <c r="Q10">
+        <v>1872.3066100000001</v>
       </c>
       <c r="R10" s="6">
-        <v>132.36429999999999</v>
+        <v>-2.034669E-4</v>
       </c>
       <c r="S10">
         <v>500</v>
@@ -1151,10 +1221,10 @@
     </row>
     <row r="11" spans="3:20" x14ac:dyDescent="0.3">
       <c r="C11" s="7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D11" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E11" s="7">
         <v>5</v>
@@ -1173,22 +1243,22 @@
       </c>
       <c r="J11" s="21"/>
       <c r="M11" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="N11" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O11">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="P11">
         <v>58.5</v>
       </c>
       <c r="Q11" s="6">
-        <v>2971.309385</v>
+        <v>1474.1254799999999</v>
       </c>
       <c r="R11" s="6">
-        <v>317.53919999999999</v>
+        <v>132.36429999999999</v>
       </c>
       <c r="S11">
         <v>500</v>
@@ -1200,7 +1270,7 @@
     <row r="12" spans="3:20" x14ac:dyDescent="0.3">
       <c r="C12" s="16"/>
       <c r="D12" s="17" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E12" s="16">
         <v>5</v>
@@ -1213,22 +1283,22 @@
       <c r="I12" s="22"/>
       <c r="J12" s="25"/>
       <c r="M12" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="N12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O12">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="P12">
         <v>58.5</v>
       </c>
       <c r="Q12" s="6">
-        <v>17000.01197</v>
+        <v>2971.309385</v>
       </c>
       <c r="R12" s="6">
-        <v>35.187019999999997</v>
+        <v>317.53919999999999</v>
       </c>
       <c r="S12">
         <v>500</v>
@@ -1239,10 +1309,10 @@
     </row>
     <row r="13" spans="3:20" x14ac:dyDescent="0.3">
       <c r="C13" s="41" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D13" s="42" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E13" s="41">
         <v>7</v>
@@ -1261,22 +1331,22 @@
       </c>
       <c r="J13" s="21"/>
       <c r="M13" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="N13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O13">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="P13">
         <v>58.5</v>
       </c>
       <c r="Q13" s="6">
-        <v>3993.4907050000002</v>
+        <v>17000.01197</v>
       </c>
       <c r="R13" s="6">
-        <v>1.1281830000000001E-3</v>
+        <v>35.187019999999997</v>
       </c>
       <c r="S13">
         <v>500</v>
@@ -1288,7 +1358,7 @@
     <row r="14" spans="3:20" x14ac:dyDescent="0.3">
       <c r="C14" s="16"/>
       <c r="D14" s="17" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E14" s="16">
         <v>7</v>
@@ -1301,22 +1371,22 @@
       <c r="I14" s="22"/>
       <c r="J14" s="25"/>
       <c r="M14" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="N14" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O14">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="P14">
         <v>58.5</v>
       </c>
       <c r="Q14" s="6">
-        <v>609.53940999999998</v>
+        <v>3993.4907050000002</v>
       </c>
       <c r="R14" s="6">
-        <v>3.1007420000000003E-8</v>
+        <v>1.1281830000000001E-3</v>
       </c>
       <c r="S14">
         <v>500</v>
@@ -1327,10 +1397,10 @@
     </row>
     <row r="15" spans="3:20" x14ac:dyDescent="0.3">
       <c r="C15" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D15" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E15" s="7">
         <v>10</v>
@@ -1348,13 +1418,35 @@
         <v>1.095445E-4</v>
       </c>
       <c r="J15" s="21"/>
-      <c r="Q15" s="6"/>
-      <c r="R15" s="6"/>
+      <c r="M15" t="s">
+        <v>32</v>
+      </c>
+      <c r="N15" t="s">
+        <v>15</v>
+      </c>
+      <c r="O15">
+        <v>2</v>
+      </c>
+      <c r="P15">
+        <v>58.5</v>
+      </c>
+      <c r="Q15" s="6">
+        <v>609.53940999999998</v>
+      </c>
+      <c r="R15" s="6">
+        <v>3.1007420000000003E-8</v>
+      </c>
+      <c r="S15">
+        <v>500</v>
+      </c>
+      <c r="T15">
+        <v>0</v>
+      </c>
     </row>
     <row r="16" spans="3:20" x14ac:dyDescent="0.3">
       <c r="C16" s="16"/>
       <c r="D16" s="17" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E16" s="16">
         <v>10</v>
@@ -1366,31 +1458,15 @@
       <c r="H16" s="24"/>
       <c r="I16" s="22"/>
       <c r="J16" s="25"/>
-      <c r="M16" t="s">
-        <v>2</v>
-      </c>
-      <c r="N16" t="s">
-        <v>21</v>
-      </c>
-      <c r="O16" t="s">
-        <v>4</v>
-      </c>
-      <c r="P16" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q16" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="R16" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="17" spans="3:21" x14ac:dyDescent="0.3">
+      <c r="Q16" s="6"/>
+      <c r="R16" s="6"/>
+    </row>
+    <row r="17" spans="3:20" x14ac:dyDescent="0.3">
       <c r="C17" s="26" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D17" s="27" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E17" s="26">
         <v>5</v>
@@ -1408,29 +1484,29 @@
         <v>143.55250000000001</v>
       </c>
       <c r="J17" s="30"/>
+      <c r="M17" t="s">
+        <v>2</v>
+      </c>
+      <c r="N17" t="s">
+        <v>20</v>
+      </c>
       <c r="O17" t="s">
-        <v>14</v>
-      </c>
-      <c r="P17" t="s">
-        <v>6</v>
-      </c>
-      <c r="Q17" t="s">
-        <v>7</v>
-      </c>
-      <c r="R17" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="S17" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="T17" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="18" spans="3:21" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+      <c r="P17" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q17" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="R17" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="3:20" x14ac:dyDescent="0.3">
       <c r="C18" s="31"/>
       <c r="D18" s="32" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E18" s="31">
         <v>5</v>
@@ -1442,20 +1518,31 @@
       <c r="H18" s="34"/>
       <c r="I18" s="33"/>
       <c r="J18" s="35"/>
-      <c r="M18" t="s">
-        <v>12</v>
-      </c>
-      <c r="N18" t="s">
+      <c r="O18" t="s">
         <v>13</v>
       </c>
-      <c r="R18" s="6"/>
-    </row>
-    <row r="19" spans="3:21" x14ac:dyDescent="0.3">
+      <c r="P18" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>7</v>
+      </c>
+      <c r="R18" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="S18" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="T18" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19" spans="3:20" x14ac:dyDescent="0.3">
       <c r="C19" s="26" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D19" s="27" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E19" s="26">
         <v>4</v>
@@ -1474,34 +1561,17 @@
       </c>
       <c r="J19" s="30"/>
       <c r="M19" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="N19" t="s">
-        <v>16</v>
-      </c>
-      <c r="O19">
-        <v>0</v>
-      </c>
-      <c r="P19">
-        <v>3.02765</v>
-      </c>
-      <c r="Q19">
-        <v>806.33566800000006</v>
-      </c>
-      <c r="R19" s="6">
-        <v>0.1025192</v>
-      </c>
-      <c r="S19">
-        <v>0</v>
-      </c>
-      <c r="T19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="3:21" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+      <c r="R19" s="6"/>
+    </row>
+    <row r="20" spans="3:20" x14ac:dyDescent="0.3">
       <c r="C20" s="31"/>
       <c r="D20" s="32" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E20" s="31">
         <v>4</v>
@@ -1514,10 +1584,10 @@
       <c r="I20" s="33"/>
       <c r="J20" s="35"/>
       <c r="M20" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="N20" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O20">
         <v>0</v>
@@ -1526,10 +1596,10 @@
         <v>3.02765</v>
       </c>
       <c r="Q20">
-        <v>947.973479</v>
+        <v>806.33566800000006</v>
       </c>
       <c r="R20" s="6">
-        <v>3.9105809999999999E-9</v>
+        <v>0.1025192</v>
       </c>
       <c r="S20">
         <v>0</v>
@@ -1538,12 +1608,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="3:21" x14ac:dyDescent="0.3">
+    <row r="21" spans="3:20" x14ac:dyDescent="0.3">
       <c r="C21" s="26" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D21" s="27" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E21" s="26">
         <v>2</v>
@@ -1562,10 +1632,10 @@
       </c>
       <c r="J21" s="30"/>
       <c r="M21" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="N21" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O21">
         <v>0</v>
@@ -1574,10 +1644,10 @@
         <v>3.02765</v>
       </c>
       <c r="Q21">
-        <v>2710.086194</v>
+        <v>947.973479</v>
       </c>
       <c r="R21" s="6">
-        <v>2.3984829999999999E-2</v>
+        <v>3.9105809999999999E-9</v>
       </c>
       <c r="S21">
         <v>0</v>
@@ -1586,10 +1656,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="3:21" x14ac:dyDescent="0.3">
+    <row r="22" spans="3:20" x14ac:dyDescent="0.3">
       <c r="C22" s="31"/>
       <c r="D22" s="32" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E22" s="31">
         <v>2</v>
@@ -1602,10 +1672,10 @@
       <c r="I22" s="33"/>
       <c r="J22" s="35"/>
       <c r="M22" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="N22" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O22">
         <v>0</v>
@@ -1614,10 +1684,10 @@
         <v>3.02765</v>
       </c>
       <c r="Q22">
-        <v>1482.143701</v>
+        <v>2710.086194</v>
       </c>
       <c r="R22" s="6">
-        <v>9.1428799999999999</v>
+        <v>2.3984829999999999E-2</v>
       </c>
       <c r="S22">
         <v>0</v>
@@ -1626,12 +1696,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="3:21" x14ac:dyDescent="0.3">
+    <row r="23" spans="3:20" x14ac:dyDescent="0.3">
       <c r="C23" s="7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D23" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E23" s="7">
         <v>10</v>
@@ -1650,10 +1720,10 @@
       </c>
       <c r="J23" s="21"/>
       <c r="M23" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="N23" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O23">
         <v>0</v>
@@ -1662,10 +1732,10 @@
         <v>3.02765</v>
       </c>
       <c r="Q23">
-        <v>55.697513999999998</v>
+        <v>1482.143701</v>
       </c>
       <c r="R23" s="6">
-        <v>1.095445E-4</v>
+        <v>9.1428799999999999</v>
       </c>
       <c r="S23">
         <v>0</v>
@@ -1674,10 +1744,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="3:21" x14ac:dyDescent="0.3">
+    <row r="24" spans="3:20" x14ac:dyDescent="0.3">
       <c r="C24" s="7"/>
       <c r="D24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E24" s="7">
         <v>10</v>
@@ -1690,10 +1760,10 @@
       <c r="I24" s="22"/>
       <c r="J24" s="21"/>
       <c r="M24" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="N24" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O24">
         <v>0</v>
@@ -1702,10 +1772,10 @@
         <v>3.02765</v>
       </c>
       <c r="Q24">
-        <v>201.451528</v>
+        <v>55.697513999999998</v>
       </c>
       <c r="R24" s="6">
-        <v>143.55250000000001</v>
+        <v>1.095445E-4</v>
       </c>
       <c r="S24">
         <v>0</v>
@@ -1714,12 +1784,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="3:21" x14ac:dyDescent="0.3">
+    <row r="25" spans="3:20" x14ac:dyDescent="0.3">
       <c r="C25" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E25" s="3">
         <v>2</v>
@@ -1738,10 +1808,10 @@
       </c>
       <c r="J25" s="23"/>
       <c r="M25" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="N25" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O25">
         <v>0</v>
@@ -1750,10 +1820,10 @@
         <v>3.02765</v>
       </c>
       <c r="Q25">
-        <v>515.86293000000001</v>
+        <v>201.451528</v>
       </c>
       <c r="R25" s="6">
-        <v>146.67269999999999</v>
+        <v>143.55250000000001</v>
       </c>
       <c r="S25">
         <v>0</v>
@@ -1762,10 +1832,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="3:21" x14ac:dyDescent="0.3">
+    <row r="26" spans="3:20" x14ac:dyDescent="0.3">
       <c r="C26" s="16"/>
       <c r="D26" s="17" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E26" s="16">
         <v>2</v>
@@ -1778,10 +1848,10 @@
       <c r="I26" s="22"/>
       <c r="J26" s="25"/>
       <c r="M26" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="N26" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O26">
         <v>0</v>
@@ -1790,10 +1860,10 @@
         <v>3.02765</v>
       </c>
       <c r="Q26">
-        <v>4495.3310320000001</v>
+        <v>515.86293000000001</v>
       </c>
       <c r="R26" s="6">
-        <v>2319.5880000000002</v>
+        <v>146.67269999999999</v>
       </c>
       <c r="S26">
         <v>0</v>
@@ -1802,12 +1872,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="3:21" x14ac:dyDescent="0.3">
+    <row r="27" spans="3:20" x14ac:dyDescent="0.3">
+      <c r="C27" t="s">
+        <v>48</v>
+      </c>
       <c r="M27" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="N27" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O27">
         <v>0</v>
@@ -1816,10 +1889,10 @@
         <v>3.02765</v>
       </c>
       <c r="Q27">
-        <v>1355.4446370000001</v>
+        <v>4495.3310320000001</v>
       </c>
       <c r="R27" s="6">
-        <v>118.1583</v>
+        <v>2319.5880000000002</v>
       </c>
       <c r="S27">
         <v>0</v>
@@ -1828,12 +1901,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="3:21" x14ac:dyDescent="0.3">
+    <row r="28" spans="3:20" x14ac:dyDescent="0.3">
       <c r="M28" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="N28" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O28">
         <v>0</v>
@@ -1842,84 +1915,2371 @@
         <v>3.02765</v>
       </c>
       <c r="Q28">
+        <v>1355.4446370000001</v>
+      </c>
+      <c r="R28" s="6">
+        <v>118.1583</v>
+      </c>
+      <c r="S28">
+        <v>0</v>
+      </c>
+      <c r="T28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:20" x14ac:dyDescent="0.3">
+      <c r="M29" t="s">
+        <v>32</v>
+      </c>
+      <c r="N29" t="s">
+        <v>15</v>
+      </c>
+      <c r="O29">
+        <v>0</v>
+      </c>
+      <c r="P29">
+        <v>3.02765</v>
+      </c>
+      <c r="Q29">
         <v>33.534042999999997</v>
       </c>
-      <c r="R28" s="6">
+      <c r="R29" s="6">
         <v>4.0774329999999998E-8</v>
       </c>
-      <c r="S28">
-        <v>0</v>
-      </c>
-      <c r="T28">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="3:21" x14ac:dyDescent="0.3">
-      <c r="R29" s="6"/>
-    </row>
-    <row r="30" spans="3:21" x14ac:dyDescent="0.3">
-      <c r="Q30" t="s">
+      <c r="S29">
+        <v>0</v>
+      </c>
+      <c r="T29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:20" x14ac:dyDescent="0.3">
+      <c r="R30" s="6"/>
+    </row>
+    <row r="31" spans="3:20" x14ac:dyDescent="0.3">
+      <c r="Q31" t="s">
         <v>7</v>
       </c>
-      <c r="R30" t="s">
+      <c r="R31" t="s">
         <v>8</v>
       </c>
-      <c r="S30" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="31" spans="3:21" x14ac:dyDescent="0.3">
-      <c r="M31" t="s">
-        <v>19</v>
-      </c>
-      <c r="N31" t="s">
-        <v>16</v>
-      </c>
-      <c r="O31">
-        <v>20</v>
-      </c>
-      <c r="Q31">
-        <v>6569.9168900000004</v>
-      </c>
-      <c r="R31">
-        <v>0.99977099999999997</v>
-      </c>
-      <c r="S31">
-        <v>0.47947800000000002</v>
-      </c>
-    </row>
-    <row r="32" spans="3:21" x14ac:dyDescent="0.3">
+      <c r="S31" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="32" spans="3:20" x14ac:dyDescent="0.3">
+      <c r="M32" t="s">
+        <v>18</v>
+      </c>
       <c r="N32" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O32">
         <v>20</v>
       </c>
       <c r="Q32">
+        <v>6569.9168900000004</v>
+      </c>
+      <c r="R32">
+        <v>0.99977099999999997</v>
+      </c>
+      <c r="S32">
+        <v>0.47947800000000002</v>
+      </c>
+    </row>
+    <row r="33" spans="14:21" x14ac:dyDescent="0.3">
+      <c r="N33" t="s">
+        <v>15</v>
+      </c>
+      <c r="O33">
+        <v>20</v>
+      </c>
+      <c r="Q33">
         <v>1795.19146</v>
       </c>
-      <c r="R32" s="6">
+      <c r="R33" s="6">
         <v>4.8106590000000001E-10</v>
       </c>
-      <c r="S32" s="6">
+      <c r="S33" s="6">
         <v>1.5764049999999999E-10</v>
       </c>
-      <c r="T32" s="37" t="s">
-        <v>20</v>
-      </c>
-      <c r="U32" s="36"/>
+      <c r="T33" s="37" t="s">
+        <v>19</v>
+      </c>
+      <c r="U33" s="36"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="I4:J4"/>
-  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D73ACDBB-3041-4110-9FE8-59E6685037CA}">
+  <dimension ref="C1:U33"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="3" max="3" width="9.6640625" customWidth="1"/>
+    <col min="4" max="4" width="8.88671875" customWidth="1"/>
+    <col min="5" max="5" width="4.77734375" customWidth="1"/>
+    <col min="6" max="6" width="6.88671875" customWidth="1"/>
+    <col min="7" max="7" width="8.77734375" customWidth="1"/>
+    <col min="9" max="9" width="9" customWidth="1"/>
+    <col min="11" max="11" width="18.5546875" customWidth="1"/>
+    <col min="12" max="12" width="3" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="3:21" ht="23.4" x14ac:dyDescent="0.45">
+      <c r="C1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="3:21" x14ac:dyDescent="0.3">
+      <c r="C2" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="3" spans="3:21" x14ac:dyDescent="0.3">
+      <c r="C3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="N3" t="s">
+        <v>2</v>
+      </c>
+      <c r="O3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R3" t="s">
+        <v>37</v>
+      </c>
+      <c r="S3" t="s">
+        <v>38</v>
+      </c>
+      <c r="T3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="3:21" x14ac:dyDescent="0.3">
+      <c r="C4" s="3"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
+      <c r="J4" s="5"/>
+      <c r="N4" t="s">
+        <v>6</v>
+      </c>
+      <c r="O4" t="s">
+        <v>7</v>
+      </c>
+      <c r="P4" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>9</v>
+      </c>
+      <c r="R4" t="s">
+        <v>10</v>
+      </c>
+      <c r="S4" t="s">
+        <v>33</v>
+      </c>
+      <c r="T4" s="6"/>
+    </row>
+    <row r="5" spans="3:21" x14ac:dyDescent="0.3">
+      <c r="C5" s="7"/>
+      <c r="E5" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="H5" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="I5" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="J5" s="13"/>
+      <c r="M5" t="s">
+        <v>11</v>
+      </c>
+      <c r="N5" t="s">
+        <v>12</v>
+      </c>
+      <c r="O5" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q5" s="6"/>
+    </row>
+    <row r="6" spans="3:21" x14ac:dyDescent="0.3">
+      <c r="C6" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" s="16"/>
+      <c r="F6" s="17"/>
+      <c r="G6" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="H6" s="17"/>
+      <c r="I6" s="18"/>
+      <c r="J6" s="19"/>
+      <c r="M6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N6" t="s">
+        <v>15</v>
+      </c>
+      <c r="O6">
+        <v>10</v>
+      </c>
+      <c r="P6">
+        <v>58.5</v>
+      </c>
+      <c r="Q6" s="6">
+        <v>2920.6830100000002</v>
+      </c>
+      <c r="R6" s="6">
+        <v>0.25236170000000002</v>
+      </c>
+      <c r="S6">
+        <v>500</v>
+      </c>
+      <c r="T6">
+        <v>0</v>
+      </c>
+      <c r="U6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="3:21" x14ac:dyDescent="0.3">
+      <c r="C7" s="41" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7" s="42" t="s">
+        <v>15</v>
+      </c>
+      <c r="E7" s="41">
+        <v>13</v>
+      </c>
+      <c r="F7" s="42">
+        <v>500</v>
+      </c>
+      <c r="G7" s="43">
+        <v>3888.6478099999999</v>
+      </c>
+      <c r="H7" s="40">
+        <v>3.8567120000000003E-2</v>
+      </c>
+      <c r="I7" s="6">
+        <v>0.1025192</v>
+      </c>
+      <c r="J7" s="21"/>
+      <c r="M7" t="s">
+        <v>24</v>
+      </c>
+      <c r="N7" t="s">
+        <v>15</v>
+      </c>
+      <c r="O7">
+        <v>3</v>
+      </c>
+      <c r="P7">
+        <v>58.5</v>
+      </c>
+      <c r="Q7" s="6">
+        <v>1467.9233400000001</v>
+      </c>
+      <c r="R7" s="6">
+        <v>9.4757980000000001E-11</v>
+      </c>
+      <c r="S7">
+        <v>500</v>
+      </c>
+      <c r="T7">
+        <v>0</v>
+      </c>
+      <c r="U7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="3:21" x14ac:dyDescent="0.3">
+      <c r="C8" s="16"/>
+      <c r="D8" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="E8" s="16">
+        <v>13</v>
+      </c>
+      <c r="F8" s="17">
+        <v>500</v>
+      </c>
+      <c r="G8" s="22"/>
+      <c r="H8" s="24"/>
+      <c r="I8" s="22"/>
+      <c r="J8" s="25"/>
+      <c r="M8" t="s">
+        <v>25</v>
+      </c>
+      <c r="N8" t="s">
+        <v>15</v>
+      </c>
+      <c r="O8">
+        <v>5</v>
+      </c>
+      <c r="P8">
+        <v>58.5</v>
+      </c>
+      <c r="Q8">
+        <v>991.33965499999999</v>
+      </c>
+      <c r="R8" s="6">
+        <v>0.35452830000000002</v>
+      </c>
+      <c r="S8">
+        <v>500</v>
+      </c>
+      <c r="T8">
+        <v>0</v>
+      </c>
+      <c r="U8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="3:21" x14ac:dyDescent="0.3">
+      <c r="C9" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="D9" t="s">
+        <v>15</v>
+      </c>
+      <c r="E9" s="7">
+        <v>2</v>
+      </c>
+      <c r="F9">
+        <v>500</v>
+      </c>
+      <c r="G9" s="20">
+        <v>2070.49449</v>
+      </c>
+      <c r="H9" s="6">
+        <v>3.5015550000000002E-11</v>
+      </c>
+      <c r="I9" s="6">
+        <v>3.9105809999999999E-9</v>
+      </c>
+      <c r="J9" s="21"/>
+      <c r="M9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N9" t="s">
+        <v>15</v>
+      </c>
+      <c r="O9">
+        <v>6</v>
+      </c>
+      <c r="P9">
+        <v>58.5</v>
+      </c>
+      <c r="Q9" s="6">
+        <v>2620.81477</v>
+      </c>
+      <c r="R9" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="S9">
+        <v>500</v>
+      </c>
+      <c r="T9">
+        <v>0</v>
+      </c>
+      <c r="U9">
+        <v>0.82789199999999996</v>
+      </c>
+    </row>
+    <row r="10" spans="3:21" x14ac:dyDescent="0.3">
+      <c r="C10" s="16"/>
+      <c r="D10" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="E10" s="16">
+        <v>2</v>
+      </c>
+      <c r="F10" s="17">
+        <v>500</v>
+      </c>
+      <c r="G10" s="22"/>
+      <c r="H10" s="24"/>
+      <c r="I10" s="22"/>
+      <c r="J10" s="25"/>
+      <c r="M10" t="s">
+        <v>27</v>
+      </c>
+      <c r="N10" t="s">
+        <v>15</v>
+      </c>
+      <c r="O10">
+        <v>9</v>
+      </c>
+      <c r="P10">
+        <v>58.5</v>
+      </c>
+      <c r="Q10">
+        <v>1322.095685</v>
+      </c>
+      <c r="R10" s="6">
+        <v>1.9695170000000002E-6</v>
+      </c>
+      <c r="S10">
+        <v>500</v>
+      </c>
+      <c r="T10">
+        <v>0</v>
+      </c>
+      <c r="U10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="3:21" x14ac:dyDescent="0.3">
+      <c r="C11" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D11" t="s">
+        <v>15</v>
+      </c>
+      <c r="E11" s="7">
+        <v>5</v>
+      </c>
+      <c r="F11">
+        <v>500</v>
+      </c>
+      <c r="G11" s="20">
+        <v>6199.09094</v>
+      </c>
+      <c r="H11" s="6">
+        <v>4.7176989999999997E-3</v>
+      </c>
+      <c r="I11" s="6">
+        <v>2.3984829999999999E-2</v>
+      </c>
+      <c r="J11" s="21"/>
+      <c r="M11" t="s">
+        <v>28</v>
+      </c>
+      <c r="N11" t="s">
+        <v>15</v>
+      </c>
+      <c r="O11">
+        <v>15</v>
+      </c>
+      <c r="P11">
+        <v>58.5</v>
+      </c>
+      <c r="Q11" s="6">
+        <v>5779.8368049999999</v>
+      </c>
+      <c r="R11" s="6">
+        <v>995.71360000000004</v>
+      </c>
+      <c r="S11">
+        <v>500</v>
+      </c>
+      <c r="T11">
+        <v>0</v>
+      </c>
+      <c r="U11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="3:21" x14ac:dyDescent="0.3">
+      <c r="C12" s="16"/>
+      <c r="D12" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="E12" s="16">
+        <v>5</v>
+      </c>
+      <c r="F12" s="17">
+        <v>500</v>
+      </c>
+      <c r="G12" s="22"/>
+      <c r="H12" s="24"/>
+      <c r="I12" s="22"/>
+      <c r="J12" s="25"/>
+      <c r="M12" t="s">
+        <v>29</v>
+      </c>
+      <c r="N12" t="s">
+        <v>15</v>
+      </c>
+      <c r="O12">
+        <v>7</v>
+      </c>
+      <c r="P12">
+        <v>58.5</v>
+      </c>
+      <c r="Q12" s="6">
+        <v>2963.3486950000001</v>
+      </c>
+      <c r="R12" s="6">
+        <v>272.05380000000002</v>
+      </c>
+      <c r="S12">
+        <v>500</v>
+      </c>
+      <c r="T12">
+        <v>0</v>
+      </c>
+      <c r="U12">
+        <v>1.137E-3</v>
+      </c>
+    </row>
+    <row r="13" spans="3:21" x14ac:dyDescent="0.3">
+      <c r="C13" s="41" t="s">
+        <v>26</v>
+      </c>
+      <c r="D13" s="42" t="s">
+        <v>15</v>
+      </c>
+      <c r="E13" s="41">
+        <v>7</v>
+      </c>
+      <c r="F13" s="42">
+        <v>500</v>
+      </c>
+      <c r="G13" s="43">
+        <v>2395.6140399999999</v>
+      </c>
+      <c r="H13" s="40">
+        <v>0.61001050000000001</v>
+      </c>
+      <c r="I13" s="40">
+        <v>9.1428799999999999</v>
+      </c>
+      <c r="J13" s="21"/>
+      <c r="M13" t="s">
+        <v>30</v>
+      </c>
+      <c r="N13" t="s">
+        <v>15</v>
+      </c>
+      <c r="O13">
+        <v>22</v>
+      </c>
+      <c r="P13">
+        <v>58.5</v>
+      </c>
+      <c r="Q13" s="6">
+        <v>6047.4524350000002</v>
+      </c>
+      <c r="R13" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="S13">
+        <v>500</v>
+      </c>
+      <c r="T13">
+        <v>0</v>
+      </c>
+      <c r="U13">
+        <v>7.867299</v>
+      </c>
+    </row>
+    <row r="14" spans="3:21" x14ac:dyDescent="0.3">
+      <c r="C14" s="16"/>
+      <c r="D14" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="E14" s="16">
+        <v>7</v>
+      </c>
+      <c r="F14" s="17">
+        <v>500</v>
+      </c>
+      <c r="G14" s="22"/>
+      <c r="H14" s="24"/>
+      <c r="I14" s="22"/>
+      <c r="J14" s="25"/>
+      <c r="M14" t="s">
+        <v>31</v>
+      </c>
+      <c r="N14" t="s">
+        <v>15</v>
+      </c>
+      <c r="O14">
+        <v>9</v>
+      </c>
+      <c r="P14">
+        <v>58.5</v>
+      </c>
+      <c r="Q14" s="6">
+        <v>2437.34157</v>
+      </c>
+      <c r="R14" s="6">
+        <v>6.0207919999999998E-6</v>
+      </c>
+      <c r="S14">
+        <v>500</v>
+      </c>
+      <c r="T14">
+        <v>0</v>
+      </c>
+      <c r="U14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="3:21" x14ac:dyDescent="0.3">
+      <c r="C15" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="D15" t="s">
+        <v>15</v>
+      </c>
+      <c r="E15" s="7">
+        <v>10</v>
+      </c>
+      <c r="F15">
+        <v>500</v>
+      </c>
+      <c r="G15" s="20">
+        <v>1872.3066100000001</v>
+      </c>
+      <c r="H15" s="6">
+        <v>-2.034669E-4</v>
+      </c>
+      <c r="I15" s="6">
+        <v>1.095445E-4</v>
+      </c>
+      <c r="J15" s="21"/>
+      <c r="M15" t="s">
+        <v>32</v>
+      </c>
+      <c r="N15" t="s">
+        <v>15</v>
+      </c>
+      <c r="O15">
+        <v>2</v>
+      </c>
+      <c r="P15">
+        <v>58.5</v>
+      </c>
+      <c r="Q15" s="6">
+        <v>700.421425</v>
+      </c>
+      <c r="R15" s="6">
+        <v>0.38026890000000002</v>
+      </c>
+      <c r="S15">
+        <v>500</v>
+      </c>
+      <c r="T15">
+        <v>0</v>
+      </c>
+      <c r="U15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="3:21" x14ac:dyDescent="0.3">
+      <c r="C16" s="16"/>
+      <c r="D16" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="E16" s="16">
+        <v>10</v>
+      </c>
+      <c r="F16" s="17">
+        <v>500</v>
+      </c>
+      <c r="G16" s="22"/>
+      <c r="H16" s="24"/>
+      <c r="I16" s="22"/>
+      <c r="J16" s="25"/>
+    </row>
+    <row r="17" spans="3:20" x14ac:dyDescent="0.3">
+      <c r="C17" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="D17" s="27" t="s">
+        <v>15</v>
+      </c>
+      <c r="E17" s="26">
+        <v>5</v>
+      </c>
+      <c r="F17" s="27">
+        <v>500</v>
+      </c>
+      <c r="G17" s="28">
+        <v>1474.1254799999999</v>
+      </c>
+      <c r="H17" s="29">
+        <v>132.36429999999999</v>
+      </c>
+      <c r="I17" s="6">
+        <v>143.55250000000001</v>
+      </c>
+      <c r="J17" s="30"/>
+      <c r="N17" t="s">
+        <v>2</v>
+      </c>
+      <c r="O17" t="s">
+        <v>20</v>
+      </c>
+      <c r="P17" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q17" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="R17" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="S17" t="s">
+        <v>38</v>
+      </c>
+      <c r="T17" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="3:20" x14ac:dyDescent="0.3">
+      <c r="C18" s="31"/>
+      <c r="D18" s="32" t="s">
+        <v>17</v>
+      </c>
+      <c r="E18" s="31">
+        <v>5</v>
+      </c>
+      <c r="F18" s="32">
+        <v>500</v>
+      </c>
+      <c r="G18" s="33"/>
+      <c r="H18" s="34"/>
+      <c r="I18" s="33"/>
+      <c r="J18" s="35"/>
+      <c r="P18" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>33</v>
+      </c>
+      <c r="R18" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="19" spans="3:20" x14ac:dyDescent="0.3">
+      <c r="C19" s="26" t="s">
+        <v>29</v>
+      </c>
+      <c r="D19" s="27" t="s">
+        <v>15</v>
+      </c>
+      <c r="E19" s="26">
+        <v>4</v>
+      </c>
+      <c r="F19" s="27">
+        <v>500</v>
+      </c>
+      <c r="G19" s="28">
+        <v>2971.309385</v>
+      </c>
+      <c r="H19" s="29">
+        <v>317.53919999999999</v>
+      </c>
+      <c r="I19" s="6">
+        <v>146.67269999999999</v>
+      </c>
+      <c r="J19" s="30"/>
+      <c r="M19" t="s">
+        <v>11</v>
+      </c>
+      <c r="N19" t="s">
+        <v>12</v>
+      </c>
+      <c r="O19" t="s">
+        <v>13</v>
+      </c>
+      <c r="R19" s="6"/>
+      <c r="S19" s="6"/>
+    </row>
+    <row r="20" spans="3:20" x14ac:dyDescent="0.3">
+      <c r="C20" s="31"/>
+      <c r="D20" s="32" t="s">
+        <v>17</v>
+      </c>
+      <c r="E20" s="31">
+        <v>4</v>
+      </c>
+      <c r="F20" s="32">
+        <v>500</v>
+      </c>
+      <c r="G20" s="33"/>
+      <c r="H20" s="34"/>
+      <c r="I20" s="33"/>
+      <c r="J20" s="35"/>
+      <c r="M20" t="s">
+        <v>23</v>
+      </c>
+      <c r="N20" t="s">
+        <v>15</v>
+      </c>
+      <c r="O20">
+        <v>10</v>
+      </c>
+      <c r="P20" s="6">
+        <v>5.5589670000000001E-2</v>
+      </c>
+      <c r="Q20">
+        <v>0</v>
+      </c>
+      <c r="R20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:20" x14ac:dyDescent="0.3">
+      <c r="C21" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="D21" s="27" t="s">
+        <v>15</v>
+      </c>
+      <c r="E21" s="26">
+        <v>2</v>
+      </c>
+      <c r="F21" s="27">
+        <v>500</v>
+      </c>
+      <c r="G21" s="28">
+        <v>17000.01197</v>
+      </c>
+      <c r="H21" s="29">
+        <v>35.187019999999997</v>
+      </c>
+      <c r="I21" s="6">
+        <v>2319.5880000000002</v>
+      </c>
+      <c r="J21" s="30"/>
+      <c r="M21" t="s">
+        <v>24</v>
+      </c>
+      <c r="N21" t="s">
+        <v>15</v>
+      </c>
+      <c r="O21">
+        <v>3</v>
+      </c>
+      <c r="P21" s="6">
+        <v>3.627449E-9</v>
+      </c>
+      <c r="Q21">
+        <v>0</v>
+      </c>
+      <c r="R21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="3:20" x14ac:dyDescent="0.3">
+      <c r="C22" s="31"/>
+      <c r="D22" s="32" t="s">
+        <v>17</v>
+      </c>
+      <c r="E22" s="31">
+        <v>2</v>
+      </c>
+      <c r="F22" s="32">
+        <v>500</v>
+      </c>
+      <c r="G22" s="33"/>
+      <c r="H22" s="34"/>
+      <c r="I22" s="33"/>
+      <c r="J22" s="35"/>
+      <c r="M22" t="s">
+        <v>25</v>
+      </c>
+      <c r="N22" t="s">
+        <v>15</v>
+      </c>
+      <c r="O22">
+        <v>5</v>
+      </c>
+      <c r="P22" s="6">
+        <v>0.27507890000000002</v>
+      </c>
+      <c r="Q22">
+        <v>0.79225500000000004</v>
+      </c>
+      <c r="R22">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:20" x14ac:dyDescent="0.3">
+      <c r="C23" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="D23" t="s">
+        <v>15</v>
+      </c>
+      <c r="E23" s="7">
+        <v>10</v>
+      </c>
+      <c r="F23">
+        <v>500</v>
+      </c>
+      <c r="G23" s="20">
+        <v>3993.4907050000002</v>
+      </c>
+      <c r="H23" s="6">
+        <v>1.1281830000000001E-3</v>
+      </c>
+      <c r="I23" s="40">
+        <v>118.1583</v>
+      </c>
+      <c r="J23" s="21"/>
+      <c r="M23" t="s">
+        <v>26</v>
+      </c>
+      <c r="N23" t="s">
+        <v>15</v>
+      </c>
+      <c r="O23">
+        <v>6</v>
+      </c>
+      <c r="P23" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q23">
+        <v>6.8633569999999997</v>
+      </c>
+      <c r="R23">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24" spans="3:20" x14ac:dyDescent="0.3">
+      <c r="C24" s="7"/>
+      <c r="D24" t="s">
+        <v>17</v>
+      </c>
+      <c r="E24" s="7">
+        <v>10</v>
+      </c>
+      <c r="F24">
+        <v>500</v>
+      </c>
+      <c r="G24" s="20"/>
+      <c r="H24" s="6"/>
+      <c r="I24" s="22"/>
+      <c r="J24" s="21"/>
+      <c r="M24" t="s">
+        <v>27</v>
+      </c>
+      <c r="N24" t="s">
+        <v>15</v>
+      </c>
+      <c r="O24">
+        <v>9</v>
+      </c>
+      <c r="P24" s="6">
+        <v>5.9642769999999998E-2</v>
+      </c>
+      <c r="Q24">
+        <v>0</v>
+      </c>
+      <c r="R24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:20" x14ac:dyDescent="0.3">
+      <c r="C25" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E25" s="3">
+        <v>2</v>
+      </c>
+      <c r="F25" s="4">
+        <v>500</v>
+      </c>
+      <c r="G25" s="38">
+        <v>609.53940999999998</v>
+      </c>
+      <c r="H25" s="39">
+        <v>3.1007420000000003E-8</v>
+      </c>
+      <c r="I25" s="6">
+        <v>4.0774329999999998E-8</v>
+      </c>
+      <c r="J25" s="23"/>
+      <c r="M25" t="s">
+        <v>28</v>
+      </c>
+      <c r="N25" t="s">
+        <v>15</v>
+      </c>
+      <c r="O25">
+        <v>15</v>
+      </c>
+      <c r="P25" s="6">
+        <v>553.72860000000003</v>
+      </c>
+      <c r="Q25">
+        <v>0</v>
+      </c>
+      <c r="R25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:20" x14ac:dyDescent="0.3">
+      <c r="C26" s="16"/>
+      <c r="D26" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="E26" s="16">
+        <v>2</v>
+      </c>
+      <c r="F26" s="17">
+        <v>500</v>
+      </c>
+      <c r="G26" s="22"/>
+      <c r="H26" s="24"/>
+      <c r="I26" s="22"/>
+      <c r="J26" s="25"/>
+      <c r="M26" t="s">
+        <v>29</v>
+      </c>
+      <c r="N26" t="s">
+        <v>15</v>
+      </c>
+      <c r="O26">
+        <v>7</v>
+      </c>
+      <c r="P26" s="6">
+        <v>78.527100000000004</v>
+      </c>
+      <c r="Q26">
+        <v>9.6179999999999998E-3</v>
+      </c>
+      <c r="R26">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" spans="3:20" x14ac:dyDescent="0.3">
+      <c r="C27" t="s">
+        <v>49</v>
+      </c>
+      <c r="M27" t="s">
+        <v>30</v>
+      </c>
+      <c r="N27" t="s">
+        <v>15</v>
+      </c>
+      <c r="O27">
+        <v>22</v>
+      </c>
+      <c r="P27" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q27">
+        <v>9.5238270000000007</v>
+      </c>
+      <c r="R27">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="28" spans="3:20" x14ac:dyDescent="0.3">
+      <c r="M28" t="s">
+        <v>31</v>
+      </c>
+      <c r="N28" t="s">
+        <v>15</v>
+      </c>
+      <c r="O28">
+        <v>9</v>
+      </c>
+      <c r="P28" s="6">
+        <v>3.2697749999999999E-9</v>
+      </c>
+      <c r="Q28">
+        <v>0</v>
+      </c>
+      <c r="R28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:20" x14ac:dyDescent="0.3">
+      <c r="M29" t="s">
+        <v>32</v>
+      </c>
+      <c r="N29" t="s">
+        <v>15</v>
+      </c>
+      <c r="O29">
+        <v>2</v>
+      </c>
+      <c r="P29" s="6">
+        <v>0.24222579999999999</v>
+      </c>
+      <c r="Q29">
+        <v>0</v>
+      </c>
+      <c r="R29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:20" x14ac:dyDescent="0.3">
+      <c r="R30" s="6"/>
+    </row>
+    <row r="31" spans="3:20" x14ac:dyDescent="0.3">
+      <c r="Q31" t="s">
+        <v>7</v>
+      </c>
+      <c r="R31" t="s">
+        <v>8</v>
+      </c>
+      <c r="S31" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="32" spans="3:20" x14ac:dyDescent="0.3">
+      <c r="M32" t="s">
+        <v>18</v>
+      </c>
+      <c r="N32" t="s">
+        <v>15</v>
+      </c>
+      <c r="O32">
+        <v>20</v>
+      </c>
+      <c r="Q32">
+        <v>6569.9168900000004</v>
+      </c>
+      <c r="R32">
+        <v>0.99977099999999997</v>
+      </c>
+      <c r="S32">
+        <v>0.47947800000000002</v>
+      </c>
+    </row>
+    <row r="33" spans="14:21" x14ac:dyDescent="0.3">
+      <c r="N33" t="s">
+        <v>15</v>
+      </c>
+      <c r="O33">
+        <v>20</v>
+      </c>
+      <c r="Q33">
+        <v>1795.19146</v>
+      </c>
+      <c r="R33" s="6">
+        <v>4.8106590000000001E-10</v>
+      </c>
+      <c r="S33" s="6">
+        <v>1.5764049999999999E-10</v>
+      </c>
+      <c r="T33" s="37" t="s">
+        <v>19</v>
+      </c>
+      <c r="U33" s="36"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE45503C-F2E8-4674-A77D-9967A224D2EC}">
+  <dimension ref="C1:U33"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="3" max="3" width="9.6640625" customWidth="1"/>
+    <col min="4" max="4" width="8.88671875" customWidth="1"/>
+    <col min="5" max="5" width="4.77734375" customWidth="1"/>
+    <col min="6" max="6" width="6.88671875" customWidth="1"/>
+    <col min="7" max="7" width="8.77734375" customWidth="1"/>
+    <col min="9" max="9" width="9" customWidth="1"/>
+    <col min="11" max="11" width="18.5546875" customWidth="1"/>
+    <col min="12" max="12" width="3" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="3:21" ht="23.4" x14ac:dyDescent="0.45">
+      <c r="C1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="3:21" x14ac:dyDescent="0.3">
+      <c r="C2" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="3" spans="3:21" x14ac:dyDescent="0.3">
+      <c r="C3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="N3" t="s">
+        <v>2</v>
+      </c>
+      <c r="O3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R3" t="s">
+        <v>22</v>
+      </c>
+      <c r="S3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="3:21" x14ac:dyDescent="0.3">
+      <c r="C4" s="3"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
+      <c r="J4" s="5"/>
+      <c r="P4" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>7</v>
+      </c>
+      <c r="R4" t="s">
+        <v>8</v>
+      </c>
+      <c r="S4" t="s">
+        <v>9</v>
+      </c>
+      <c r="T4" t="s">
+        <v>10</v>
+      </c>
+      <c r="U4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5" spans="3:21" x14ac:dyDescent="0.3">
+      <c r="C5" s="7"/>
+      <c r="E5" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="H5" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="I5" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="J5" s="13"/>
+      <c r="M5" t="s">
+        <v>11</v>
+      </c>
+      <c r="N5" t="s">
+        <v>12</v>
+      </c>
+      <c r="O5" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q5" s="6"/>
+    </row>
+    <row r="6" spans="3:21" x14ac:dyDescent="0.3">
+      <c r="C6" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" s="16"/>
+      <c r="F6" s="17"/>
+      <c r="G6" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="H6" s="17"/>
+      <c r="I6" s="18"/>
+      <c r="J6" s="19"/>
+      <c r="M6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N6" t="s">
+        <v>15</v>
+      </c>
+      <c r="O6">
+        <v>10</v>
+      </c>
+      <c r="P6">
+        <v>58.5</v>
+      </c>
+      <c r="Q6" s="6">
+        <v>3592.6765999999998</v>
+      </c>
+      <c r="R6" s="6">
+        <v>0.25236170000000002</v>
+      </c>
+      <c r="S6" s="6">
+        <v>5.5589670000000001E-2</v>
+      </c>
+      <c r="T6">
+        <v>0</v>
+      </c>
+      <c r="U6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="3:21" x14ac:dyDescent="0.3">
+      <c r="C7" s="41" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7" s="42" t="s">
+        <v>15</v>
+      </c>
+      <c r="E7" s="41">
+        <v>13</v>
+      </c>
+      <c r="F7" s="42">
+        <v>500</v>
+      </c>
+      <c r="G7" s="43">
+        <v>3888.6478099999999</v>
+      </c>
+      <c r="H7" s="40">
+        <v>0.25236170000000002</v>
+      </c>
+      <c r="I7" s="6">
+        <v>5.5589670000000001E-2</v>
+      </c>
+      <c r="J7" s="21"/>
+      <c r="M7" t="s">
+        <v>24</v>
+      </c>
+      <c r="N7" t="s">
+        <v>15</v>
+      </c>
+      <c r="O7">
+        <v>3</v>
+      </c>
+      <c r="P7">
+        <v>58.5</v>
+      </c>
+      <c r="Q7" s="6">
+        <v>1478.997775</v>
+      </c>
+      <c r="R7" s="6">
+        <v>9.4757980000000001E-11</v>
+      </c>
+      <c r="S7" s="6">
+        <v>3.627449E-9</v>
+      </c>
+      <c r="T7">
+        <v>0</v>
+      </c>
+      <c r="U7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="3:21" x14ac:dyDescent="0.3">
+      <c r="C8" s="16"/>
+      <c r="D8" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="E8" s="16">
+        <v>13</v>
+      </c>
+      <c r="F8" s="17">
+        <v>500</v>
+      </c>
+      <c r="G8" s="22"/>
+      <c r="H8" s="24"/>
+      <c r="I8" s="22"/>
+      <c r="J8" s="25"/>
+      <c r="M8" t="s">
+        <v>25</v>
+      </c>
+      <c r="N8" t="s">
+        <v>15</v>
+      </c>
+      <c r="O8">
+        <v>5</v>
+      </c>
+      <c r="P8">
+        <v>58.5</v>
+      </c>
+      <c r="Q8">
+        <v>1140.0182950000001</v>
+      </c>
+      <c r="R8" s="6">
+        <v>0.39021549999999999</v>
+      </c>
+      <c r="S8" s="6">
+        <v>0.25917600000000002</v>
+      </c>
+      <c r="T8">
+        <v>0</v>
+      </c>
+      <c r="U8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="3:21" x14ac:dyDescent="0.3">
+      <c r="C9" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="D9" t="s">
+        <v>15</v>
+      </c>
+      <c r="E9" s="7">
+        <v>2</v>
+      </c>
+      <c r="F9">
+        <v>500</v>
+      </c>
+      <c r="G9" s="20">
+        <v>2070.49449</v>
+      </c>
+      <c r="H9" s="6">
+        <v>9.4757980000000001E-11</v>
+      </c>
+      <c r="I9" s="6">
+        <v>3.627449E-9</v>
+      </c>
+      <c r="J9" s="21"/>
+      <c r="M9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N9" t="s">
+        <v>15</v>
+      </c>
+      <c r="O9">
+        <v>6</v>
+      </c>
+      <c r="P9">
+        <v>58.5</v>
+      </c>
+      <c r="Q9" s="6">
+        <v>5101.20172</v>
+      </c>
+      <c r="R9" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="S9" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="T9">
+        <v>0</v>
+      </c>
+      <c r="U9">
+        <v>0.82789199999999996</v>
+      </c>
+    </row>
+    <row r="10" spans="3:21" x14ac:dyDescent="0.3">
+      <c r="C10" s="16"/>
+      <c r="D10" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="E10" s="16">
+        <v>2</v>
+      </c>
+      <c r="F10" s="17">
+        <v>500</v>
+      </c>
+      <c r="G10" s="22"/>
+      <c r="H10" s="24"/>
+      <c r="I10" s="22"/>
+      <c r="J10" s="25"/>
+      <c r="M10" t="s">
+        <v>27</v>
+      </c>
+      <c r="N10" t="s">
+        <v>15</v>
+      </c>
+      <c r="O10">
+        <v>9</v>
+      </c>
+      <c r="P10">
+        <v>58.5</v>
+      </c>
+      <c r="Q10">
+        <v>4673.11391</v>
+      </c>
+      <c r="R10" s="6">
+        <v>8.6602490000000002E-5</v>
+      </c>
+      <c r="S10" s="6">
+        <v>1.2550110000000001E-4</v>
+      </c>
+      <c r="T10">
+        <v>0</v>
+      </c>
+      <c r="U10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="3:21" x14ac:dyDescent="0.3">
+      <c r="C11" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D11" t="s">
+        <v>15</v>
+      </c>
+      <c r="E11" s="7">
+        <v>5</v>
+      </c>
+      <c r="F11">
+        <v>500</v>
+      </c>
+      <c r="G11" s="20">
+        <v>6199.09094</v>
+      </c>
+      <c r="H11" s="6">
+        <v>0.39021549999999999</v>
+      </c>
+      <c r="I11" s="6">
+        <v>0.25917600000000002</v>
+      </c>
+      <c r="J11" s="21"/>
+      <c r="M11" t="s">
+        <v>28</v>
+      </c>
+      <c r="N11" t="s">
+        <v>15</v>
+      </c>
+      <c r="O11">
+        <v>15</v>
+      </c>
+      <c r="P11">
+        <v>58.5</v>
+      </c>
+      <c r="Q11" s="6">
+        <v>8734.5927649999994</v>
+      </c>
+      <c r="R11" s="6">
+        <v>978.48789999999997</v>
+      </c>
+      <c r="S11" s="6">
+        <v>761.50710000000004</v>
+      </c>
+      <c r="T11">
+        <v>0</v>
+      </c>
+      <c r="U11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="3:21" x14ac:dyDescent="0.3">
+      <c r="C12" s="16"/>
+      <c r="D12" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="E12" s="16">
+        <v>5</v>
+      </c>
+      <c r="F12" s="17">
+        <v>500</v>
+      </c>
+      <c r="G12" s="22"/>
+      <c r="H12" s="24"/>
+      <c r="I12" s="22"/>
+      <c r="J12" s="25"/>
+      <c r="M12" t="s">
+        <v>29</v>
+      </c>
+      <c r="N12" t="s">
+        <v>15</v>
+      </c>
+      <c r="O12">
+        <v>7</v>
+      </c>
+      <c r="P12">
+        <v>58.5</v>
+      </c>
+      <c r="Q12" s="6">
+        <v>10614.685755</v>
+      </c>
+      <c r="R12" s="6">
+        <v>272.6311</v>
+      </c>
+      <c r="S12" s="6">
+        <v>139.57169999999999</v>
+      </c>
+      <c r="T12">
+        <v>0</v>
+      </c>
+      <c r="U12">
+        <v>2.444E-3</v>
+      </c>
+    </row>
+    <row r="13" spans="3:21" x14ac:dyDescent="0.3">
+      <c r="C13" s="41" t="s">
+        <v>26</v>
+      </c>
+      <c r="D13" s="42" t="s">
+        <v>15</v>
+      </c>
+      <c r="E13" s="41">
+        <v>7</v>
+      </c>
+      <c r="F13" s="42">
+        <v>500</v>
+      </c>
+      <c r="G13" s="43">
+        <v>2395.6140399999999</v>
+      </c>
+      <c r="H13" s="40" t="s">
+        <v>45</v>
+      </c>
+      <c r="I13" s="40" t="s">
+        <v>45</v>
+      </c>
+      <c r="J13" s="21"/>
+      <c r="M13" t="s">
+        <v>30</v>
+      </c>
+      <c r="N13" t="s">
+        <v>15</v>
+      </c>
+      <c r="O13">
+        <v>22</v>
+      </c>
+      <c r="P13">
+        <v>58.5</v>
+      </c>
+      <c r="Q13" s="6">
+        <v>5244.9437250000001</v>
+      </c>
+      <c r="R13" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="S13" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="T13">
+        <v>0</v>
+      </c>
+      <c r="U13">
+        <v>6.4378260000000003</v>
+      </c>
+    </row>
+    <row r="14" spans="3:21" x14ac:dyDescent="0.3">
+      <c r="C14" s="16"/>
+      <c r="D14" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="E14" s="16">
+        <v>7</v>
+      </c>
+      <c r="F14" s="17">
+        <v>500</v>
+      </c>
+      <c r="G14" s="22"/>
+      <c r="H14" s="24"/>
+      <c r="I14" s="22"/>
+      <c r="J14" s="25"/>
+      <c r="M14" t="s">
+        <v>31</v>
+      </c>
+      <c r="N14" t="s">
+        <v>15</v>
+      </c>
+      <c r="O14">
+        <v>9</v>
+      </c>
+      <c r="P14">
+        <v>58.5</v>
+      </c>
+      <c r="Q14" s="6">
+        <v>2785.9532899999999</v>
+      </c>
+      <c r="R14" s="6">
+        <v>6.6843999999999999E-6</v>
+      </c>
+      <c r="S14" s="6">
+        <v>2.084729E-3</v>
+      </c>
+      <c r="T14">
+        <v>0</v>
+      </c>
+      <c r="U14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="3:21" x14ac:dyDescent="0.3">
+      <c r="C15" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="D15" t="s">
+        <v>15</v>
+      </c>
+      <c r="E15" s="7">
+        <v>10</v>
+      </c>
+      <c r="F15">
+        <v>500</v>
+      </c>
+      <c r="G15" s="20">
+        <v>1872.3066100000001</v>
+      </c>
+      <c r="H15" s="6">
+        <v>8.6602490000000002E-5</v>
+      </c>
+      <c r="I15" s="6">
+        <v>1.2550110000000001E-4</v>
+      </c>
+      <c r="J15" s="21"/>
+      <c r="M15" t="s">
+        <v>32</v>
+      </c>
+      <c r="N15" t="s">
+        <v>15</v>
+      </c>
+      <c r="O15">
+        <v>2</v>
+      </c>
+      <c r="P15">
+        <v>58.5</v>
+      </c>
+      <c r="Q15" s="6">
+        <v>682.56723</v>
+      </c>
+      <c r="R15" s="6">
+        <v>0.3811059</v>
+      </c>
+      <c r="S15" s="6">
+        <v>0.24947330000000001</v>
+      </c>
+      <c r="T15">
+        <v>0</v>
+      </c>
+      <c r="U15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="3:21" x14ac:dyDescent="0.3">
+      <c r="C16" s="16"/>
+      <c r="D16" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="E16" s="16">
+        <v>10</v>
+      </c>
+      <c r="F16" s="17">
+        <v>500</v>
+      </c>
+      <c r="G16" s="22"/>
+      <c r="H16" s="24"/>
+      <c r="I16" s="22"/>
+      <c r="J16" s="25"/>
+      <c r="Q16" s="6"/>
+      <c r="R16" s="6"/>
+    </row>
+    <row r="17" spans="3:21" x14ac:dyDescent="0.3">
+      <c r="C17" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="D17" s="27" t="s">
+        <v>15</v>
+      </c>
+      <c r="E17" s="26">
+        <v>5</v>
+      </c>
+      <c r="F17" s="27">
+        <v>500</v>
+      </c>
+      <c r="G17" s="28">
+        <v>1474.1254799999999</v>
+      </c>
+      <c r="H17" s="29">
+        <v>978.48789999999997</v>
+      </c>
+      <c r="I17" s="6">
+        <v>761.50710000000004</v>
+      </c>
+      <c r="J17" s="30"/>
+      <c r="N17" t="s">
+        <v>2</v>
+      </c>
+      <c r="O17" t="s">
+        <v>20</v>
+      </c>
+      <c r="P17" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q17" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="R17" t="s">
+        <v>22</v>
+      </c>
+      <c r="S17" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="3:21" x14ac:dyDescent="0.3">
+      <c r="C18" s="31"/>
+      <c r="D18" s="32" t="s">
+        <v>17</v>
+      </c>
+      <c r="E18" s="31">
+        <v>5</v>
+      </c>
+      <c r="F18" s="32">
+        <v>500</v>
+      </c>
+      <c r="G18" s="33"/>
+      <c r="H18" s="34"/>
+      <c r="I18" s="33"/>
+      <c r="J18" s="35"/>
+      <c r="P18" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>7</v>
+      </c>
+      <c r="R18" t="s">
+        <v>8</v>
+      </c>
+      <c r="S18" t="s">
+        <v>9</v>
+      </c>
+      <c r="T18" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="U18" s="6" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="19" spans="3:21" x14ac:dyDescent="0.3">
+      <c r="C19" s="26" t="s">
+        <v>29</v>
+      </c>
+      <c r="D19" s="27" t="s">
+        <v>15</v>
+      </c>
+      <c r="E19" s="26">
+        <v>4</v>
+      </c>
+      <c r="F19" s="27">
+        <v>500</v>
+      </c>
+      <c r="G19" s="28">
+        <v>2971.309385</v>
+      </c>
+      <c r="H19" s="29">
+        <v>272.6311</v>
+      </c>
+      <c r="I19" s="6">
+        <v>139.57169999999999</v>
+      </c>
+      <c r="J19" s="30"/>
+      <c r="M19" t="s">
+        <v>11</v>
+      </c>
+      <c r="N19" t="s">
+        <v>12</v>
+      </c>
+      <c r="O19" t="s">
+        <v>13</v>
+      </c>
+      <c r="R19" s="6"/>
+    </row>
+    <row r="20" spans="3:21" x14ac:dyDescent="0.3">
+      <c r="C20" s="31"/>
+      <c r="D20" s="32" t="s">
+        <v>17</v>
+      </c>
+      <c r="E20" s="31">
+        <v>4</v>
+      </c>
+      <c r="F20" s="32">
+        <v>500</v>
+      </c>
+      <c r="G20" s="33"/>
+      <c r="H20" s="34"/>
+      <c r="I20" s="33"/>
+      <c r="J20" s="35"/>
+      <c r="M20" t="s">
+        <v>23</v>
+      </c>
+      <c r="N20" t="s">
+        <v>15</v>
+      </c>
+      <c r="O20">
+        <v>10</v>
+      </c>
+      <c r="P20">
+        <v>3.02765</v>
+      </c>
+      <c r="Q20">
+        <v>1305.014868</v>
+      </c>
+      <c r="R20" s="6">
+        <v>5.5589670000000001E-2</v>
+      </c>
+      <c r="S20">
+        <v>0</v>
+      </c>
+      <c r="T20">
+        <v>0</v>
+      </c>
+      <c r="U20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:21" x14ac:dyDescent="0.3">
+      <c r="C21" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="D21" s="27" t="s">
+        <v>15</v>
+      </c>
+      <c r="E21" s="26">
+        <v>2</v>
+      </c>
+      <c r="F21" s="27">
+        <v>500</v>
+      </c>
+      <c r="G21" s="28">
+        <v>17000.01197</v>
+      </c>
+      <c r="H21" s="29" t="s">
+        <v>45</v>
+      </c>
+      <c r="I21" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="J21" s="30"/>
+      <c r="M21" t="s">
+        <v>24</v>
+      </c>
+      <c r="N21" t="s">
+        <v>15</v>
+      </c>
+      <c r="O21">
+        <v>3</v>
+      </c>
+      <c r="P21">
+        <v>3.02765</v>
+      </c>
+      <c r="Q21">
+        <v>107.874757</v>
+      </c>
+      <c r="R21" s="6">
+        <v>3.627449E-9</v>
+      </c>
+      <c r="S21">
+        <v>0</v>
+      </c>
+      <c r="T21">
+        <v>0</v>
+      </c>
+      <c r="U21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="3:21" x14ac:dyDescent="0.3">
+      <c r="C22" s="31"/>
+      <c r="D22" s="32" t="s">
+        <v>17</v>
+      </c>
+      <c r="E22" s="31">
+        <v>2</v>
+      </c>
+      <c r="F22" s="32">
+        <v>500</v>
+      </c>
+      <c r="G22" s="33"/>
+      <c r="H22" s="34"/>
+      <c r="I22" s="33"/>
+      <c r="J22" s="35"/>
+      <c r="M22" t="s">
+        <v>25</v>
+      </c>
+      <c r="N22" t="s">
+        <v>15</v>
+      </c>
+      <c r="O22">
+        <v>5</v>
+      </c>
+      <c r="P22">
+        <v>3.02765</v>
+      </c>
+      <c r="Q22">
+        <v>379.071887</v>
+      </c>
+      <c r="R22" s="6">
+        <v>0.25917600000000002</v>
+      </c>
+      <c r="S22">
+        <v>0</v>
+      </c>
+      <c r="T22">
+        <v>0</v>
+      </c>
+      <c r="U22">
+        <v>2.2192090000000002</v>
+      </c>
+    </row>
+    <row r="23" spans="3:21" x14ac:dyDescent="0.3">
+      <c r="C23" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="D23" t="s">
+        <v>15</v>
+      </c>
+      <c r="E23" s="7">
+        <v>10</v>
+      </c>
+      <c r="F23">
+        <v>500</v>
+      </c>
+      <c r="G23" s="20">
+        <v>3993.4907050000002</v>
+      </c>
+      <c r="H23" s="6">
+        <v>6.6843999999999999E-6</v>
+      </c>
+      <c r="I23" s="40">
+        <v>2.084729E-3</v>
+      </c>
+      <c r="J23" s="21"/>
+      <c r="M23" t="s">
+        <v>26</v>
+      </c>
+      <c r="N23" t="s">
+        <v>15</v>
+      </c>
+      <c r="O23">
+        <v>6</v>
+      </c>
+      <c r="P23">
+        <v>3.02765</v>
+      </c>
+      <c r="Q23">
+        <v>4517.8191459999998</v>
+      </c>
+      <c r="R23" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="S23">
+        <v>0</v>
+      </c>
+      <c r="T23">
+        <v>0</v>
+      </c>
+      <c r="U23">
+        <v>6.8633569999999997</v>
+      </c>
+    </row>
+    <row r="24" spans="3:21" x14ac:dyDescent="0.3">
+      <c r="C24" s="7"/>
+      <c r="D24" t="s">
+        <v>17</v>
+      </c>
+      <c r="E24" s="7">
+        <v>10</v>
+      </c>
+      <c r="F24">
+        <v>500</v>
+      </c>
+      <c r="G24" s="20"/>
+      <c r="H24" s="6"/>
+      <c r="I24" s="22"/>
+      <c r="J24" s="21"/>
+      <c r="M24" t="s">
+        <v>27</v>
+      </c>
+      <c r="N24" t="s">
+        <v>15</v>
+      </c>
+      <c r="O24">
+        <v>9</v>
+      </c>
+      <c r="P24">
+        <v>3.02765</v>
+      </c>
+      <c r="Q24">
+        <v>547385.12895499996</v>
+      </c>
+      <c r="R24" s="6">
+        <v>1.2550110000000001E-4</v>
+      </c>
+      <c r="S24">
+        <v>0</v>
+      </c>
+      <c r="T24">
+        <v>0</v>
+      </c>
+      <c r="U24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:21" x14ac:dyDescent="0.3">
+      <c r="C25" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E25" s="3">
+        <v>2</v>
+      </c>
+      <c r="F25" s="4">
+        <v>500</v>
+      </c>
+      <c r="G25" s="38">
+        <v>609.53940999999998</v>
+      </c>
+      <c r="H25" s="39">
+        <v>0.3811059</v>
+      </c>
+      <c r="I25" s="6">
+        <v>0.24947330000000001</v>
+      </c>
+      <c r="J25" s="23"/>
+      <c r="M25" t="s">
+        <v>28</v>
+      </c>
+      <c r="N25" t="s">
+        <v>15</v>
+      </c>
+      <c r="O25">
+        <v>15</v>
+      </c>
+      <c r="P25">
+        <v>3.02765</v>
+      </c>
+      <c r="Q25">
+        <v>934.82921799999997</v>
+      </c>
+      <c r="R25" s="6">
+        <v>761.50710000000004</v>
+      </c>
+      <c r="S25">
+        <v>0</v>
+      </c>
+      <c r="T25">
+        <v>0</v>
+      </c>
+      <c r="U25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:21" x14ac:dyDescent="0.3">
+      <c r="C26" s="16"/>
+      <c r="D26" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="E26" s="16">
+        <v>2</v>
+      </c>
+      <c r="F26" s="17">
+        <v>500</v>
+      </c>
+      <c r="G26" s="22"/>
+      <c r="H26" s="24"/>
+      <c r="I26" s="22"/>
+      <c r="J26" s="25"/>
+      <c r="M26" t="s">
+        <v>29</v>
+      </c>
+      <c r="N26" t="s">
+        <v>15</v>
+      </c>
+      <c r="O26">
+        <v>7</v>
+      </c>
+      <c r="P26">
+        <v>3.02765</v>
+      </c>
+      <c r="Q26">
+        <v>1095.5545890000001</v>
+      </c>
+      <c r="R26" s="6">
+        <v>139.57169999999999</v>
+      </c>
+      <c r="S26">
+        <v>0</v>
+      </c>
+      <c r="T26">
+        <v>0</v>
+      </c>
+      <c r="U26">
+        <v>1.2312E-2</v>
+      </c>
+    </row>
+    <row r="27" spans="3:21" x14ac:dyDescent="0.3">
+      <c r="C27" t="s">
+        <v>50</v>
+      </c>
+      <c r="M27" t="s">
+        <v>30</v>
+      </c>
+      <c r="N27" t="s">
+        <v>15</v>
+      </c>
+      <c r="O27">
+        <v>22</v>
+      </c>
+      <c r="P27">
+        <v>3.02765</v>
+      </c>
+      <c r="Q27">
+        <v>452.61137400000001</v>
+      </c>
+      <c r="R27" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="S27">
+        <v>0</v>
+      </c>
+      <c r="T27">
+        <v>0</v>
+      </c>
+      <c r="U27">
+        <v>8.3941579999999991</v>
+      </c>
+    </row>
+    <row r="28" spans="3:21" x14ac:dyDescent="0.3">
+      <c r="M28" t="s">
+        <v>31</v>
+      </c>
+      <c r="N28" t="s">
+        <v>15</v>
+      </c>
+      <c r="O28">
+        <v>9</v>
+      </c>
+      <c r="P28">
+        <v>3.02765</v>
+      </c>
+      <c r="Q28">
+        <v>390.36645700000003</v>
+      </c>
+      <c r="R28" s="6">
+        <v>2.084729E-3</v>
+      </c>
+      <c r="S28">
+        <v>0</v>
+      </c>
+      <c r="T28">
+        <v>0</v>
+      </c>
+      <c r="U28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:21" x14ac:dyDescent="0.3">
+      <c r="M29" t="s">
+        <v>32</v>
+      </c>
+      <c r="N29" t="s">
+        <v>15</v>
+      </c>
+      <c r="O29">
+        <v>2</v>
+      </c>
+      <c r="P29">
+        <v>3.02765</v>
+      </c>
+      <c r="Q29">
+        <v>148.856977</v>
+      </c>
+      <c r="R29" s="6">
+        <v>0.24947330000000001</v>
+      </c>
+      <c r="S29">
+        <v>0</v>
+      </c>
+      <c r="T29">
+        <v>0</v>
+      </c>
+      <c r="U29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:21" x14ac:dyDescent="0.3">
+      <c r="R30" s="6"/>
+    </row>
+    <row r="31" spans="3:21" x14ac:dyDescent="0.3">
+      <c r="Q31" t="s">
+        <v>7</v>
+      </c>
+      <c r="R31" t="s">
+        <v>8</v>
+      </c>
+      <c r="S31" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="32" spans="3:21" x14ac:dyDescent="0.3">
+      <c r="M32" t="s">
+        <v>18</v>
+      </c>
+      <c r="N32" t="s">
+        <v>15</v>
+      </c>
+      <c r="O32">
+        <v>20</v>
+      </c>
+      <c r="Q32">
+        <v>6569.9168900000004</v>
+      </c>
+      <c r="R32">
+        <v>0.99977099999999997</v>
+      </c>
+      <c r="S32">
+        <v>0.47947800000000002</v>
+      </c>
+    </row>
+    <row r="33" spans="14:21" x14ac:dyDescent="0.3">
+      <c r="N33" t="s">
+        <v>15</v>
+      </c>
+      <c r="O33">
+        <v>20</v>
+      </c>
+      <c r="Q33">
+        <v>1795.19146</v>
+      </c>
+      <c r="R33" s="6">
+        <v>4.8106590000000001E-10</v>
+      </c>
+      <c r="S33" s="6">
+        <v>1.5764049999999999E-10</v>
+      </c>
+      <c r="T33" s="37" t="s">
+        <v>19</v>
+      </c>
+      <c r="U33" s="36"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{086DCCED-70F6-45A9-8496-98A0FEEDF10E}">
   <dimension ref="C1:U33"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1943,7 +4303,7 @@
     </row>
     <row r="2" spans="3:21" x14ac:dyDescent="0.3">
       <c r="C2" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M2" t="s">
         <v>2</v>
@@ -1958,7 +4318,7 @@
         <v>5</v>
       </c>
       <c r="Q2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R2" t="s">
         <v>2</v>
@@ -1966,7 +4326,7 @@
     </row>
     <row r="3" spans="3:21" x14ac:dyDescent="0.3">
       <c r="C3" s="2" t="s">
-        <v>1</v>
+        <v>42</v>
       </c>
       <c r="P3" t="s">
         <v>6</v>
@@ -1984,7 +4344,7 @@
         <v>10</v>
       </c>
       <c r="U3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4" spans="3:21" x14ac:dyDescent="0.3">
@@ -1994,20 +4354,20 @@
       <c r="I4" s="8"/>
       <c r="J4" s="9"/>
       <c r="M4" t="s">
+        <v>11</v>
+      </c>
+      <c r="N4" t="s">
         <v>12</v>
       </c>
-      <c r="N4" t="s">
+      <c r="O4" t="s">
         <v>13</v>
-      </c>
-      <c r="O4" t="s">
-        <v>14</v>
       </c>
       <c r="T4" s="6"/>
     </row>
     <row r="5" spans="3:21" x14ac:dyDescent="0.3">
       <c r="C5" s="7"/>
       <c r="E5" s="10" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>9</v>
@@ -2019,14 +4379,14 @@
         <v>8</v>
       </c>
       <c r="I5" s="11" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J5" s="13"/>
       <c r="M5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="N5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O5">
         <v>10</v>
@@ -2052,24 +4412,24 @@
     </row>
     <row r="6" spans="3:21" x14ac:dyDescent="0.3">
       <c r="C6" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6" s="15" t="s">
         <v>12</v>
-      </c>
-      <c r="D6" s="15" t="s">
-        <v>13</v>
       </c>
       <c r="E6" s="16"/>
       <c r="F6" s="17"/>
       <c r="G6" s="18" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H6" s="17"/>
       <c r="I6" s="18"/>
       <c r="J6" s="19"/>
       <c r="M6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="N6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O6">
         <v>3</v>
@@ -2095,10 +4455,10 @@
     </row>
     <row r="7" spans="3:21" x14ac:dyDescent="0.3">
       <c r="C7" s="46" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D7" s="47" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E7" s="46">
         <v>13</v>
@@ -2117,10 +4477,10 @@
       </c>
       <c r="J7" s="23"/>
       <c r="M7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O7">
         <v>5</v>
@@ -2147,7 +4507,7 @@
     <row r="8" spans="3:21" x14ac:dyDescent="0.3">
       <c r="C8" s="51"/>
       <c r="D8" s="52" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E8" s="51">
         <v>13</v>
@@ -2160,10 +4520,10 @@
       <c r="I8" s="53"/>
       <c r="J8" s="25"/>
       <c r="M8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="N8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O8">
         <v>6</v>
@@ -2189,10 +4549,10 @@
     </row>
     <row r="9" spans="3:21" x14ac:dyDescent="0.3">
       <c r="C9" s="46" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D9" s="47" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E9" s="46">
         <v>2</v>
@@ -2211,10 +4571,10 @@
       </c>
       <c r="J9" s="23"/>
       <c r="M9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="N9" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O9">
         <v>9</v>
@@ -2241,7 +4601,7 @@
     <row r="10" spans="3:21" x14ac:dyDescent="0.3">
       <c r="C10" s="51"/>
       <c r="D10" s="52" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E10" s="51">
         <v>2</v>
@@ -2254,10 +4614,10 @@
       <c r="I10" s="53"/>
       <c r="J10" s="25"/>
       <c r="M10" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O10">
         <v>15</v>
@@ -2283,10 +4643,10 @@
     </row>
     <row r="11" spans="3:21" x14ac:dyDescent="0.3">
       <c r="C11" s="46" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D11" s="47" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E11" s="46">
         <v>5</v>
@@ -2305,10 +4665,10 @@
       </c>
       <c r="J11" s="23"/>
       <c r="M11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="N11" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O11">
         <v>7</v>
@@ -2335,7 +4695,7 @@
     <row r="12" spans="3:21" x14ac:dyDescent="0.3">
       <c r="C12" s="51"/>
       <c r="D12" s="52" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E12" s="51">
         <v>5</v>
@@ -2348,10 +4708,10 @@
       <c r="I12" s="53"/>
       <c r="J12" s="25"/>
       <c r="M12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="N12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O12">
         <v>22</v>
@@ -2377,10 +4737,10 @@
     </row>
     <row r="13" spans="3:21" x14ac:dyDescent="0.3">
       <c r="C13" s="46" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D13" s="47" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E13" s="46">
         <v>7</v>
@@ -2399,10 +4759,10 @@
       </c>
       <c r="J13" s="23"/>
       <c r="M13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="N13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O13">
         <v>9</v>
@@ -2429,7 +4789,7 @@
     <row r="14" spans="3:21" x14ac:dyDescent="0.3">
       <c r="C14" s="51"/>
       <c r="D14" s="52" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E14" s="51">
         <v>7</v>
@@ -2442,10 +4802,10 @@
       <c r="I14" s="53"/>
       <c r="J14" s="25"/>
       <c r="M14" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="N14" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O14">
         <v>2</v>
@@ -2471,10 +4831,10 @@
     </row>
     <row r="15" spans="3:21" x14ac:dyDescent="0.3">
       <c r="C15" s="46" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D15" s="47" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E15" s="46">
         <v>10</v>
@@ -2498,7 +4858,7 @@
     <row r="16" spans="3:21" x14ac:dyDescent="0.3">
       <c r="C16" s="51"/>
       <c r="D16" s="52" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E16" s="51">
         <v>10</v>
@@ -2514,7 +4874,7 @@
         <v>2</v>
       </c>
       <c r="N16" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="O16" s="6" t="s">
         <v>4</v>
@@ -2523,7 +4883,7 @@
         <v>5</v>
       </c>
       <c r="Q16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R16" t="s">
         <v>2</v>
@@ -2531,10 +4891,10 @@
     </row>
     <row r="17" spans="3:21" x14ac:dyDescent="0.3">
       <c r="C17" s="46" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D17" s="47" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E17" s="46">
         <v>5</v>
@@ -2562,13 +4922,13 @@
         <v>8</v>
       </c>
       <c r="U17" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="18" spans="3:21" x14ac:dyDescent="0.3">
       <c r="C18" s="51"/>
       <c r="D18" s="52" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E18" s="51">
         <v>5</v>
@@ -2581,21 +4941,21 @@
       <c r="I18" s="53"/>
       <c r="J18" s="25"/>
       <c r="M18" t="s">
+        <v>11</v>
+      </c>
+      <c r="N18" t="s">
         <v>12</v>
       </c>
-      <c r="N18" t="s">
+      <c r="O18" t="s">
         <v>13</v>
-      </c>
-      <c r="O18" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="19" spans="3:21" x14ac:dyDescent="0.3">
       <c r="C19" s="46" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D19" s="47" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E19" s="46">
         <v>4</v>
@@ -2614,10 +4974,10 @@
       </c>
       <c r="J19" s="23"/>
       <c r="M19" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="N19" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O19">
         <v>10</v>
@@ -2638,7 +4998,7 @@
     <row r="20" spans="3:21" x14ac:dyDescent="0.3">
       <c r="C20" s="51"/>
       <c r="D20" s="52" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E20" s="51">
         <v>4</v>
@@ -2651,10 +5011,10 @@
       <c r="I20" s="53"/>
       <c r="J20" s="25"/>
       <c r="M20" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="N20" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O20">
         <v>3</v>
@@ -2674,10 +5034,10 @@
     </row>
     <row r="21" spans="3:21" x14ac:dyDescent="0.3">
       <c r="C21" s="46" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D21" s="47" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E21" s="46">
         <v>2</v>
@@ -2695,13 +5055,13 @@
         <v>6.07</v>
       </c>
       <c r="J21" s="58" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="M21" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N21" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O21">
         <v>5</v>
@@ -2722,7 +5082,7 @@
     <row r="22" spans="3:21" x14ac:dyDescent="0.3">
       <c r="C22" s="51"/>
       <c r="D22" s="52" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E22" s="51">
         <v>2</v>
@@ -2735,10 +5095,10 @@
       <c r="I22" s="53"/>
       <c r="J22" s="25"/>
       <c r="M22" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="N22" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O22">
         <v>6</v>
@@ -2758,10 +5118,10 @@
     </row>
     <row r="23" spans="3:21" x14ac:dyDescent="0.3">
       <c r="C23" s="46" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D23" s="47" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E23" s="46">
         <v>10</v>
@@ -2780,10 +5140,10 @@
       </c>
       <c r="J23" s="23"/>
       <c r="M23" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="N23" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O23">
         <v>9</v>
@@ -2804,7 +5164,7 @@
     <row r="24" spans="3:21" x14ac:dyDescent="0.3">
       <c r="C24" s="51"/>
       <c r="D24" s="52" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E24" s="51">
         <v>10</v>
@@ -2817,10 +5177,10 @@
       <c r="I24" s="53"/>
       <c r="J24" s="25"/>
       <c r="M24" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N24" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O24">
         <v>15</v>
@@ -2840,10 +5200,10 @@
     </row>
     <row r="25" spans="3:21" x14ac:dyDescent="0.3">
       <c r="C25" s="46" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D25" s="47" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E25" s="46">
         <v>2</v>
@@ -2862,10 +5222,10 @@
       </c>
       <c r="J25" s="23"/>
       <c r="M25" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="N25" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O25">
         <v>7</v>
@@ -2886,7 +5246,7 @@
     <row r="26" spans="3:21" x14ac:dyDescent="0.3">
       <c r="C26" s="51"/>
       <c r="D26" s="52" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E26" s="51">
         <v>2</v>
@@ -2899,10 +5259,10 @@
       <c r="I26" s="53"/>
       <c r="J26" s="25"/>
       <c r="M26" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="N26" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O26">
         <v>22</v>
@@ -2922,10 +5282,10 @@
     </row>
     <row r="27" spans="3:21" x14ac:dyDescent="0.3">
       <c r="M27" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="N27" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O27">
         <v>9</v>
@@ -2945,10 +5305,10 @@
     </row>
     <row r="28" spans="3:21" x14ac:dyDescent="0.3">
       <c r="M28" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="N28" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O28">
         <v>2</v>
@@ -2981,7 +5341,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55D91BD8-0048-428B-8029-9C24A623F1BA}">
   <dimension ref="C1:U33"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -3005,7 +5365,7 @@
     </row>
     <row r="2" spans="3:21" x14ac:dyDescent="0.3">
       <c r="C2" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="M2" t="s">
         <v>2</v>
@@ -3020,10 +5380,10 @@
         <v>5</v>
       </c>
       <c r="Q2" t="s">
+        <v>37</v>
+      </c>
+      <c r="R2" t="s">
         <v>38</v>
-      </c>
-      <c r="R2" t="s">
-        <v>39</v>
       </c>
       <c r="S2" t="s">
         <v>2</v>
@@ -3031,7 +5391,7 @@
     </row>
     <row r="3" spans="3:21" x14ac:dyDescent="0.3">
       <c r="C3" s="2" t="s">
-        <v>1</v>
+        <v>42</v>
       </c>
       <c r="P3" t="s">
         <v>6</v>
@@ -3049,7 +5409,7 @@
         <v>10</v>
       </c>
       <c r="U3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4" spans="3:21" x14ac:dyDescent="0.3">
@@ -3059,20 +5419,20 @@
       <c r="I4" s="8"/>
       <c r="J4" s="9"/>
       <c r="M4" t="s">
+        <v>11</v>
+      </c>
+      <c r="N4" t="s">
         <v>12</v>
       </c>
-      <c r="N4" t="s">
+      <c r="O4" t="s">
         <v>13</v>
-      </c>
-      <c r="O4" t="s">
-        <v>14</v>
       </c>
       <c r="T4" s="6"/>
     </row>
     <row r="5" spans="3:21" x14ac:dyDescent="0.3">
       <c r="C5" s="7"/>
       <c r="E5" s="10" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>9</v>
@@ -3084,14 +5444,14 @@
         <v>8</v>
       </c>
       <c r="I5" s="11" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J5" s="13"/>
       <c r="M5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="N5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O5">
         <v>10</v>
@@ -3117,24 +5477,24 @@
     </row>
     <row r="6" spans="3:21" x14ac:dyDescent="0.3">
       <c r="C6" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6" s="15" t="s">
         <v>12</v>
-      </c>
-      <c r="D6" s="15" t="s">
-        <v>13</v>
       </c>
       <c r="E6" s="16"/>
       <c r="F6" s="17"/>
       <c r="G6" s="18" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H6" s="17"/>
       <c r="I6" s="18"/>
       <c r="J6" s="19"/>
       <c r="M6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="N6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O6">
         <v>3</v>
@@ -3160,10 +5520,10 @@
     </row>
     <row r="7" spans="3:21" x14ac:dyDescent="0.3">
       <c r="C7" s="46" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D7" s="47" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E7" s="46">
         <v>13</v>
@@ -3182,10 +5542,10 @@
       </c>
       <c r="J7" s="23"/>
       <c r="M7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O7">
         <v>5</v>
@@ -3212,7 +5572,7 @@
     <row r="8" spans="3:21" x14ac:dyDescent="0.3">
       <c r="C8" s="51"/>
       <c r="D8" s="52" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E8" s="51">
         <v>13</v>
@@ -3225,10 +5585,10 @@
       <c r="I8" s="53"/>
       <c r="J8" s="25"/>
       <c r="M8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="N8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O8">
         <v>6</v>
@@ -3254,10 +5614,10 @@
     </row>
     <row r="9" spans="3:21" x14ac:dyDescent="0.3">
       <c r="C9" s="46" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D9" s="47" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E9" s="46">
         <v>2</v>
@@ -3276,10 +5636,10 @@
       </c>
       <c r="J9" s="23"/>
       <c r="M9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="N9" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O9">
         <v>9</v>
@@ -3306,7 +5666,7 @@
     <row r="10" spans="3:21" x14ac:dyDescent="0.3">
       <c r="C10" s="51"/>
       <c r="D10" s="52" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E10" s="51">
         <v>2</v>
@@ -3319,10 +5679,10 @@
       <c r="I10" s="53"/>
       <c r="J10" s="25"/>
       <c r="M10" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O10">
         <v>15</v>
@@ -3348,10 +5708,10 @@
     </row>
     <row r="11" spans="3:21" x14ac:dyDescent="0.3">
       <c r="C11" s="46" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D11" s="47" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E11" s="46">
         <v>5</v>
@@ -3370,10 +5730,10 @@
       </c>
       <c r="J11" s="23"/>
       <c r="M11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="N11" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O11">
         <v>7</v>
@@ -3400,7 +5760,7 @@
     <row r="12" spans="3:21" x14ac:dyDescent="0.3">
       <c r="C12" s="51"/>
       <c r="D12" s="52" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E12" s="51">
         <v>5</v>
@@ -3413,10 +5773,10 @@
       <c r="I12" s="53"/>
       <c r="J12" s="25"/>
       <c r="M12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="N12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O12">
         <v>22</v>
@@ -3442,10 +5802,10 @@
     </row>
     <row r="13" spans="3:21" x14ac:dyDescent="0.3">
       <c r="C13" s="46" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D13" s="47" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E13" s="46">
         <v>7</v>
@@ -3464,10 +5824,10 @@
       </c>
       <c r="J13" s="23"/>
       <c r="M13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="N13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O13">
         <v>9</v>
@@ -3494,7 +5854,7 @@
     <row r="14" spans="3:21" x14ac:dyDescent="0.3">
       <c r="C14" s="51"/>
       <c r="D14" s="52" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E14" s="51">
         <v>7</v>
@@ -3507,10 +5867,10 @@
       <c r="I14" s="53"/>
       <c r="J14" s="25"/>
       <c r="M14" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="N14" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O14">
         <v>2</v>
@@ -3536,10 +5896,10 @@
     </row>
     <row r="15" spans="3:21" x14ac:dyDescent="0.3">
       <c r="C15" s="46" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D15" s="47" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E15" s="46">
         <v>10</v>
@@ -3551,7 +5911,7 @@
         <v>2606.6076699999999</v>
       </c>
       <c r="H15" s="49">
-        <v>1.437852E-9</v>
+        <v>8.7000000000000001E-5</v>
       </c>
       <c r="I15" s="50">
         <v>1.25499E-4</v>
@@ -3561,7 +5921,7 @@
     <row r="16" spans="3:21" x14ac:dyDescent="0.3">
       <c r="C16" s="51"/>
       <c r="D16" s="52" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E16" s="51">
         <v>10</v>
@@ -3577,7 +5937,7 @@
         <v>2</v>
       </c>
       <c r="N16" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="O16" t="s">
         <v>4</v>
@@ -3586,10 +5946,10 @@
         <v>5</v>
       </c>
       <c r="Q16" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="R16" t="s">
         <v>38</v>
-      </c>
-      <c r="R16" t="s">
-        <v>39</v>
       </c>
       <c r="S16" t="s">
         <v>2</v>
@@ -3597,10 +5957,10 @@
     </row>
     <row r="17" spans="3:21" x14ac:dyDescent="0.3">
       <c r="C17" s="46" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D17" s="47" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E17" s="46">
         <v>5</v>
@@ -3622,13 +5982,13 @@
         <v>8</v>
       </c>
       <c r="Q17" s="6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="18" spans="3:21" x14ac:dyDescent="0.3">
       <c r="C18" s="51"/>
       <c r="D18" s="52" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E18" s="51">
         <v>5</v>
@@ -3641,21 +6001,21 @@
       <c r="I18" s="53"/>
       <c r="J18" s="25"/>
       <c r="M18" t="s">
+        <v>11</v>
+      </c>
+      <c r="N18" t="s">
         <v>12</v>
       </c>
-      <c r="N18" t="s">
+      <c r="O18" t="s">
         <v>13</v>
-      </c>
-      <c r="O18" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="19" spans="3:21" x14ac:dyDescent="0.3">
       <c r="C19" s="46" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D19" s="47" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E19" s="46">
         <v>4</v>
@@ -3664,20 +6024,20 @@
         <v>500</v>
       </c>
       <c r="G19" s="48">
-        <v>5980.545795</v>
-      </c>
-      <c r="H19" s="56">
-        <v>6.2415400000000003E-2</v>
+        <v>3898</v>
+      </c>
+      <c r="H19" s="49">
+        <v>2.051E-7</v>
       </c>
       <c r="I19" s="50">
         <v>1.464305E-5</v>
       </c>
       <c r="J19" s="23"/>
       <c r="M19" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="N19" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O19">
         <v>10</v>
@@ -3693,7 +6053,7 @@
     <row r="20" spans="3:21" x14ac:dyDescent="0.3">
       <c r="C20" s="51"/>
       <c r="D20" s="52" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E20" s="51">
         <v>4</v>
@@ -3706,10 +6066,10 @@
       <c r="I20" s="53"/>
       <c r="J20" s="25"/>
       <c r="M20" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="N20" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O20">
         <v>3</v>
@@ -3725,10 +6085,10 @@
     </row>
     <row r="21" spans="3:21" x14ac:dyDescent="0.3">
       <c r="C21" s="46" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D21" s="47" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E21" s="46">
         <v>2</v>
@@ -3746,13 +6106,13 @@
         <v>6.1523750000000001</v>
       </c>
       <c r="J21" s="58" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="M21" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N21" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O21">
         <v>5</v>
@@ -3769,7 +6129,7 @@
     <row r="22" spans="3:21" x14ac:dyDescent="0.3">
       <c r="C22" s="51"/>
       <c r="D22" s="52" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E22" s="51">
         <v>2</v>
@@ -3782,10 +6142,10 @@
       <c r="I22" s="53"/>
       <c r="J22" s="25"/>
       <c r="M22" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="N22" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O22">
         <v>6</v>
@@ -3801,10 +6161,10 @@
     </row>
     <row r="23" spans="3:21" x14ac:dyDescent="0.3">
       <c r="C23" s="46" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D23" s="47" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E23" s="46">
         <v>10</v>
@@ -3815,18 +6175,18 @@
       <c r="G23" s="48">
         <v>4381.5028949999996</v>
       </c>
-      <c r="H23" s="49">
+      <c r="H23" s="56">
         <v>2.5072789999999998E-3</v>
       </c>
-      <c r="I23" s="50">
+      <c r="I23" s="55">
         <v>2.471897E-2</v>
       </c>
       <c r="J23" s="23"/>
       <c r="M23" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="N23" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O23">
         <v>9</v>
@@ -3843,7 +6203,7 @@
     <row r="24" spans="3:21" x14ac:dyDescent="0.3">
       <c r="C24" s="51"/>
       <c r="D24" s="52" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E24" s="51">
         <v>10</v>
@@ -3856,10 +6216,10 @@
       <c r="I24" s="53"/>
       <c r="J24" s="25"/>
       <c r="M24" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N24" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O24">
         <v>15</v>
@@ -3875,10 +6235,10 @@
     </row>
     <row r="25" spans="3:21" x14ac:dyDescent="0.3">
       <c r="C25" s="46" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D25" s="47" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E25" s="46">
         <v>2</v>
@@ -3897,10 +6257,10 @@
       </c>
       <c r="J25" s="23"/>
       <c r="M25" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="N25" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O25">
         <v>7</v>
@@ -3917,7 +6277,7 @@
     <row r="26" spans="3:21" x14ac:dyDescent="0.3">
       <c r="C26" s="51"/>
       <c r="D26" s="52" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E26" s="51">
         <v>2</v>
@@ -3930,10 +6290,10 @@
       <c r="I26" s="53"/>
       <c r="J26" s="25"/>
       <c r="M26" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="N26" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O26">
         <v>22</v>
@@ -3949,10 +6309,10 @@
     </row>
     <row r="27" spans="3:21" x14ac:dyDescent="0.3">
       <c r="M27" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="N27" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O27">
         <v>9</v>
@@ -3968,10 +6328,10 @@
     </row>
     <row r="28" spans="3:21" x14ac:dyDescent="0.3">
       <c r="M28" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="N28" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O28">
         <v>2</v>
@@ -3987,7 +6347,1029 @@
     </row>
     <row r="29" spans="3:21" x14ac:dyDescent="0.3">
       <c r="C29" t="s">
+        <v>40</v>
+      </c>
+      <c r="R29" s="6"/>
+    </row>
+    <row r="30" spans="3:21" x14ac:dyDescent="0.3">
+      <c r="R30" s="6"/>
+    </row>
+    <row r="33" spans="18:18" x14ac:dyDescent="0.3">
+      <c r="R33" s="6"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F1827695-A9C0-4BE6-AEFB-B5C1FCB8A6CD}">
+  <dimension ref="C1:U33"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="3" max="3" width="9.6640625" customWidth="1"/>
+    <col min="4" max="4" width="8.88671875" customWidth="1"/>
+    <col min="5" max="5" width="4.77734375" customWidth="1"/>
+    <col min="6" max="6" width="6.88671875" customWidth="1"/>
+    <col min="7" max="7" width="8.77734375" customWidth="1"/>
+    <col min="9" max="9" width="9" customWidth="1"/>
+    <col min="11" max="11" width="18.5546875" customWidth="1"/>
+    <col min="12" max="12" width="3" customWidth="1"/>
+    <col min="19" max="19" width="7.5546875" customWidth="1"/>
+    <col min="20" max="20" width="8" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="3:21" ht="23.4" x14ac:dyDescent="0.45">
+      <c r="C1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="3:21" x14ac:dyDescent="0.3">
+      <c r="C2" s="2" t="s">
         <v>41</v>
+      </c>
+      <c r="M2" t="s">
+        <v>2</v>
+      </c>
+      <c r="N2" t="s">
+        <v>3</v>
+      </c>
+      <c r="O2" t="s">
+        <v>4</v>
+      </c>
+      <c r="P2" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>37</v>
+      </c>
+      <c r="R2" t="s">
+        <v>38</v>
+      </c>
+      <c r="S2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="3:21" x14ac:dyDescent="0.3">
+      <c r="C3" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="P3" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>7</v>
+      </c>
+      <c r="R3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S3" t="s">
+        <v>9</v>
+      </c>
+      <c r="T3" t="s">
+        <v>10</v>
+      </c>
+      <c r="U3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="4" spans="3:21" x14ac:dyDescent="0.3">
+      <c r="C4" s="7"/>
+      <c r="G4" s="44"/>
+      <c r="H4" s="45"/>
+      <c r="I4" s="44"/>
+      <c r="J4" s="45"/>
+      <c r="M4" t="s">
+        <v>11</v>
+      </c>
+      <c r="N4" t="s">
+        <v>12</v>
+      </c>
+      <c r="O4" t="s">
+        <v>13</v>
+      </c>
+      <c r="T4" s="6"/>
+    </row>
+    <row r="5" spans="3:21" x14ac:dyDescent="0.3">
+      <c r="C5" s="7"/>
+      <c r="E5" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="H5" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="I5" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="J5" s="13"/>
+      <c r="M5" t="s">
+        <v>23</v>
+      </c>
+      <c r="N5" t="s">
+        <v>15</v>
+      </c>
+      <c r="O5">
+        <v>10</v>
+      </c>
+      <c r="P5">
+        <v>58.5</v>
+      </c>
+      <c r="Q5" s="6">
+        <v>5386.3504000000003</v>
+      </c>
+      <c r="R5" s="6">
+        <v>1.124565E-8</v>
+      </c>
+      <c r="S5">
+        <v>500</v>
+      </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
+      <c r="U5" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="3:21" x14ac:dyDescent="0.3">
+      <c r="C6" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" s="16"/>
+      <c r="F6" s="17"/>
+      <c r="G6" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="H6" s="17"/>
+      <c r="I6" s="18"/>
+      <c r="J6" s="19"/>
+      <c r="M6" t="s">
+        <v>24</v>
+      </c>
+      <c r="N6" t="s">
+        <v>15</v>
+      </c>
+      <c r="O6">
+        <v>3</v>
+      </c>
+      <c r="P6">
+        <v>58.5</v>
+      </c>
+      <c r="Q6" s="6">
+        <v>2024.4151300000001</v>
+      </c>
+      <c r="R6" s="6">
+        <v>9.5042200000000006E-11</v>
+      </c>
+      <c r="S6">
+        <v>500</v>
+      </c>
+      <c r="T6">
+        <v>0</v>
+      </c>
+      <c r="U6" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="3:21" x14ac:dyDescent="0.3">
+      <c r="C7" s="46" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7" s="47" t="s">
+        <v>15</v>
+      </c>
+      <c r="E7" s="46">
+        <v>13</v>
+      </c>
+      <c r="F7" s="47">
+        <v>500</v>
+      </c>
+      <c r="G7" s="48">
+        <v>5386.3504000000003</v>
+      </c>
+      <c r="H7" s="49">
+        <v>1.124565E-8</v>
+      </c>
+      <c r="I7" s="50">
+        <v>1.9351190000000002E-12</v>
+      </c>
+      <c r="J7" s="23"/>
+      <c r="M7" t="s">
+        <v>25</v>
+      </c>
+      <c r="N7" t="s">
+        <v>15</v>
+      </c>
+      <c r="O7">
+        <v>5</v>
+      </c>
+      <c r="P7">
+        <v>58.5</v>
+      </c>
+      <c r="Q7" s="6">
+        <v>4019.3682699999999</v>
+      </c>
+      <c r="R7" s="6">
+        <v>-1.308386E-9</v>
+      </c>
+      <c r="S7">
+        <v>500</v>
+      </c>
+      <c r="T7">
+        <v>0</v>
+      </c>
+      <c r="U7" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="3:21" x14ac:dyDescent="0.3">
+      <c r="C8" s="51"/>
+      <c r="D8" s="52" t="s">
+        <v>17</v>
+      </c>
+      <c r="E8" s="51">
+        <v>13</v>
+      </c>
+      <c r="F8" s="52">
+        <v>500</v>
+      </c>
+      <c r="G8" s="53"/>
+      <c r="H8" s="54"/>
+      <c r="I8" s="53"/>
+      <c r="J8" s="25"/>
+      <c r="M8" t="s">
+        <v>26</v>
+      </c>
+      <c r="N8" t="s">
+        <v>15</v>
+      </c>
+      <c r="O8">
+        <v>6</v>
+      </c>
+      <c r="P8">
+        <v>58.5</v>
+      </c>
+      <c r="Q8">
+        <v>3534.5307499999999</v>
+      </c>
+      <c r="R8" s="6">
+        <v>4.259731E-5</v>
+      </c>
+      <c r="S8">
+        <v>500</v>
+      </c>
+      <c r="T8">
+        <v>0</v>
+      </c>
+      <c r="U8" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="3:21" x14ac:dyDescent="0.3">
+      <c r="C9" s="46" t="s">
+        <v>24</v>
+      </c>
+      <c r="D9" s="47" t="s">
+        <v>15</v>
+      </c>
+      <c r="E9" s="46">
+        <v>2</v>
+      </c>
+      <c r="F9" s="47">
+        <v>500</v>
+      </c>
+      <c r="G9" s="48">
+        <v>2024.4151300000001</v>
+      </c>
+      <c r="H9" s="49">
+        <v>9.5042200000000006E-11</v>
+      </c>
+      <c r="I9" s="50">
+        <v>2.4119299999999998E-12</v>
+      </c>
+      <c r="J9" s="23"/>
+      <c r="M9" t="s">
+        <v>27</v>
+      </c>
+      <c r="N9" t="s">
+        <v>15</v>
+      </c>
+      <c r="O9">
+        <v>9</v>
+      </c>
+      <c r="P9">
+        <v>58.5</v>
+      </c>
+      <c r="Q9" s="6">
+        <v>2653.58086</v>
+      </c>
+      <c r="R9" s="6">
+        <v>-8.6601069999999998E-5</v>
+      </c>
+      <c r="S9">
+        <v>500</v>
+      </c>
+      <c r="T9">
+        <v>0</v>
+      </c>
+      <c r="U9" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="3:21" x14ac:dyDescent="0.3">
+      <c r="C10" s="51"/>
+      <c r="D10" s="52" t="s">
+        <v>17</v>
+      </c>
+      <c r="E10" s="51">
+        <v>2</v>
+      </c>
+      <c r="F10" s="52">
+        <v>500</v>
+      </c>
+      <c r="G10" s="53"/>
+      <c r="H10" s="54"/>
+      <c r="I10" s="53"/>
+      <c r="J10" s="25"/>
+      <c r="M10" t="s">
+        <v>28</v>
+      </c>
+      <c r="N10" t="s">
+        <v>15</v>
+      </c>
+      <c r="O10">
+        <v>15</v>
+      </c>
+      <c r="P10">
+        <v>58.5</v>
+      </c>
+      <c r="Q10">
+        <v>13935.77074</v>
+      </c>
+      <c r="R10" s="6">
+        <v>-1.012523E-10</v>
+      </c>
+      <c r="S10">
+        <v>500</v>
+      </c>
+      <c r="T10">
+        <v>0</v>
+      </c>
+      <c r="U10" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="3:21" x14ac:dyDescent="0.3">
+      <c r="C11" s="46" t="s">
+        <v>25</v>
+      </c>
+      <c r="D11" s="47" t="s">
+        <v>15</v>
+      </c>
+      <c r="E11" s="46">
+        <v>5</v>
+      </c>
+      <c r="F11" s="47">
+        <v>500</v>
+      </c>
+      <c r="G11" s="48">
+        <v>4019.3682699999999</v>
+      </c>
+      <c r="H11" s="49">
+        <v>-1.308386E-9</v>
+      </c>
+      <c r="I11" s="50">
+        <v>1.7227079999999998E-8</v>
+      </c>
+      <c r="J11" s="23"/>
+      <c r="M11" t="s">
+        <v>29</v>
+      </c>
+      <c r="N11" t="s">
+        <v>15</v>
+      </c>
+      <c r="O11">
+        <v>7</v>
+      </c>
+      <c r="P11">
+        <v>58.5</v>
+      </c>
+      <c r="Q11" s="6">
+        <v>3771.9048699999998</v>
+      </c>
+      <c r="R11" s="6">
+        <v>7.5076919999999995E-7</v>
+      </c>
+      <c r="S11">
+        <v>500</v>
+      </c>
+      <c r="T11">
+        <v>0</v>
+      </c>
+      <c r="U11" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="3:21" x14ac:dyDescent="0.3">
+      <c r="C12" s="51"/>
+      <c r="D12" s="52" t="s">
+        <v>17</v>
+      </c>
+      <c r="E12" s="51">
+        <v>5</v>
+      </c>
+      <c r="F12" s="52">
+        <v>500</v>
+      </c>
+      <c r="G12" s="53"/>
+      <c r="H12" s="54"/>
+      <c r="I12" s="53"/>
+      <c r="J12" s="25"/>
+      <c r="M12" t="s">
+        <v>30</v>
+      </c>
+      <c r="N12" t="s">
+        <v>15</v>
+      </c>
+      <c r="O12">
+        <v>22</v>
+      </c>
+      <c r="P12">
+        <v>58.5</v>
+      </c>
+      <c r="Q12" s="6">
+        <v>12808.41705</v>
+      </c>
+      <c r="R12" s="6">
+        <v>21.488810000000001</v>
+      </c>
+      <c r="S12">
+        <v>500</v>
+      </c>
+      <c r="T12">
+        <v>0</v>
+      </c>
+      <c r="U12" s="57">
+        <v>3.5510479999999998E-9</v>
+      </c>
+    </row>
+    <row r="13" spans="3:21" x14ac:dyDescent="0.3">
+      <c r="C13" s="46" t="s">
+        <v>26</v>
+      </c>
+      <c r="D13" s="47" t="s">
+        <v>15</v>
+      </c>
+      <c r="E13" s="46">
+        <v>7</v>
+      </c>
+      <c r="F13" s="47">
+        <v>500</v>
+      </c>
+      <c r="G13" s="48">
+        <v>3534.5307499999999</v>
+      </c>
+      <c r="H13" s="49">
+        <v>4.259731E-5</v>
+      </c>
+      <c r="I13" s="50">
+        <v>4.4385239999999999E-5</v>
+      </c>
+      <c r="J13" s="23"/>
+      <c r="M13" t="s">
+        <v>31</v>
+      </c>
+      <c r="N13" t="s">
+        <v>15</v>
+      </c>
+      <c r="O13">
+        <v>9</v>
+      </c>
+      <c r="P13">
+        <v>58.5</v>
+      </c>
+      <c r="Q13" s="6">
+        <v>3784.6693700000001</v>
+      </c>
+      <c r="R13" s="6">
+        <v>6.0208199999999997E-6</v>
+      </c>
+      <c r="S13">
+        <v>500</v>
+      </c>
+      <c r="T13">
+        <v>0</v>
+      </c>
+      <c r="U13" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="3:21" x14ac:dyDescent="0.3">
+      <c r="C14" s="51"/>
+      <c r="D14" s="52" t="s">
+        <v>17</v>
+      </c>
+      <c r="E14" s="51">
+        <v>7</v>
+      </c>
+      <c r="F14" s="52">
+        <v>500</v>
+      </c>
+      <c r="G14" s="53"/>
+      <c r="H14" s="54"/>
+      <c r="I14" s="53"/>
+      <c r="J14" s="25"/>
+      <c r="M14" t="s">
+        <v>32</v>
+      </c>
+      <c r="N14" t="s">
+        <v>15</v>
+      </c>
+      <c r="O14">
+        <v>2</v>
+      </c>
+      <c r="P14">
+        <v>58.5</v>
+      </c>
+      <c r="Q14" s="6">
+        <v>702.35568499999999</v>
+      </c>
+      <c r="R14" s="6">
+        <v>2.2727720000000002E-3</v>
+      </c>
+      <c r="S14">
+        <v>500</v>
+      </c>
+      <c r="T14">
+        <v>0</v>
+      </c>
+      <c r="U14" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="3:21" x14ac:dyDescent="0.3">
+      <c r="C15" s="46" t="s">
+        <v>27</v>
+      </c>
+      <c r="D15" s="47" t="s">
+        <v>15</v>
+      </c>
+      <c r="E15" s="46">
+        <v>10</v>
+      </c>
+      <c r="F15" s="47">
+        <v>500</v>
+      </c>
+      <c r="G15" s="61">
+        <v>2612.3460500000001</v>
+      </c>
+      <c r="H15" s="62">
+        <v>-1.0324689999999999E-11</v>
+      </c>
+      <c r="I15" s="55">
+        <v>0.2206071</v>
+      </c>
+      <c r="J15" s="23"/>
+    </row>
+    <row r="16" spans="3:21" x14ac:dyDescent="0.3">
+      <c r="C16" s="51"/>
+      <c r="D16" s="52" t="s">
+        <v>17</v>
+      </c>
+      <c r="E16" s="51">
+        <v>10</v>
+      </c>
+      <c r="F16" s="52">
+        <v>500</v>
+      </c>
+      <c r="G16" s="53"/>
+      <c r="H16" s="54"/>
+      <c r="I16" s="53"/>
+      <c r="J16" s="25"/>
+      <c r="M16" t="s">
+        <v>2</v>
+      </c>
+      <c r="N16" t="s">
+        <v>20</v>
+      </c>
+      <c r="O16" t="s">
+        <v>4</v>
+      </c>
+      <c r="P16" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>37</v>
+      </c>
+      <c r="R16" t="s">
+        <v>38</v>
+      </c>
+      <c r="S16" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="3:21" x14ac:dyDescent="0.3">
+      <c r="C17" s="46" t="s">
+        <v>28</v>
+      </c>
+      <c r="D17" s="47" t="s">
+        <v>15</v>
+      </c>
+      <c r="E17" s="46">
+        <v>5</v>
+      </c>
+      <c r="F17" s="47">
+        <v>500</v>
+      </c>
+      <c r="G17" s="48">
+        <v>13935.77074</v>
+      </c>
+      <c r="H17" s="49">
+        <v>-1.012523E-10</v>
+      </c>
+      <c r="I17" s="50">
+        <v>9.5688479999999997E-8</v>
+      </c>
+      <c r="J17" s="23"/>
+      <c r="P17" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="18" spans="3:21" x14ac:dyDescent="0.3">
+      <c r="C18" s="51"/>
+      <c r="D18" s="52" t="s">
+        <v>17</v>
+      </c>
+      <c r="E18" s="51">
+        <v>5</v>
+      </c>
+      <c r="F18" s="52">
+        <v>500</v>
+      </c>
+      <c r="G18" s="53"/>
+      <c r="H18" s="54"/>
+      <c r="I18" s="53"/>
+      <c r="J18" s="25"/>
+      <c r="M18" t="s">
+        <v>11</v>
+      </c>
+      <c r="N18" t="s">
+        <v>12</v>
+      </c>
+      <c r="O18" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q18" s="6"/>
+    </row>
+    <row r="19" spans="3:21" x14ac:dyDescent="0.3">
+      <c r="C19" s="46" t="s">
+        <v>29</v>
+      </c>
+      <c r="D19" s="47" t="s">
+        <v>15</v>
+      </c>
+      <c r="E19" s="46">
+        <v>4</v>
+      </c>
+      <c r="F19" s="47">
+        <v>500</v>
+      </c>
+      <c r="G19" s="48">
+        <v>3771.9048699999998</v>
+      </c>
+      <c r="H19" s="49">
+        <v>7.5076919999999995E-7</v>
+      </c>
+      <c r="I19" s="50">
+        <v>1.7519529999999999E-5</v>
+      </c>
+      <c r="J19" s="23"/>
+      <c r="M19" t="s">
+        <v>23</v>
+      </c>
+      <c r="N19" t="s">
+        <v>15</v>
+      </c>
+      <c r="O19">
+        <v>10</v>
+      </c>
+      <c r="P19" s="6">
+        <v>1.9351190000000002E-12</v>
+      </c>
+      <c r="Q19">
+        <v>0</v>
+      </c>
+      <c r="U19" s="6"/>
+    </row>
+    <row r="20" spans="3:21" x14ac:dyDescent="0.3">
+      <c r="C20" s="51"/>
+      <c r="D20" s="52" t="s">
+        <v>17</v>
+      </c>
+      <c r="E20" s="51">
+        <v>4</v>
+      </c>
+      <c r="F20" s="52">
+        <v>500</v>
+      </c>
+      <c r="G20" s="53"/>
+      <c r="H20" s="54"/>
+      <c r="I20" s="53"/>
+      <c r="J20" s="25"/>
+      <c r="M20" t="s">
+        <v>24</v>
+      </c>
+      <c r="N20" t="s">
+        <v>15</v>
+      </c>
+      <c r="O20">
+        <v>3</v>
+      </c>
+      <c r="P20" s="6">
+        <v>2.4119299999999998E-12</v>
+      </c>
+      <c r="Q20">
+        <v>0</v>
+      </c>
+      <c r="U20" s="6"/>
+    </row>
+    <row r="21" spans="3:21" x14ac:dyDescent="0.3">
+      <c r="C21" s="46" t="s">
+        <v>30</v>
+      </c>
+      <c r="D21" s="47" t="s">
+        <v>15</v>
+      </c>
+      <c r="E21" s="46">
+        <v>2</v>
+      </c>
+      <c r="F21" s="47">
+        <v>500</v>
+      </c>
+      <c r="G21" s="48">
+        <v>12808.41705</v>
+      </c>
+      <c r="H21" s="56">
+        <v>21.488810000000001</v>
+      </c>
+      <c r="I21" s="55">
+        <v>135.69540000000001</v>
+      </c>
+      <c r="J21" s="58" t="s">
+        <v>35</v>
+      </c>
+      <c r="M21" t="s">
+        <v>25</v>
+      </c>
+      <c r="N21" t="s">
+        <v>15</v>
+      </c>
+      <c r="O21">
+        <v>5</v>
+      </c>
+      <c r="P21" s="6">
+        <v>1.7227079999999998E-8</v>
+      </c>
+      <c r="Q21">
+        <v>0</v>
+      </c>
+      <c r="R21" s="6"/>
+      <c r="U21" s="6"/>
+    </row>
+    <row r="22" spans="3:21" x14ac:dyDescent="0.3">
+      <c r="C22" s="51"/>
+      <c r="D22" s="52" t="s">
+        <v>17</v>
+      </c>
+      <c r="E22" s="51">
+        <v>2</v>
+      </c>
+      <c r="F22" s="52">
+        <v>500</v>
+      </c>
+      <c r="G22" s="53"/>
+      <c r="H22" s="54"/>
+      <c r="I22" s="53"/>
+      <c r="J22" s="25"/>
+      <c r="M22" t="s">
+        <v>26</v>
+      </c>
+      <c r="N22" t="s">
+        <v>15</v>
+      </c>
+      <c r="O22">
+        <v>6</v>
+      </c>
+      <c r="P22" s="6">
+        <v>4.4385239999999999E-5</v>
+      </c>
+      <c r="Q22">
+        <v>0</v>
+      </c>
+      <c r="R22" s="6"/>
+      <c r="U22" s="6"/>
+    </row>
+    <row r="23" spans="3:21" x14ac:dyDescent="0.3">
+      <c r="C23" s="46" t="s">
+        <v>31</v>
+      </c>
+      <c r="D23" s="47" t="s">
+        <v>15</v>
+      </c>
+      <c r="E23" s="46">
+        <v>10</v>
+      </c>
+      <c r="F23" s="47">
+        <v>500</v>
+      </c>
+      <c r="G23" s="48">
+        <v>3784.6693700000001</v>
+      </c>
+      <c r="H23" s="59">
+        <v>6.0208199999999997E-6</v>
+      </c>
+      <c r="I23" s="60">
+        <v>1.8979380000000001E-6</v>
+      </c>
+      <c r="J23" s="23"/>
+      <c r="M23" t="s">
+        <v>27</v>
+      </c>
+      <c r="N23" t="s">
+        <v>15</v>
+      </c>
+      <c r="O23">
+        <v>9</v>
+      </c>
+      <c r="P23" s="6">
+        <v>0.2206071</v>
+      </c>
+      <c r="Q23">
+        <v>0</v>
+      </c>
+      <c r="R23" s="6"/>
+      <c r="U23" s="6"/>
+    </row>
+    <row r="24" spans="3:21" x14ac:dyDescent="0.3">
+      <c r="C24" s="51"/>
+      <c r="D24" s="52" t="s">
+        <v>17</v>
+      </c>
+      <c r="E24" s="51">
+        <v>10</v>
+      </c>
+      <c r="F24" s="52">
+        <v>500</v>
+      </c>
+      <c r="G24" s="53"/>
+      <c r="H24" s="54"/>
+      <c r="I24" s="53"/>
+      <c r="J24" s="25"/>
+      <c r="M24" t="s">
+        <v>28</v>
+      </c>
+      <c r="N24" t="s">
+        <v>15</v>
+      </c>
+      <c r="O24">
+        <v>15</v>
+      </c>
+      <c r="P24" s="6">
+        <v>9.5840719999999995E-8</v>
+      </c>
+      <c r="Q24">
+        <v>0</v>
+      </c>
+      <c r="R24" s="6"/>
+      <c r="U24" s="6"/>
+    </row>
+    <row r="25" spans="3:21" x14ac:dyDescent="0.3">
+      <c r="C25" s="46" t="s">
+        <v>32</v>
+      </c>
+      <c r="D25" s="47" t="s">
+        <v>15</v>
+      </c>
+      <c r="E25" s="46">
+        <v>2</v>
+      </c>
+      <c r="F25" s="47">
+        <v>500</v>
+      </c>
+      <c r="G25" s="48">
+        <v>702.35568499999999</v>
+      </c>
+      <c r="H25" s="56">
+        <v>2.2727720000000002E-3</v>
+      </c>
+      <c r="I25" s="55">
+        <v>2.4827299999999998E-3</v>
+      </c>
+      <c r="J25" s="23"/>
+      <c r="M25" t="s">
+        <v>29</v>
+      </c>
+      <c r="N25" t="s">
+        <v>15</v>
+      </c>
+      <c r="O25">
+        <v>7</v>
+      </c>
+      <c r="P25" s="6">
+        <v>1.7519529999999999E-5</v>
+      </c>
+      <c r="Q25">
+        <v>0</v>
+      </c>
+      <c r="R25" s="6"/>
+      <c r="U25" s="6"/>
+    </row>
+    <row r="26" spans="3:21" x14ac:dyDescent="0.3">
+      <c r="C26" s="51"/>
+      <c r="D26" s="52" t="s">
+        <v>17</v>
+      </c>
+      <c r="E26" s="51">
+        <v>2</v>
+      </c>
+      <c r="F26" s="52">
+        <v>500</v>
+      </c>
+      <c r="G26" s="53"/>
+      <c r="H26" s="54"/>
+      <c r="I26" s="53"/>
+      <c r="J26" s="25"/>
+      <c r="M26" t="s">
+        <v>30</v>
+      </c>
+      <c r="N26" t="s">
+        <v>15</v>
+      </c>
+      <c r="O26">
+        <v>22</v>
+      </c>
+      <c r="P26" s="6">
+        <v>135.69540000000001</v>
+      </c>
+      <c r="Q26">
+        <v>0.44560100000000002</v>
+      </c>
+      <c r="R26" s="6"/>
+      <c r="U26" s="57"/>
+    </row>
+    <row r="27" spans="3:21" x14ac:dyDescent="0.3">
+      <c r="M27" t="s">
+        <v>31</v>
+      </c>
+      <c r="N27" t="s">
+        <v>15</v>
+      </c>
+      <c r="O27">
+        <v>9</v>
+      </c>
+      <c r="P27" s="6">
+        <v>1.8979380000000001E-6</v>
+      </c>
+      <c r="Q27">
+        <v>0</v>
+      </c>
+      <c r="R27" s="6"/>
+      <c r="U27" s="6"/>
+    </row>
+    <row r="28" spans="3:21" x14ac:dyDescent="0.3">
+      <c r="M28" t="s">
+        <v>32</v>
+      </c>
+      <c r="N28" t="s">
+        <v>15</v>
+      </c>
+      <c r="O28">
+        <v>2</v>
+      </c>
+      <c r="P28" s="6">
+        <v>2.4827299999999998E-3</v>
+      </c>
+      <c r="Q28">
+        <v>0</v>
+      </c>
+      <c r="R28" s="6"/>
+      <c r="U28" s="6"/>
+    </row>
+    <row r="29" spans="3:21" x14ac:dyDescent="0.3">
+      <c r="C29" t="s">
+        <v>40</v>
       </c>
       <c r="R29" s="6"/>
     </row>

--- a/test/G14-G24.xlsx
+++ b/test/G14-G24.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wolfgang\Documents\GitHub\SACOBRA_Py\test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9997AEB9-44CE-45CF-A9FB-8A3C1B6387D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71852591-B033-402D-86E2-8A26D2659F26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23016" windowHeight="12216" activeTab="2" xr2:uid="{6EF9DD2D-A48A-4E61-B7E9-B72FBCB815D4}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="2" xr2:uid="{6EF9DD2D-A48A-4E61-B7E9-B72FBCB815D4}"/>
   </bookViews>
   <sheets>
     <sheet name="Python, MIDPTS" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="700" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="798" uniqueCount="65">
   <si>
     <t>SACOBRA_Py, 10 runs, mean(time), median(err)</t>
   </si>
@@ -280,8 +280,17 @@
     <t>NaN</t>
   </si>
   <si>
+    <t>df2_conTol0.0-trueFunc-fe500-G14-G24.feather from 12.09.2025</t>
+  </si>
+  <si>
+    <t>df2_conTol0.0-MIDPTS-fe500-G14-G24-EPS0.feather from 17.09.2025</t>
+  </si>
+  <si>
+    <t>df2_conTol0.0-MIDPTS-fe500-G14-G24-EPSNone.feather from 18.09.2025</t>
+  </si>
+  <si>
     <r>
-      <t xml:space="preserve">TGR=np.inf, muFinal=1e-7, </t>
+      <t xml:space="preserve">TGR=1e3, muFinal=1e-7, </t>
     </r>
     <r>
       <rPr>
@@ -296,16 +305,49 @@
     </r>
   </si>
   <si>
-    <t>n_infeasible</t>
+    <t>7 infeasible</t>
   </si>
   <si>
-    <t>df2_conTol0.0-trueFunc-fe500-G14-G24.feather from 12.09.2025</t>
+    <t>Runs</t>
   </si>
   <si>
-    <t>df2_conTol0.0-MIDPTS-fe500-G14-G24-EPS0.feather from 17.09.2025</t>
+    <t>that</t>
   </si>
   <si>
-    <t>df2_conTol0.0-MIDPTS-fe500-G14-G24-EPSNone.feather from 18.09.2025</t>
+    <t>found</t>
+  </si>
+  <si>
+    <t>no</t>
+  </si>
+  <si>
+    <t>feasible</t>
+  </si>
+  <si>
+    <t>solution</t>
+  </si>
+  <si>
+    <t>infeas</t>
+  </si>
+  <si>
+    <t>10 infeasible</t>
+  </si>
+  <si>
+    <t>TGR = np.inf</t>
+  </si>
+  <si>
+    <t>with TGR = np.inf, muFinal=1e-7:</t>
+  </si>
+  <si>
+    <t>infeasible</t>
+  </si>
+  <si>
+    <t>with TGR = np.inf, muFinal=1e-4:</t>
+  </si>
+  <si>
+    <t>after completing test_adCon2:</t>
+  </si>
+  <si>
+    <t>The results for G16, G21 are approx the same, those for G22 a bit worse, because all 10 instead of 7 runs are infeasible</t>
   </si>
 </sst>
 </file>
@@ -507,7 +549,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -589,6 +631,7 @@
     <xf numFmtId="11" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="1" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="11" fontId="0" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -1874,7 +1917,7 @@
     </row>
     <row r="27" spans="3:20" x14ac:dyDescent="0.3">
       <c r="C27" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="M27" t="s">
         <v>30</v>
@@ -2016,7 +2059,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D73ACDBB-3041-4110-9FE8-59E6685037CA}">
-  <dimension ref="C1:U33"/>
+  <dimension ref="C1:U42"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="9.6640625" customWidth="1"/>
@@ -2074,25 +2117,24 @@
       <c r="H4" s="4"/>
       <c r="I4" s="4"/>
       <c r="J4" s="5"/>
-      <c r="N4" t="s">
+      <c r="P4" t="s">
         <v>6</v>
       </c>
-      <c r="O4" t="s">
+      <c r="Q4" t="s">
         <v>7</v>
       </c>
-      <c r="P4" t="s">
+      <c r="R4" t="s">
         <v>8</v>
       </c>
-      <c r="Q4" t="s">
-        <v>9</v>
-      </c>
-      <c r="R4" t="s">
-        <v>10</v>
-      </c>
       <c r="S4" t="s">
+        <v>21</v>
+      </c>
+      <c r="T4" t="s">
+        <v>57</v>
+      </c>
+      <c r="U4" t="s">
         <v>33</v>
       </c>
-      <c r="T4" s="6"/>
     </row>
     <row r="5" spans="3:21" x14ac:dyDescent="0.3">
       <c r="C5" s="7"/>
@@ -2156,8 +2198,8 @@
       <c r="R6" s="6">
         <v>0.25236170000000002</v>
       </c>
-      <c r="S6">
-        <v>500</v>
+      <c r="S6" s="6">
+        <v>5.5589670000000001E-2</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -2180,13 +2222,13 @@
         <v>500</v>
       </c>
       <c r="G7" s="43">
-        <v>3888.6478099999999</v>
+        <v>2920.6830100000002</v>
       </c>
       <c r="H7" s="40">
-        <v>3.8567120000000003E-2</v>
+        <v>0.25236170000000002</v>
       </c>
       <c r="I7" s="6">
-        <v>0.1025192</v>
+        <v>5.5589670000000001E-2</v>
       </c>
       <c r="J7" s="21"/>
       <c r="M7" t="s">
@@ -2207,8 +2249,8 @@
       <c r="R7" s="6">
         <v>9.4757980000000001E-11</v>
       </c>
-      <c r="S7">
-        <v>500</v>
+      <c r="S7" s="6">
+        <v>3.627449E-9</v>
       </c>
       <c r="T7">
         <v>0</v>
@@ -2250,11 +2292,11 @@
       <c r="R8" s="6">
         <v>0.35452830000000002</v>
       </c>
-      <c r="S8">
-        <v>500</v>
+      <c r="S8" s="6">
+        <v>0.27507890000000002</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U8">
         <v>0</v>
@@ -2274,13 +2316,13 @@
         <v>500</v>
       </c>
       <c r="G9" s="20">
-        <v>2070.49449</v>
+        <v>1467.9233400000001</v>
       </c>
       <c r="H9" s="6">
-        <v>3.5015550000000002E-11</v>
+        <v>9.4757980000000001E-11</v>
       </c>
       <c r="I9" s="6">
-        <v>3.9105809999999999E-9</v>
+        <v>3.627449E-9</v>
       </c>
       <c r="J9" s="21"/>
       <c r="M9" t="s">
@@ -2301,11 +2343,11 @@
       <c r="R9" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="S9">
-        <v>500</v>
+      <c r="S9" t="s">
+        <v>45</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="U9">
         <v>0.82789199999999996</v>
@@ -2344,8 +2386,8 @@
       <c r="R10" s="6">
         <v>1.9695170000000002E-6</v>
       </c>
-      <c r="S10">
-        <v>500</v>
+      <c r="S10" s="6">
+        <v>5.9642769999999998E-2</v>
       </c>
       <c r="T10">
         <v>0</v>
@@ -2368,15 +2410,17 @@
         <v>500</v>
       </c>
       <c r="G11" s="20">
-        <v>6199.09094</v>
-      </c>
-      <c r="H11" s="6">
-        <v>4.7176989999999997E-3</v>
-      </c>
-      <c r="I11" s="6">
-        <v>2.3984829999999999E-2</v>
-      </c>
-      <c r="J11" s="21"/>
+        <v>991.33965499999999</v>
+      </c>
+      <c r="H11" s="40">
+        <v>0.35452830000000002</v>
+      </c>
+      <c r="I11" s="40">
+        <v>0.27507890000000002</v>
+      </c>
+      <c r="J11" s="21" t="s">
+        <v>39</v>
+      </c>
       <c r="M11" t="s">
         <v>28</v>
       </c>
@@ -2395,8 +2439,8 @@
       <c r="R11" s="6">
         <v>995.71360000000004</v>
       </c>
-      <c r="S11">
-        <v>500</v>
+      <c r="S11" s="6">
+        <v>553.72860000000003</v>
       </c>
       <c r="T11">
         <v>0</v>
@@ -2438,39 +2482,41 @@
       <c r="R12" s="6">
         <v>272.05380000000002</v>
       </c>
-      <c r="S12">
-        <v>500</v>
+      <c r="S12" s="6">
+        <v>78.527100000000004</v>
       </c>
       <c r="T12">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U12">
         <v>1.137E-3</v>
       </c>
     </row>
     <row r="13" spans="3:21" x14ac:dyDescent="0.3">
-      <c r="C13" s="41" t="s">
+      <c r="C13" s="26" t="s">
         <v>26</v>
       </c>
-      <c r="D13" s="42" t="s">
-        <v>15</v>
-      </c>
-      <c r="E13" s="41">
+      <c r="D13" s="27" t="s">
+        <v>15</v>
+      </c>
+      <c r="E13" s="26">
         <v>7</v>
       </c>
-      <c r="F13" s="42">
-        <v>500</v>
-      </c>
-      <c r="G13" s="43">
-        <v>2395.6140399999999</v>
-      </c>
-      <c r="H13" s="40">
-        <v>0.61001050000000001</v>
-      </c>
-      <c r="I13" s="40">
-        <v>9.1428799999999999</v>
-      </c>
-      <c r="J13" s="21"/>
+      <c r="F13" s="27">
+        <v>500</v>
+      </c>
+      <c r="G13" s="28">
+        <v>2620.81477</v>
+      </c>
+      <c r="H13" s="29" t="s">
+        <v>45</v>
+      </c>
+      <c r="I13" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="J13" s="30" t="s">
+        <v>58</v>
+      </c>
       <c r="M13" t="s">
         <v>30</v>
       </c>
@@ -2489,11 +2535,11 @@
       <c r="R13" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="S13">
-        <v>500</v>
+      <c r="S13" t="s">
+        <v>45</v>
       </c>
       <c r="T13">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="U13">
         <v>7.867299</v>
@@ -2532,8 +2578,8 @@
       <c r="R14" s="6">
         <v>6.0207919999999998E-6</v>
       </c>
-      <c r="S14">
-        <v>500</v>
+      <c r="S14" s="6">
+        <v>3.2697749999999999E-9</v>
       </c>
       <c r="T14">
         <v>0</v>
@@ -2556,13 +2602,13 @@
         <v>500</v>
       </c>
       <c r="G15" s="20">
-        <v>1872.3066100000001</v>
+        <v>1322.095685</v>
       </c>
       <c r="H15" s="6">
-        <v>-2.034669E-4</v>
+        <v>1.9695170000000002E-6</v>
       </c>
       <c r="I15" s="6">
-        <v>1.095445E-4</v>
+        <v>5.9642769999999998E-2</v>
       </c>
       <c r="J15" s="21"/>
       <c r="M15" t="s">
@@ -2583,8 +2629,8 @@
       <c r="R15" s="6">
         <v>0.38026890000000002</v>
       </c>
-      <c r="S15">
-        <v>500</v>
+      <c r="S15" s="6">
+        <v>0.24222579999999999</v>
       </c>
       <c r="T15">
         <v>0</v>
@@ -2609,7 +2655,7 @@
       <c r="I16" s="22"/>
       <c r="J16" s="25"/>
     </row>
-    <row r="17" spans="3:20" x14ac:dyDescent="0.3">
+    <row r="17" spans="3:21" x14ac:dyDescent="0.3">
       <c r="C17" s="26" t="s">
         <v>28</v>
       </c>
@@ -2623,13 +2669,13 @@
         <v>500</v>
       </c>
       <c r="G17" s="28">
-        <v>1474.1254799999999</v>
+        <v>5779.8368049999999</v>
       </c>
       <c r="H17" s="29">
-        <v>132.36429999999999</v>
+        <v>995.71360000000004</v>
       </c>
       <c r="I17" s="6">
-        <v>143.55250000000001</v>
+        <v>553.72860000000003</v>
       </c>
       <c r="J17" s="30"/>
       <c r="N17" t="s">
@@ -2654,7 +2700,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="3:20" x14ac:dyDescent="0.3">
+    <row r="18" spans="3:21" x14ac:dyDescent="0.3">
       <c r="C18" s="31"/>
       <c r="D18" s="32" t="s">
         <v>17</v>
@@ -2676,10 +2722,10 @@
         <v>33</v>
       </c>
       <c r="R18" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="19" spans="3:20" x14ac:dyDescent="0.3">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="19" spans="3:21" x14ac:dyDescent="0.3">
       <c r="C19" s="26" t="s">
         <v>29</v>
       </c>
@@ -2693,15 +2739,17 @@
         <v>500</v>
       </c>
       <c r="G19" s="28">
-        <v>2971.309385</v>
+        <v>2963.3486950000001</v>
       </c>
       <c r="H19" s="29">
-        <v>317.53919999999999</v>
+        <v>272.05380000000002</v>
       </c>
       <c r="I19" s="6">
-        <v>146.67269999999999</v>
-      </c>
-      <c r="J19" s="30"/>
+        <v>78.527100000000004</v>
+      </c>
+      <c r="J19" s="21" t="s">
+        <v>35</v>
+      </c>
       <c r="M19" t="s">
         <v>11</v>
       </c>
@@ -2714,7 +2762,7 @@
       <c r="R19" s="6"/>
       <c r="S19" s="6"/>
     </row>
-    <row r="20" spans="3:20" x14ac:dyDescent="0.3">
+    <row r="20" spans="3:21" x14ac:dyDescent="0.3">
       <c r="C20" s="31"/>
       <c r="D20" s="32" t="s">
         <v>17</v>
@@ -2748,7 +2796,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="3:20" x14ac:dyDescent="0.3">
+    <row r="21" spans="3:21" x14ac:dyDescent="0.3">
       <c r="C21" s="26" t="s">
         <v>30</v>
       </c>
@@ -2762,15 +2810,17 @@
         <v>500</v>
       </c>
       <c r="G21" s="28">
-        <v>17000.01197</v>
-      </c>
-      <c r="H21" s="29">
-        <v>35.187019999999997</v>
-      </c>
-      <c r="I21" s="6">
-        <v>2319.5880000000002</v>
-      </c>
-      <c r="J21" s="30"/>
+        <v>6047.4524350000002</v>
+      </c>
+      <c r="H21" s="29" t="s">
+        <v>45</v>
+      </c>
+      <c r="I21" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="J21" s="21" t="s">
+        <v>58</v>
+      </c>
       <c r="M21" t="s">
         <v>24</v>
       </c>
@@ -2790,7 +2840,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="3:20" x14ac:dyDescent="0.3">
+    <row r="22" spans="3:21" x14ac:dyDescent="0.3">
       <c r="C22" s="31"/>
       <c r="D22" s="32" t="s">
         <v>17</v>
@@ -2824,7 +2874,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="23" spans="3:20" x14ac:dyDescent="0.3">
+    <row r="23" spans="3:21" x14ac:dyDescent="0.3">
       <c r="C23" s="7" t="s">
         <v>31</v>
       </c>
@@ -2838,13 +2888,13 @@
         <v>500</v>
       </c>
       <c r="G23" s="20">
-        <v>3993.4907050000002</v>
+        <v>2437.34157</v>
       </c>
       <c r="H23" s="6">
-        <v>1.1281830000000001E-3</v>
-      </c>
-      <c r="I23" s="40">
-        <v>118.1583</v>
+        <v>6.0207919999999998E-6</v>
+      </c>
+      <c r="I23" s="6">
+        <v>3.2697749999999999E-9</v>
       </c>
       <c r="J23" s="21"/>
       <c r="M23" t="s">
@@ -2866,7 +2916,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="24" spans="3:20" x14ac:dyDescent="0.3">
+    <row r="24" spans="3:21" x14ac:dyDescent="0.3">
       <c r="C24" s="7"/>
       <c r="D24" t="s">
         <v>17</v>
@@ -2900,7 +2950,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="3:20" x14ac:dyDescent="0.3">
+    <row r="25" spans="3:21" x14ac:dyDescent="0.3">
       <c r="C25" s="3" t="s">
         <v>32</v>
       </c>
@@ -2914,13 +2964,13 @@
         <v>500</v>
       </c>
       <c r="G25" s="38">
-        <v>609.53940999999998</v>
-      </c>
-      <c r="H25" s="39">
-        <v>3.1007420000000003E-8</v>
-      </c>
-      <c r="I25" s="6">
-        <v>4.0774329999999998E-8</v>
+        <v>700.421425</v>
+      </c>
+      <c r="H25" s="40">
+        <v>0.38026890000000002</v>
+      </c>
+      <c r="I25" s="40">
+        <v>0.24222579999999999</v>
       </c>
       <c r="J25" s="23"/>
       <c r="M25" t="s">
@@ -2942,7 +2992,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="3:20" x14ac:dyDescent="0.3">
+    <row r="26" spans="3:21" x14ac:dyDescent="0.3">
       <c r="C26" s="16"/>
       <c r="D26" s="17" t="s">
         <v>17</v>
@@ -2976,9 +3026,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="27" spans="3:20" x14ac:dyDescent="0.3">
+    <row r="27" spans="3:21" x14ac:dyDescent="0.3">
       <c r="C27" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="M27" t="s">
         <v>30</v>
@@ -2999,7 +3049,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="28" spans="3:20" x14ac:dyDescent="0.3">
+    <row r="28" spans="3:21" x14ac:dyDescent="0.3">
       <c r="M28" t="s">
         <v>31</v>
       </c>
@@ -3019,7 +3069,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="3:20" x14ac:dyDescent="0.3">
+    <row r="29" spans="3:21" x14ac:dyDescent="0.3">
       <c r="M29" t="s">
         <v>32</v>
       </c>
@@ -3039,60 +3089,189 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="3:20" x14ac:dyDescent="0.3">
+    <row r="30" spans="3:21" x14ac:dyDescent="0.3">
       <c r="R30" s="6"/>
     </row>
-    <row r="31" spans="3:20" x14ac:dyDescent="0.3">
+    <row r="31" spans="3:21" x14ac:dyDescent="0.3">
+      <c r="N31" t="s">
+        <v>2</v>
+      </c>
+      <c r="O31" t="s">
+        <v>51</v>
+      </c>
+      <c r="P31" t="s">
+        <v>52</v>
+      </c>
       <c r="Q31" t="s">
+        <v>53</v>
+      </c>
+      <c r="R31" t="s">
+        <v>54</v>
+      </c>
+      <c r="S31" t="s">
+        <v>55</v>
+      </c>
+      <c r="T31" t="s">
+        <v>56</v>
+      </c>
+      <c r="U31" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32" spans="3:21" x14ac:dyDescent="0.3">
+      <c r="M32" t="s">
+        <v>11</v>
+      </c>
+      <c r="N32" t="s">
+        <v>12</v>
+      </c>
+      <c r="O32" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="33" spans="13:21" x14ac:dyDescent="0.3">
+      <c r="M33" t="s">
+        <v>23</v>
+      </c>
+      <c r="N33" t="s">
+        <v>15</v>
+      </c>
+      <c r="O33">
+        <v>10</v>
+      </c>
+      <c r="P33">
+        <v>0</v>
+      </c>
+      <c r="R33" s="6"/>
+      <c r="S33" s="6"/>
+      <c r="T33" s="37"/>
+      <c r="U33" s="36"/>
+    </row>
+    <row r="34" spans="13:21" x14ac:dyDescent="0.3">
+      <c r="M34" t="s">
+        <v>24</v>
+      </c>
+      <c r="N34" t="s">
+        <v>15</v>
+      </c>
+      <c r="O34">
+        <v>3</v>
+      </c>
+      <c r="P34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="13:21" x14ac:dyDescent="0.3">
+      <c r="M35" t="s">
+        <v>25</v>
+      </c>
+      <c r="N35" t="s">
+        <v>15</v>
+      </c>
+      <c r="O35">
+        <v>5</v>
+      </c>
+      <c r="P35">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="36" spans="13:21" x14ac:dyDescent="0.3">
+      <c r="M36" t="s">
+        <v>26</v>
+      </c>
+      <c r="N36" t="s">
+        <v>15</v>
+      </c>
+      <c r="O36">
+        <v>6</v>
+      </c>
+      <c r="P36">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="37" spans="13:21" x14ac:dyDescent="0.3">
+      <c r="M37" t="s">
+        <v>27</v>
+      </c>
+      <c r="N37" t="s">
+        <v>15</v>
+      </c>
+      <c r="O37">
+        <v>9</v>
+      </c>
+      <c r="P37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="13:21" x14ac:dyDescent="0.3">
+      <c r="M38" t="s">
+        <v>28</v>
+      </c>
+      <c r="N38" t="s">
+        <v>15</v>
+      </c>
+      <c r="O38">
+        <v>15</v>
+      </c>
+      <c r="P38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="13:21" x14ac:dyDescent="0.3">
+      <c r="M39" t="s">
+        <v>29</v>
+      </c>
+      <c r="N39" t="s">
+        <v>15</v>
+      </c>
+      <c r="O39">
         <v>7</v>
       </c>
-      <c r="R31" t="s">
-        <v>8</v>
-      </c>
-      <c r="S31" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="32" spans="3:20" x14ac:dyDescent="0.3">
-      <c r="M32" t="s">
-        <v>18</v>
-      </c>
-      <c r="N32" t="s">
-        <v>15</v>
-      </c>
-      <c r="O32">
-        <v>20</v>
-      </c>
-      <c r="Q32">
-        <v>6569.9168900000004</v>
-      </c>
-      <c r="R32">
-        <v>0.99977099999999997</v>
-      </c>
-      <c r="S32">
-        <v>0.47947800000000002</v>
-      </c>
-    </row>
-    <row r="33" spans="14:21" x14ac:dyDescent="0.3">
-      <c r="N33" t="s">
-        <v>15</v>
-      </c>
-      <c r="O33">
-        <v>20</v>
-      </c>
-      <c r="Q33">
-        <v>1795.19146</v>
-      </c>
-      <c r="R33" s="6">
-        <v>4.8106590000000001E-10</v>
-      </c>
-      <c r="S33" s="6">
-        <v>1.5764049999999999E-10</v>
-      </c>
-      <c r="T33" s="37" t="s">
-        <v>19</v>
-      </c>
-      <c r="U33" s="36"/>
+      <c r="P39">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="40" spans="13:21" x14ac:dyDescent="0.3">
+      <c r="M40" t="s">
+        <v>30</v>
+      </c>
+      <c r="N40" t="s">
+        <v>15</v>
+      </c>
+      <c r="O40">
+        <v>22</v>
+      </c>
+      <c r="P40">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="41" spans="13:21" x14ac:dyDescent="0.3">
+      <c r="M41" t="s">
+        <v>31</v>
+      </c>
+      <c r="N41" t="s">
+        <v>15</v>
+      </c>
+      <c r="O41">
+        <v>9</v>
+      </c>
+      <c r="P41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="13:21" x14ac:dyDescent="0.3">
+      <c r="M42" t="s">
+        <v>32</v>
+      </c>
+      <c r="N42" t="s">
+        <v>15</v>
+      </c>
+      <c r="O42">
+        <v>2</v>
+      </c>
+      <c r="P42">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
@@ -3102,7 +3281,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE45503C-F2E8-4674-A77D-9967A224D2EC}">
-  <dimension ref="C1:U33"/>
+  <dimension ref="C1:U64"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="9.6640625" customWidth="1"/>
@@ -3122,7 +3301,7 @@
     </row>
     <row r="2" spans="3:21" x14ac:dyDescent="0.3">
       <c r="C2" s="2" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3" spans="3:21" x14ac:dyDescent="0.3">
@@ -3142,9 +3321,12 @@
         <v>5</v>
       </c>
       <c r="R3" t="s">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="S3" t="s">
+        <v>38</v>
+      </c>
+      <c r="T3" t="s">
         <v>2</v>
       </c>
     </row>
@@ -3167,7 +3349,7 @@
         <v>8</v>
       </c>
       <c r="S4" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="T4" t="s">
         <v>10</v>
@@ -3233,13 +3415,13 @@
         <v>58.5</v>
       </c>
       <c r="Q6" s="6">
-        <v>3592.6765999999998</v>
+        <v>9393.7015050000009</v>
       </c>
       <c r="R6" s="6">
-        <v>0.25236170000000002</v>
+        <v>2.1038279999999999E-3</v>
       </c>
       <c r="S6" s="6">
-        <v>5.5589670000000001E-2</v>
+        <v>2.4601499999999998E-2</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -3262,13 +3444,13 @@
         <v>500</v>
       </c>
       <c r="G7" s="43">
-        <v>3888.6478099999999</v>
+        <v>9393.7015050000009</v>
       </c>
       <c r="H7" s="40">
-        <v>0.25236170000000002</v>
+        <v>2.1038279999999999E-3</v>
       </c>
       <c r="I7" s="6">
-        <v>5.5589670000000001E-2</v>
+        <v>2.4601499999999998E-2</v>
       </c>
       <c r="J7" s="21"/>
       <c r="M7" t="s">
@@ -3284,13 +3466,13 @@
         <v>58.5</v>
       </c>
       <c r="Q7" s="6">
-        <v>1478.997775</v>
+        <v>5978.2993800000004</v>
       </c>
       <c r="R7" s="6">
-        <v>9.4757980000000001E-11</v>
+        <v>6.5767840000000003E-11</v>
       </c>
       <c r="S7" s="6">
-        <v>3.627449E-9</v>
+        <v>3.4637669999999998E-10</v>
       </c>
       <c r="T7">
         <v>0</v>
@@ -3327,13 +3509,13 @@
         <v>58.5</v>
       </c>
       <c r="Q8">
-        <v>1140.0182950000001</v>
+        <v>8213.395235</v>
       </c>
       <c r="R8" s="6">
-        <v>0.39021549999999999</v>
+        <v>5.043685E-3</v>
       </c>
       <c r="S8" s="6">
-        <v>0.25917600000000002</v>
+        <v>3.8680099999999999E-3</v>
       </c>
       <c r="T8">
         <v>0</v>
@@ -3356,13 +3538,13 @@
         <v>500</v>
       </c>
       <c r="G9" s="20">
-        <v>2070.49449</v>
+        <v>5978.2993800000004</v>
       </c>
       <c r="H9" s="6">
-        <v>9.4757980000000001E-11</v>
+        <v>6.5767840000000003E-11</v>
       </c>
       <c r="I9" s="6">
-        <v>3.627449E-9</v>
+        <v>3.4637669999999998E-10</v>
       </c>
       <c r="J9" s="21"/>
       <c r="M9" t="s">
@@ -3378,19 +3560,19 @@
         <v>58.5</v>
       </c>
       <c r="Q9" s="6">
-        <v>5101.20172</v>
-      </c>
-      <c r="R9" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="S9" s="6" t="s">
-        <v>45</v>
+        <v>7741.224905</v>
+      </c>
+      <c r="R9" s="6">
+        <v>1.5529409999999999</v>
+      </c>
+      <c r="S9" s="6">
+        <v>6.6845429999999997</v>
       </c>
       <c r="T9">
         <v>0</v>
       </c>
       <c r="U9">
-        <v>0.82789199999999996</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="3:21" x14ac:dyDescent="0.3">
@@ -3421,13 +3603,13 @@
         <v>58.5</v>
       </c>
       <c r="Q10">
-        <v>4673.11391</v>
+        <v>5714.4406349999999</v>
       </c>
       <c r="R10" s="6">
-        <v>8.6602490000000002E-5</v>
+        <v>8.660188E-5</v>
       </c>
       <c r="S10" s="6">
-        <v>1.2550110000000001E-4</v>
+        <v>1.095445E-4</v>
       </c>
       <c r="T10">
         <v>0</v>
@@ -3450,13 +3632,13 @@
         <v>500</v>
       </c>
       <c r="G11" s="20">
-        <v>6199.09094</v>
+        <v>8213.395235</v>
       </c>
       <c r="H11" s="6">
-        <v>0.39021549999999999</v>
+        <v>5.043685E-3</v>
       </c>
       <c r="I11" s="6">
-        <v>0.25917600000000002</v>
+        <v>3.8680099999999999E-3</v>
       </c>
       <c r="J11" s="21"/>
       <c r="M11" t="s">
@@ -3472,13 +3654,13 @@
         <v>58.5</v>
       </c>
       <c r="Q11" s="6">
-        <v>8734.5927649999994</v>
+        <v>4166.08</v>
       </c>
       <c r="R11" s="6">
-        <v>978.48789999999997</v>
+        <v>194.70959999999999</v>
       </c>
       <c r="S11" s="6">
-        <v>761.50710000000004</v>
+        <v>138.19730000000001</v>
       </c>
       <c r="T11">
         <v>0</v>
@@ -3490,7 +3672,7 @@
     <row r="12" spans="3:21" x14ac:dyDescent="0.3">
       <c r="C12" s="16"/>
       <c r="D12" s="17" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E12" s="16">
         <v>5</v>
@@ -3498,10 +3680,19 @@
       <c r="F12" s="17">
         <v>500</v>
       </c>
-      <c r="G12" s="22"/>
-      <c r="H12" s="24"/>
-      <c r="I12" s="22"/>
+      <c r="G12" s="22">
+        <v>11497.557994999999</v>
+      </c>
+      <c r="H12" s="24">
+        <v>1.771E-3</v>
+      </c>
+      <c r="I12" s="63">
+        <v>7.3415999999999995E-2</v>
+      </c>
       <c r="J12" s="25"/>
+      <c r="K12" t="s">
+        <v>59</v>
+      </c>
       <c r="M12" t="s">
         <v>29</v>
       </c>
@@ -3515,19 +3706,19 @@
         <v>58.5</v>
       </c>
       <c r="Q12" s="6">
-        <v>10614.685755</v>
+        <v>7889.6981100000003</v>
       </c>
       <c r="R12" s="6">
-        <v>272.6311</v>
+        <v>1.612616E-2</v>
       </c>
       <c r="S12" s="6">
-        <v>139.57169999999999</v>
+        <v>4.1754729999999997E-2</v>
       </c>
       <c r="T12">
         <v>0</v>
       </c>
       <c r="U12">
-        <v>2.444E-3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="3:21" x14ac:dyDescent="0.3">
@@ -3544,13 +3735,13 @@
         <v>500</v>
       </c>
       <c r="G13" s="43">
-        <v>2395.6140399999999</v>
-      </c>
-      <c r="H13" s="40" t="s">
-        <v>45</v>
-      </c>
-      <c r="I13" s="40" t="s">
-        <v>45</v>
+        <v>7741.224905</v>
+      </c>
+      <c r="H13" s="40">
+        <v>1.5529409999999999</v>
+      </c>
+      <c r="I13" s="40">
+        <v>6.6845429999999997</v>
       </c>
       <c r="J13" s="21"/>
       <c r="M13" t="s">
@@ -3566,36 +3757,34 @@
         <v>58.5</v>
       </c>
       <c r="Q13" s="6">
-        <v>5244.9437250000001</v>
-      </c>
-      <c r="R13" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="S13" s="6" t="s">
-        <v>45</v>
+        <v>11229.704555</v>
+      </c>
+      <c r="R13" s="6">
+        <v>10.59858</v>
+      </c>
+      <c r="S13" s="6">
+        <v>5.1004160000000001</v>
       </c>
       <c r="T13">
         <v>0</v>
       </c>
       <c r="U13">
-        <v>6.4378260000000003</v>
+        <v>2.382E-3</v>
       </c>
     </row>
     <row r="14" spans="3:21" x14ac:dyDescent="0.3">
       <c r="C14" s="16"/>
-      <c r="D14" s="17" t="s">
-        <v>17</v>
-      </c>
+      <c r="D14" s="19"/>
       <c r="E14" s="16">
         <v>7</v>
       </c>
       <c r="F14" s="17">
         <v>500</v>
       </c>
-      <c r="G14" s="22"/>
-      <c r="H14" s="24"/>
-      <c r="I14" s="22"/>
-      <c r="J14" s="25"/>
+      <c r="G14" s="17"/>
+      <c r="H14" s="17"/>
+      <c r="I14" s="17"/>
+      <c r="J14" s="17"/>
       <c r="M14" t="s">
         <v>31</v>
       </c>
@@ -3609,13 +3798,13 @@
         <v>58.5</v>
       </c>
       <c r="Q14" s="6">
-        <v>2785.9532899999999</v>
+        <v>3641.20739</v>
       </c>
       <c r="R14" s="6">
-        <v>6.6843999999999999E-6</v>
+        <v>6.1006459999999997E-6</v>
       </c>
       <c r="S14" s="6">
-        <v>2.084729E-3</v>
+        <v>6.3437500000000004E-3</v>
       </c>
       <c r="T14">
         <v>0</v>
@@ -3638,13 +3827,13 @@
         <v>500</v>
       </c>
       <c r="G15" s="20">
-        <v>1872.3066100000001</v>
+        <v>5714.4406349999999</v>
       </c>
       <c r="H15" s="6">
-        <v>8.6602490000000002E-5</v>
+        <v>8.660188E-5</v>
       </c>
       <c r="I15" s="6">
-        <v>1.2550110000000001E-4</v>
+        <v>1.095445E-4</v>
       </c>
       <c r="J15" s="21"/>
       <c r="M15" t="s">
@@ -3660,13 +3849,13 @@
         <v>58.5</v>
       </c>
       <c r="Q15" s="6">
-        <v>682.56723</v>
+        <v>624.53863000000001</v>
       </c>
       <c r="R15" s="6">
-        <v>0.3811059</v>
+        <v>3.1007420000000003E-8</v>
       </c>
       <c r="S15" s="6">
-        <v>0.24947330000000001</v>
+        <v>4.0774329999999998E-8</v>
       </c>
       <c r="T15">
         <v>0</v>
@@ -3707,13 +3896,13 @@
         <v>500</v>
       </c>
       <c r="G17" s="28">
-        <v>1474.1254799999999</v>
+        <v>4166.08</v>
       </c>
       <c r="H17" s="29">
-        <v>978.48789999999997</v>
+        <v>194.70959999999999</v>
       </c>
       <c r="I17" s="6">
-        <v>761.50710000000004</v>
+        <v>138.19730000000001</v>
       </c>
       <c r="J17" s="30"/>
       <c r="N17" t="s">
@@ -3729,9 +3918,12 @@
         <v>5</v>
       </c>
       <c r="R17" t="s">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="S17" t="s">
+        <v>38</v>
+      </c>
+      <c r="T17" t="s">
         <v>2</v>
       </c>
     </row>
@@ -3750,48 +3942,38 @@
       <c r="H18" s="34"/>
       <c r="I18" s="33"/>
       <c r="J18" s="35"/>
-      <c r="P18" t="s">
-        <v>6</v>
-      </c>
-      <c r="Q18" t="s">
-        <v>7</v>
-      </c>
-      <c r="R18" t="s">
+      <c r="N18" t="s">
         <v>8</v>
       </c>
-      <c r="S18" t="s">
-        <v>9</v>
-      </c>
-      <c r="T18" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="U18" s="6" t="s">
+      <c r="O18" t="s">
         <v>33</v>
       </c>
+      <c r="T18" s="6"/>
+      <c r="U18" s="6"/>
     </row>
     <row r="19" spans="3:21" x14ac:dyDescent="0.3">
-      <c r="C19" s="26" t="s">
+      <c r="C19" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="D19" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="E19" s="26">
+      <c r="D19" t="s">
+        <v>15</v>
+      </c>
+      <c r="E19" s="7">
         <v>4</v>
       </c>
-      <c r="F19" s="27">
-        <v>500</v>
-      </c>
-      <c r="G19" s="28">
-        <v>2971.309385</v>
-      </c>
-      <c r="H19" s="29">
-        <v>272.6311</v>
+      <c r="F19">
+        <v>500</v>
+      </c>
+      <c r="G19" s="20">
+        <v>7889.6981100000003</v>
+      </c>
+      <c r="H19" s="6">
+        <v>1.612616E-2</v>
       </c>
       <c r="I19" s="6">
-        <v>139.57169999999999</v>
-      </c>
-      <c r="J19" s="30"/>
+        <v>4.1754729999999997E-2</v>
+      </c>
+      <c r="J19" s="21"/>
       <c r="M19" t="s">
         <v>11</v>
       </c>
@@ -3804,20 +3986,29 @@
       <c r="R19" s="6"/>
     </row>
     <row r="20" spans="3:21" x14ac:dyDescent="0.3">
-      <c r="C20" s="31"/>
-      <c r="D20" s="32" t="s">
-        <v>17</v>
-      </c>
-      <c r="E20" s="31">
+      <c r="C20" s="16"/>
+      <c r="D20" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="E20" s="16">
         <v>4</v>
       </c>
-      <c r="F20" s="32">
-        <v>500</v>
-      </c>
-      <c r="G20" s="33"/>
-      <c r="H20" s="34"/>
-      <c r="I20" s="33"/>
-      <c r="J20" s="35"/>
+      <c r="F20" s="17">
+        <v>500</v>
+      </c>
+      <c r="G20" s="22">
+        <v>9021.6708450000006</v>
+      </c>
+      <c r="H20" s="24">
+        <v>1.699E-3</v>
+      </c>
+      <c r="I20" s="63">
+        <v>1.5568E-2</v>
+      </c>
+      <c r="J20" s="25"/>
+      <c r="K20" t="s">
+        <v>59</v>
+      </c>
       <c r="M20" t="s">
         <v>23</v>
       </c>
@@ -3827,24 +4018,13 @@
       <c r="O20">
         <v>10</v>
       </c>
-      <c r="P20">
-        <v>3.02765</v>
+      <c r="P20" s="6">
+        <v>2.4601499999999998E-2</v>
       </c>
       <c r="Q20">
-        <v>1305.014868</v>
-      </c>
-      <c r="R20" s="6">
-        <v>5.5589670000000001E-2</v>
-      </c>
-      <c r="S20">
-        <v>0</v>
-      </c>
-      <c r="T20">
-        <v>0</v>
-      </c>
-      <c r="U20">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="R20" s="6"/>
     </row>
     <row r="21" spans="3:21" x14ac:dyDescent="0.3">
       <c r="C21" s="26" t="s">
@@ -3860,15 +4040,17 @@
         <v>500</v>
       </c>
       <c r="G21" s="28">
-        <v>17000.01197</v>
-      </c>
-      <c r="H21" s="29" t="s">
-        <v>45</v>
-      </c>
-      <c r="I21" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="J21" s="30"/>
+        <v>11229.704555</v>
+      </c>
+      <c r="H21" s="29">
+        <v>10.59858</v>
+      </c>
+      <c r="I21" s="6">
+        <v>5.1004160000000001</v>
+      </c>
+      <c r="J21" s="30" t="s">
+        <v>50</v>
+      </c>
       <c r="M21" t="s">
         <v>24</v>
       </c>
@@ -3878,24 +4060,13 @@
       <c r="O21">
         <v>3</v>
       </c>
-      <c r="P21">
-        <v>3.02765</v>
+      <c r="P21" s="6">
+        <v>3.4637669999999998E-10</v>
       </c>
       <c r="Q21">
-        <v>107.874757</v>
-      </c>
-      <c r="R21" s="6">
-        <v>3.627449E-9</v>
-      </c>
-      <c r="S21">
-        <v>0</v>
-      </c>
-      <c r="T21">
-        <v>0</v>
-      </c>
-      <c r="U21">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="R21" s="6"/>
     </row>
     <row r="22" spans="3:21" x14ac:dyDescent="0.3">
       <c r="C22" s="31"/>
@@ -3908,10 +4079,21 @@
       <c r="F22" s="32">
         <v>500</v>
       </c>
-      <c r="G22" s="33"/>
-      <c r="H22" s="34"/>
-      <c r="I22" s="33"/>
-      <c r="J22" s="35"/>
+      <c r="G22" s="33">
+        <v>16759.19471</v>
+      </c>
+      <c r="H22" s="34" t="s">
+        <v>45</v>
+      </c>
+      <c r="I22" s="33" t="s">
+        <v>45</v>
+      </c>
+      <c r="J22" s="35" t="s">
+        <v>58</v>
+      </c>
+      <c r="K22" t="s">
+        <v>59</v>
+      </c>
       <c r="M22" t="s">
         <v>25</v>
       </c>
@@ -3921,24 +4103,13 @@
       <c r="O22">
         <v>5</v>
       </c>
-      <c r="P22">
-        <v>3.02765</v>
+      <c r="P22" s="6">
+        <v>3.8680099999999999E-3</v>
       </c>
       <c r="Q22">
-        <v>379.071887</v>
-      </c>
-      <c r="R22" s="6">
-        <v>0.25917600000000002</v>
-      </c>
-      <c r="S22">
-        <v>0</v>
-      </c>
-      <c r="T22">
-        <v>0</v>
-      </c>
-      <c r="U22">
-        <v>2.2192090000000002</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="R22" s="6"/>
     </row>
     <row r="23" spans="3:21" x14ac:dyDescent="0.3">
       <c r="C23" s="7" t="s">
@@ -3954,13 +4125,13 @@
         <v>500</v>
       </c>
       <c r="G23" s="20">
-        <v>3993.4907050000002</v>
+        <v>3641.20739</v>
       </c>
       <c r="H23" s="6">
-        <v>6.6843999999999999E-6</v>
-      </c>
-      <c r="I23" s="40">
-        <v>2.084729E-3</v>
+        <v>6.1006459999999997E-6</v>
+      </c>
+      <c r="I23" s="6">
+        <v>6.3437500000000004E-3</v>
       </c>
       <c r="J23" s="21"/>
       <c r="M23" t="s">
@@ -3972,24 +4143,13 @@
       <c r="O23">
         <v>6</v>
       </c>
-      <c r="P23">
-        <v>3.02765</v>
+      <c r="P23" s="6">
+        <v>6.6845429999999997</v>
       </c>
       <c r="Q23">
-        <v>4517.8191459999998</v>
-      </c>
-      <c r="R23" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="S23">
-        <v>0</v>
-      </c>
-      <c r="T23">
-        <v>0</v>
-      </c>
-      <c r="U23">
-        <v>6.8633569999999997</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="R23" s="6"/>
     </row>
     <row r="24" spans="3:21" x14ac:dyDescent="0.3">
       <c r="C24" s="7"/>
@@ -4015,24 +4175,13 @@
       <c r="O24">
         <v>9</v>
       </c>
-      <c r="P24">
-        <v>3.02765</v>
+      <c r="P24" s="6">
+        <v>1.095445E-4</v>
       </c>
       <c r="Q24">
-        <v>547385.12895499996</v>
-      </c>
-      <c r="R24" s="6">
-        <v>1.2550110000000001E-4</v>
-      </c>
-      <c r="S24">
-        <v>0</v>
-      </c>
-      <c r="T24">
-        <v>0</v>
-      </c>
-      <c r="U24">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="R24" s="6"/>
     </row>
     <row r="25" spans="3:21" x14ac:dyDescent="0.3">
       <c r="C25" s="3" t="s">
@@ -4048,13 +4197,13 @@
         <v>500</v>
       </c>
       <c r="G25" s="38">
-        <v>609.53940999999998</v>
+        <v>624.53863000000001</v>
       </c>
       <c r="H25" s="39">
-        <v>0.3811059</v>
+        <v>3.1007420000000003E-8</v>
       </c>
       <c r="I25" s="6">
-        <v>0.24947330000000001</v>
+        <v>4.0774329999999998E-8</v>
       </c>
       <c r="J25" s="23"/>
       <c r="M25" t="s">
@@ -4066,24 +4215,13 @@
       <c r="O25">
         <v>15</v>
       </c>
-      <c r="P25">
-        <v>3.02765</v>
+      <c r="P25" s="6">
+        <v>138.19730000000001</v>
       </c>
       <c r="Q25">
-        <v>934.82921799999997</v>
-      </c>
-      <c r="R25" s="6">
-        <v>761.50710000000004</v>
-      </c>
-      <c r="S25">
-        <v>0</v>
-      </c>
-      <c r="T25">
-        <v>0</v>
-      </c>
-      <c r="U25">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="R25" s="6"/>
     </row>
     <row r="26" spans="3:21" x14ac:dyDescent="0.3">
       <c r="C26" s="16"/>
@@ -4109,28 +4247,17 @@
       <c r="O26">
         <v>7</v>
       </c>
-      <c r="P26">
-        <v>3.02765</v>
+      <c r="P26" s="6">
+        <v>4.1754729999999997E-2</v>
       </c>
       <c r="Q26">
-        <v>1095.5545890000001</v>
-      </c>
-      <c r="R26" s="6">
-        <v>139.57169999999999</v>
-      </c>
-      <c r="S26">
-        <v>0</v>
-      </c>
-      <c r="T26">
-        <v>0</v>
-      </c>
-      <c r="U26">
-        <v>1.2312E-2</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="R26" s="6"/>
     </row>
     <row r="27" spans="3:21" x14ac:dyDescent="0.3">
       <c r="C27" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="M27" t="s">
         <v>30</v>
@@ -4141,24 +4268,13 @@
       <c r="O27">
         <v>22</v>
       </c>
-      <c r="P27">
-        <v>3.02765</v>
+      <c r="P27" s="6">
+        <v>5.1004160000000001</v>
       </c>
       <c r="Q27">
-        <v>452.61137400000001</v>
-      </c>
-      <c r="R27" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="S27">
-        <v>0</v>
-      </c>
-      <c r="T27">
-        <v>0</v>
-      </c>
-      <c r="U27">
-        <v>8.3941579999999991</v>
-      </c>
+        <v>5.8510000000000003E-3</v>
+      </c>
+      <c r="R27" s="6"/>
     </row>
     <row r="28" spans="3:21" x14ac:dyDescent="0.3">
       <c r="M28" t="s">
@@ -4170,24 +4286,13 @@
       <c r="O28">
         <v>9</v>
       </c>
-      <c r="P28">
-        <v>3.02765</v>
+      <c r="P28" s="6">
+        <v>6.3437500000000004E-3</v>
       </c>
       <c r="Q28">
-        <v>390.36645700000003</v>
-      </c>
-      <c r="R28" s="6">
-        <v>2.084729E-3</v>
-      </c>
-      <c r="S28">
-        <v>0</v>
-      </c>
-      <c r="T28">
-        <v>0</v>
-      </c>
-      <c r="U28">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="R28" s="6"/>
     </row>
     <row r="29" spans="3:21" x14ac:dyDescent="0.3">
       <c r="M29" t="s">
@@ -4199,24 +4304,13 @@
       <c r="O29">
         <v>2</v>
       </c>
-      <c r="P29">
-        <v>3.02765</v>
+      <c r="P29" s="6">
+        <v>4.0774329999999998E-8</v>
       </c>
       <c r="Q29">
-        <v>148.856977</v>
-      </c>
-      <c r="R29" s="6">
-        <v>0.24947330000000001</v>
-      </c>
-      <c r="S29">
-        <v>0</v>
-      </c>
-      <c r="T29">
-        <v>0</v>
-      </c>
-      <c r="U29">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="R29" s="6"/>
     </row>
     <row r="30" spans="3:21" x14ac:dyDescent="0.3">
       <c r="R30" s="6"/>
@@ -4252,7 +4346,7 @@
         <v>0.47947800000000002</v>
       </c>
     </row>
-    <row r="33" spans="14:21" x14ac:dyDescent="0.3">
+    <row r="33" spans="13:21" x14ac:dyDescent="0.3">
       <c r="N33" t="s">
         <v>15</v>
       </c>
@@ -4272,6 +4366,400 @@
         <v>19</v>
       </c>
       <c r="U33" s="36"/>
+    </row>
+    <row r="36" spans="13:21" x14ac:dyDescent="0.3">
+      <c r="M36" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="37" spans="13:21" x14ac:dyDescent="0.3">
+      <c r="N37" t="s">
+        <v>2</v>
+      </c>
+      <c r="O37" t="s">
+        <v>3</v>
+      </c>
+      <c r="P37" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q37" t="s">
+        <v>5</v>
+      </c>
+      <c r="R37" t="s">
+        <v>37</v>
+      </c>
+      <c r="S37" t="s">
+        <v>38</v>
+      </c>
+      <c r="T37" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="38" spans="13:21" x14ac:dyDescent="0.3">
+      <c r="P38" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q38" t="s">
+        <v>7</v>
+      </c>
+      <c r="R38" t="s">
+        <v>8</v>
+      </c>
+      <c r="S38" t="s">
+        <v>21</v>
+      </c>
+      <c r="T38" t="s">
+        <v>61</v>
+      </c>
+      <c r="U38" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="39" spans="13:21" x14ac:dyDescent="0.3">
+      <c r="M39" t="s">
+        <v>11</v>
+      </c>
+      <c r="N39" t="s">
+        <v>12</v>
+      </c>
+      <c r="O39" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="40" spans="13:21" x14ac:dyDescent="0.3">
+      <c r="M40" t="s">
+        <v>25</v>
+      </c>
+      <c r="N40" t="s">
+        <v>15</v>
+      </c>
+      <c r="O40">
+        <v>5</v>
+      </c>
+      <c r="P40">
+        <v>58.5</v>
+      </c>
+      <c r="Q40">
+        <v>11497.557994999999</v>
+      </c>
+      <c r="R40">
+        <v>1.771E-3</v>
+      </c>
+      <c r="S40">
+        <v>7.3415999999999995E-2</v>
+      </c>
+      <c r="T40">
+        <v>0</v>
+      </c>
+      <c r="U40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="13:21" x14ac:dyDescent="0.3">
+      <c r="M41" t="s">
+        <v>29</v>
+      </c>
+      <c r="N41" t="s">
+        <v>15</v>
+      </c>
+      <c r="O41">
+        <v>7</v>
+      </c>
+      <c r="P41">
+        <v>58.5</v>
+      </c>
+      <c r="Q41">
+        <v>9021.6708450000006</v>
+      </c>
+      <c r="R41">
+        <v>1.699E-3</v>
+      </c>
+      <c r="S41">
+        <v>1.5568E-2</v>
+      </c>
+      <c r="T41">
+        <v>0</v>
+      </c>
+      <c r="U41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="13:21" x14ac:dyDescent="0.3">
+      <c r="M42" t="s">
+        <v>30</v>
+      </c>
+      <c r="N42" t="s">
+        <v>15</v>
+      </c>
+      <c r="O42">
+        <v>22</v>
+      </c>
+      <c r="P42">
+        <v>58.5</v>
+      </c>
+      <c r="Q42">
+        <v>16759.19471</v>
+      </c>
+      <c r="R42" t="s">
+        <v>45</v>
+      </c>
+      <c r="S42" t="s">
+        <v>45</v>
+      </c>
+      <c r="T42">
+        <v>10</v>
+      </c>
+      <c r="U42">
+        <v>5.8215999999999997E-2</v>
+      </c>
+    </row>
+    <row r="44" spans="13:21" x14ac:dyDescent="0.3">
+      <c r="M44" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="45" spans="13:21" x14ac:dyDescent="0.3">
+      <c r="N45" t="s">
+        <v>2</v>
+      </c>
+      <c r="O45" t="s">
+        <v>3</v>
+      </c>
+      <c r="P45" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q45" t="s">
+        <v>5</v>
+      </c>
+      <c r="R45" t="s">
+        <v>37</v>
+      </c>
+      <c r="S45" t="s">
+        <v>38</v>
+      </c>
+      <c r="T45" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="46" spans="13:21" x14ac:dyDescent="0.3">
+      <c r="P46" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q46" t="s">
+        <v>7</v>
+      </c>
+      <c r="R46" t="s">
+        <v>8</v>
+      </c>
+      <c r="S46" t="s">
+        <v>21</v>
+      </c>
+      <c r="T46" t="s">
+        <v>61</v>
+      </c>
+      <c r="U46" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="47" spans="13:21" x14ac:dyDescent="0.3">
+      <c r="M47" t="s">
+        <v>11</v>
+      </c>
+      <c r="N47" t="s">
+        <v>12</v>
+      </c>
+      <c r="O47" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="48" spans="13:21" x14ac:dyDescent="0.3">
+      <c r="M48" t="s">
+        <v>30</v>
+      </c>
+      <c r="N48" t="s">
+        <v>15</v>
+      </c>
+      <c r="O48">
+        <v>22</v>
+      </c>
+      <c r="P48">
+        <v>58.5</v>
+      </c>
+      <c r="Q48">
+        <v>16759.19471</v>
+      </c>
+      <c r="R48">
+        <v>487</v>
+      </c>
+      <c r="S48">
+        <v>688</v>
+      </c>
+      <c r="T48">
+        <v>8</v>
+      </c>
+      <c r="U48">
+        <v>5.8215999999999997E-2</v>
+      </c>
+    </row>
+    <row r="51" spans="13:21" x14ac:dyDescent="0.3">
+      <c r="M51" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="52" spans="13:21" x14ac:dyDescent="0.3">
+      <c r="M52" t="s">
+        <v>2</v>
+      </c>
+      <c r="N52" t="s">
+        <v>3</v>
+      </c>
+      <c r="O52" t="s">
+        <v>4</v>
+      </c>
+      <c r="P52" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q52" t="s">
+        <v>37</v>
+      </c>
+      <c r="R52" t="s">
+        <v>38</v>
+      </c>
+      <c r="S52" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="53" spans="13:21" x14ac:dyDescent="0.3">
+      <c r="P53" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q53" t="s">
+        <v>7</v>
+      </c>
+      <c r="R53" t="s">
+        <v>8</v>
+      </c>
+      <c r="S53" t="s">
+        <v>21</v>
+      </c>
+      <c r="T53" t="s">
+        <v>61</v>
+      </c>
+      <c r="U53" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="54" spans="13:21" x14ac:dyDescent="0.3">
+      <c r="M54" t="s">
+        <v>11</v>
+      </c>
+      <c r="N54" t="s">
+        <v>12</v>
+      </c>
+      <c r="O54" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="55" spans="13:21" x14ac:dyDescent="0.3">
+      <c r="M55" t="s">
+        <v>25</v>
+      </c>
+      <c r="N55" t="s">
+        <v>15</v>
+      </c>
+      <c r="O55">
+        <v>5</v>
+      </c>
+      <c r="P55">
+        <v>58.5</v>
+      </c>
+      <c r="Q55">
+        <v>4285.8503449999998</v>
+      </c>
+      <c r="R55" s="6">
+        <v>4.9059999999999998E-3</v>
+      </c>
+      <c r="S55">
+        <v>6.6350999999999993E-2</v>
+      </c>
+      <c r="T55">
+        <v>0</v>
+      </c>
+      <c r="U55" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="13:21" x14ac:dyDescent="0.3">
+      <c r="M56" t="s">
+        <v>29</v>
+      </c>
+      <c r="N56" t="s">
+        <v>15</v>
+      </c>
+      <c r="O56">
+        <v>7</v>
+      </c>
+      <c r="P56">
+        <v>58.5</v>
+      </c>
+      <c r="Q56">
+        <v>2784.4817149999999</v>
+      </c>
+      <c r="R56" s="6">
+        <v>5.8756000000000003E-2</v>
+      </c>
+      <c r="S56">
+        <v>0.118936</v>
+      </c>
+      <c r="T56">
+        <v>0</v>
+      </c>
+      <c r="U56" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="13:21" x14ac:dyDescent="0.3">
+      <c r="M57" t="s">
+        <v>30</v>
+      </c>
+      <c r="N57" t="s">
+        <v>15</v>
+      </c>
+      <c r="O57">
+        <v>22</v>
+      </c>
+      <c r="P57">
+        <v>58.5</v>
+      </c>
+      <c r="Q57">
+        <v>16661.278170000001</v>
+      </c>
+      <c r="R57" t="s">
+        <v>45</v>
+      </c>
+      <c r="S57" t="s">
+        <v>45</v>
+      </c>
+      <c r="T57">
+        <v>10</v>
+      </c>
+      <c r="U57" s="6">
+        <v>33111880</v>
+      </c>
+    </row>
+    <row r="59" spans="13:21" x14ac:dyDescent="0.3">
+      <c r="M59" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="62" spans="13:21" x14ac:dyDescent="0.3">
+      <c r="Q62" s="6"/>
+    </row>
+    <row r="63" spans="13:21" x14ac:dyDescent="0.3">
+      <c r="Q63" s="6"/>
+    </row>
+    <row r="64" spans="13:21" x14ac:dyDescent="0.3">
+      <c r="Q64" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>

--- a/test/G14-G24.xlsx
+++ b/test/G14-G24.xlsx
@@ -8,17 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wolfgang\Documents\GitHub\SACOBRA_Py\test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71852591-B033-402D-86E2-8A26D2659F26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC77C04C-78E1-4CDA-9BE2-5ED204A5A8FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="2" xr2:uid="{6EF9DD2D-A48A-4E61-B7E9-B72FBCB815D4}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="3" xr2:uid="{6EF9DD2D-A48A-4E61-B7E9-B72FBCB815D4}"/>
   </bookViews>
   <sheets>
     <sheet name="Python, MIDPTS" sheetId="1" r:id="rId1"/>
     <sheet name="Python, MIDPTS EPS=0" sheetId="6" r:id="rId2"/>
     <sheet name="Python, MIDPTS EPS" sheetId="7" r:id="rId3"/>
-    <sheet name="Python, trueFunc OLD" sheetId="4" r:id="rId4"/>
-    <sheet name="Python, trueFunc" sheetId="3" r:id="rId5"/>
-    <sheet name="Python, trueFunc EPS=0" sheetId="5" r:id="rId6"/>
+    <sheet name="Python, MIDPTS+repair" sheetId="8" r:id="rId4"/>
+    <sheet name="Python, trueFunc OLD" sheetId="4" r:id="rId5"/>
+    <sheet name="Python, trueFunc" sheetId="3" r:id="rId6"/>
+    <sheet name="Python, trueFunc EPS=0" sheetId="5" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="798" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="946" uniqueCount="81">
   <si>
     <t>SACOBRA_Py, 10 runs, mean(time), median(err)</t>
   </si>
@@ -349,12 +350,63 @@
   <si>
     <t>The results for G16, G21 are approx the same, those for G22 a bit worse, because all 10 instead of 7 runs are infeasible</t>
   </si>
+  <si>
+    <t>n_repair</t>
+  </si>
+  <si>
+    <t>n_rep_suc</t>
+  </si>
+  <si>
+    <t>ISA.onlinePLOG = O_LOGIC.MIDPTS, RBF.kernel="cubic", repair with q=10, eps2=0</t>
+  </si>
+  <si>
+    <t>df2_repair-conTol0.0-MIDPTS-cubic-fe500-G14-24.feather from 17.10.2025</t>
+  </si>
+  <si>
+    <t>err slightly smaller</t>
+  </si>
+  <si>
+    <t>worse</t>
+  </si>
+  <si>
+    <t>muFinal</t>
+  </si>
+  <si>
+    <t>feather</t>
+  </si>
+  <si>
+    <t>df2-G22-T5</t>
+  </si>
+  <si>
+    <t>df2-G22-T1</t>
+  </si>
+  <si>
+    <t>df2-G22-T2</t>
+  </si>
+  <si>
+    <t>df2-G22-T3</t>
+  </si>
+  <si>
+    <t>df2-G22-T4</t>
+  </si>
+  <si>
+    <t>q</t>
+  </si>
+  <si>
+    <t>different conTol-muFinal-q-combinations:</t>
+  </si>
+  <si>
+    <t>better than trueFunc</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0"/>
+  </numFmts>
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -382,6 +434,12 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -549,7 +607,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -632,6 +690,8 @@
     <xf numFmtId="1" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="11" fontId="0" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -2890,13 +2950,16 @@
       <c r="G23" s="20">
         <v>2437.34157</v>
       </c>
-      <c r="H23" s="6">
+      <c r="H23" s="49">
         <v>6.0207919999999998E-6</v>
       </c>
-      <c r="I23" s="6">
+      <c r="I23" s="49">
         <v>3.2697749999999999E-9</v>
       </c>
       <c r="J23" s="21"/>
+      <c r="K23" t="s">
+        <v>80</v>
+      </c>
       <c r="M23" t="s">
         <v>26</v>
       </c>
@@ -4071,7 +4134,7 @@
     <row r="22" spans="3:21" x14ac:dyDescent="0.3">
       <c r="C22" s="31"/>
       <c r="D22" s="32" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E22" s="31">
         <v>2</v>
@@ -4127,13 +4190,16 @@
       <c r="G23" s="20">
         <v>3641.20739</v>
       </c>
-      <c r="H23" s="6">
+      <c r="H23" s="49">
         <v>6.1006459999999997E-6</v>
       </c>
-      <c r="I23" s="6">
+      <c r="I23" s="65">
         <v>6.3437500000000004E-3</v>
       </c>
-      <c r="J23" s="21"/>
+      <c r="J23" s="23"/>
+      <c r="K23" t="s">
+        <v>80</v>
+      </c>
       <c r="M23" t="s">
         <v>26</v>
       </c>
@@ -4165,7 +4231,7 @@
       <c r="G24" s="20"/>
       <c r="H24" s="6"/>
       <c r="I24" s="22"/>
-      <c r="J24" s="21"/>
+      <c r="J24" s="25"/>
       <c r="M24" t="s">
         <v>27</v>
       </c>
@@ -4202,7 +4268,7 @@
       <c r="H25" s="39">
         <v>3.1007420000000003E-8</v>
       </c>
-      <c r="I25" s="6">
+      <c r="I25" s="65">
         <v>4.0774329999999998E-8</v>
       </c>
       <c r="J25" s="23"/>
@@ -4768,6 +4834,1250 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48A95010-3662-48A4-8239-690C66FF4AEA}">
+  <dimension ref="C1:V64"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="3" max="3" width="9.6640625" customWidth="1"/>
+    <col min="4" max="4" width="8.88671875" customWidth="1"/>
+    <col min="5" max="5" width="4.77734375" customWidth="1"/>
+    <col min="6" max="6" width="6.88671875" customWidth="1"/>
+    <col min="7" max="7" width="8.77734375" customWidth="1"/>
+    <col min="9" max="9" width="9" customWidth="1"/>
+    <col min="11" max="11" width="18.5546875" customWidth="1"/>
+    <col min="12" max="12" width="3" customWidth="1"/>
+    <col min="22" max="22" width="4.5546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="3:19" ht="23.4" x14ac:dyDescent="0.45">
+      <c r="C1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="3:19" x14ac:dyDescent="0.3">
+      <c r="C2" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3" spans="3:19" x14ac:dyDescent="0.3">
+      <c r="C3" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="M3" t="s">
+        <v>2</v>
+      </c>
+      <c r="N3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>37</v>
+      </c>
+      <c r="R3" t="s">
+        <v>38</v>
+      </c>
+      <c r="S3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="3:19" x14ac:dyDescent="0.3">
+      <c r="C4" s="3"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
+      <c r="J4" s="5"/>
+      <c r="P4" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>8</v>
+      </c>
+      <c r="R4" t="s">
+        <v>65</v>
+      </c>
+      <c r="S4" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="5" spans="3:19" x14ac:dyDescent="0.3">
+      <c r="C5" s="7"/>
+      <c r="E5" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="H5" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="I5" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="J5" s="13"/>
+      <c r="M5" t="s">
+        <v>11</v>
+      </c>
+      <c r="N5" t="s">
+        <v>12</v>
+      </c>
+      <c r="O5" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q5" s="6"/>
+    </row>
+    <row r="6" spans="3:19" x14ac:dyDescent="0.3">
+      <c r="C6" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" s="16"/>
+      <c r="F6" s="17"/>
+      <c r="G6" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="H6" s="17"/>
+      <c r="I6" s="18"/>
+      <c r="J6" s="19"/>
+      <c r="M6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N6" t="s">
+        <v>15</v>
+      </c>
+      <c r="O6">
+        <v>10</v>
+      </c>
+      <c r="P6">
+        <v>3743.8103700000001</v>
+      </c>
+      <c r="Q6" s="6">
+        <v>3.4551759999999999E-3</v>
+      </c>
+      <c r="R6" s="64">
+        <v>14</v>
+      </c>
+      <c r="S6" s="64">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="3:19" x14ac:dyDescent="0.3">
+      <c r="C7" s="41" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7" s="42" t="s">
+        <v>15</v>
+      </c>
+      <c r="E7" s="41">
+        <v>13</v>
+      </c>
+      <c r="F7" s="42">
+        <v>500</v>
+      </c>
+      <c r="G7" s="43">
+        <v>3743.8103700000001</v>
+      </c>
+      <c r="H7" s="40">
+        <v>3.4551759999999999E-3</v>
+      </c>
+      <c r="I7" s="6">
+        <v>7.9131149999999997E-2</v>
+      </c>
+      <c r="J7" s="21"/>
+      <c r="M7" t="s">
+        <v>24</v>
+      </c>
+      <c r="N7" t="s">
+        <v>15</v>
+      </c>
+      <c r="O7">
+        <v>3</v>
+      </c>
+      <c r="P7">
+        <v>2080.46387</v>
+      </c>
+      <c r="Q7" s="6">
+        <v>4.8999030000000001E-11</v>
+      </c>
+      <c r="R7" s="64">
+        <v>74</v>
+      </c>
+      <c r="S7" s="64">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="8" spans="3:19" x14ac:dyDescent="0.3">
+      <c r="C8" s="16"/>
+      <c r="D8" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="E8" s="16">
+        <v>13</v>
+      </c>
+      <c r="F8" s="17">
+        <v>500</v>
+      </c>
+      <c r="G8" s="22"/>
+      <c r="H8" s="24"/>
+      <c r="I8" s="22"/>
+      <c r="J8" s="25"/>
+      <c r="M8" t="s">
+        <v>25</v>
+      </c>
+      <c r="N8" t="s">
+        <v>15</v>
+      </c>
+      <c r="O8">
+        <v>5</v>
+      </c>
+      <c r="P8">
+        <v>3580.32098</v>
+      </c>
+      <c r="Q8" s="6">
+        <v>5.026043E-3</v>
+      </c>
+      <c r="R8" s="64">
+        <v>2.5</v>
+      </c>
+      <c r="S8" s="64">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="9" spans="3:19" x14ac:dyDescent="0.3">
+      <c r="C9" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="D9" t="s">
+        <v>15</v>
+      </c>
+      <c r="E9" s="7">
+        <v>2</v>
+      </c>
+      <c r="F9">
+        <v>500</v>
+      </c>
+      <c r="G9" s="20">
+        <v>2080.46387</v>
+      </c>
+      <c r="H9" s="6">
+        <v>4.8999030000000001E-11</v>
+      </c>
+      <c r="I9" s="6">
+        <v>4.0780320000000002E-10</v>
+      </c>
+      <c r="J9" s="21"/>
+      <c r="M9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N9" t="s">
+        <v>15</v>
+      </c>
+      <c r="O9">
+        <v>6</v>
+      </c>
+      <c r="P9">
+        <v>2381.8217800000002</v>
+      </c>
+      <c r="Q9" s="6">
+        <v>4.0424420000000003</v>
+      </c>
+      <c r="R9" s="64">
+        <v>121</v>
+      </c>
+      <c r="S9" s="64">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="10" spans="3:19" x14ac:dyDescent="0.3">
+      <c r="C10" s="16"/>
+      <c r="D10" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="E10" s="16">
+        <v>2</v>
+      </c>
+      <c r="F10" s="17">
+        <v>500</v>
+      </c>
+      <c r="G10" s="22"/>
+      <c r="H10" s="24"/>
+      <c r="I10" s="22"/>
+      <c r="J10" s="25"/>
+      <c r="M10" t="s">
+        <v>27</v>
+      </c>
+      <c r="N10" t="s">
+        <v>15</v>
+      </c>
+      <c r="O10">
+        <v>9</v>
+      </c>
+      <c r="P10">
+        <v>2484.8226650000001</v>
+      </c>
+      <c r="Q10" s="6">
+        <v>8.6602399999999996E-5</v>
+      </c>
+      <c r="R10" s="64">
+        <v>20</v>
+      </c>
+      <c r="S10" s="64">
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="11" spans="3:19" x14ac:dyDescent="0.3">
+      <c r="C11" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D11" t="s">
+        <v>15</v>
+      </c>
+      <c r="E11" s="7">
+        <v>5</v>
+      </c>
+      <c r="F11">
+        <v>500</v>
+      </c>
+      <c r="G11" s="20">
+        <v>3580.32098</v>
+      </c>
+      <c r="H11" s="6">
+        <v>5.026043E-3</v>
+      </c>
+      <c r="I11" s="6">
+        <v>2.3976250000000001E-2</v>
+      </c>
+      <c r="J11" s="21"/>
+      <c r="M11" t="s">
+        <v>28</v>
+      </c>
+      <c r="N11" t="s">
+        <v>15</v>
+      </c>
+      <c r="O11">
+        <v>15</v>
+      </c>
+      <c r="P11">
+        <v>2771.9239499999999</v>
+      </c>
+      <c r="Q11" s="6">
+        <v>71.813209999999998</v>
+      </c>
+      <c r="R11" s="64">
+        <v>25</v>
+      </c>
+      <c r="S11" s="64">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="12" spans="3:19" x14ac:dyDescent="0.3">
+      <c r="C12" s="16"/>
+      <c r="D12" s="17"/>
+      <c r="E12" s="16"/>
+      <c r="F12" s="17"/>
+      <c r="G12" s="22"/>
+      <c r="H12" s="24"/>
+      <c r="I12" s="63"/>
+      <c r="J12" s="25"/>
+      <c r="M12" t="s">
+        <v>29</v>
+      </c>
+      <c r="N12" t="s">
+        <v>15</v>
+      </c>
+      <c r="O12">
+        <v>7</v>
+      </c>
+      <c r="P12">
+        <v>4392.4121150000001</v>
+      </c>
+      <c r="Q12" s="6">
+        <v>5.1046800000000003E-2</v>
+      </c>
+      <c r="R12" s="64">
+        <v>53</v>
+      </c>
+      <c r="S12" s="64">
+        <v>51.5</v>
+      </c>
+    </row>
+    <row r="13" spans="3:19" x14ac:dyDescent="0.3">
+      <c r="C13" s="41" t="s">
+        <v>26</v>
+      </c>
+      <c r="D13" s="42" t="s">
+        <v>15</v>
+      </c>
+      <c r="E13" s="41">
+        <v>7</v>
+      </c>
+      <c r="F13" s="42">
+        <v>500</v>
+      </c>
+      <c r="G13" s="43">
+        <v>2381.8217800000002</v>
+      </c>
+      <c r="H13" s="40">
+        <v>4.0424420000000003</v>
+      </c>
+      <c r="I13" s="40">
+        <v>29.82807</v>
+      </c>
+      <c r="J13" s="21"/>
+      <c r="M13" t="s">
+        <v>30</v>
+      </c>
+      <c r="N13" t="s">
+        <v>15</v>
+      </c>
+      <c r="O13">
+        <v>22</v>
+      </c>
+      <c r="P13">
+        <v>11605.569545</v>
+      </c>
+      <c r="Q13" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="R13" s="64">
+        <v>0</v>
+      </c>
+      <c r="S13" s="64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="3:19" x14ac:dyDescent="0.3">
+      <c r="C14" s="16"/>
+      <c r="D14" s="19"/>
+      <c r="E14" s="16">
+        <v>7</v>
+      </c>
+      <c r="F14" s="17">
+        <v>500</v>
+      </c>
+      <c r="G14" s="17"/>
+      <c r="H14" s="17"/>
+      <c r="I14" s="17"/>
+      <c r="J14" s="17"/>
+      <c r="M14" t="s">
+        <v>31</v>
+      </c>
+      <c r="N14" t="s">
+        <v>15</v>
+      </c>
+      <c r="O14">
+        <v>9</v>
+      </c>
+      <c r="P14">
+        <v>5333.496255</v>
+      </c>
+      <c r="Q14" s="6">
+        <v>1.0793980000000001E-5</v>
+      </c>
+      <c r="R14" s="64">
+        <v>93</v>
+      </c>
+      <c r="S14" s="64">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="15" spans="3:19" x14ac:dyDescent="0.3">
+      <c r="C15" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="D15" t="s">
+        <v>15</v>
+      </c>
+      <c r="E15" s="7">
+        <v>10</v>
+      </c>
+      <c r="F15">
+        <v>500</v>
+      </c>
+      <c r="G15" s="20">
+        <v>2484.8226650000001</v>
+      </c>
+      <c r="H15" s="6">
+        <v>8.6602399999999996E-5</v>
+      </c>
+      <c r="I15" s="6">
+        <v>8.2158320000000004E-5</v>
+      </c>
+      <c r="J15" s="21"/>
+      <c r="M15" t="s">
+        <v>32</v>
+      </c>
+      <c r="N15" t="s">
+        <v>15</v>
+      </c>
+      <c r="O15">
+        <v>2</v>
+      </c>
+      <c r="P15">
+        <v>1008.424625</v>
+      </c>
+      <c r="Q15" s="6">
+        <v>2.4152220000000001E-8</v>
+      </c>
+      <c r="R15" s="64">
+        <v>98</v>
+      </c>
+      <c r="S15" s="64">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="16" spans="3:19" x14ac:dyDescent="0.3">
+      <c r="C16" s="16"/>
+      <c r="D16" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="E16" s="16">
+        <v>10</v>
+      </c>
+      <c r="F16" s="17">
+        <v>500</v>
+      </c>
+      <c r="G16" s="22"/>
+      <c r="H16" s="24"/>
+      <c r="I16" s="22"/>
+      <c r="J16" s="25"/>
+      <c r="Q16" s="6"/>
+      <c r="R16" s="6"/>
+    </row>
+    <row r="17" spans="3:21" x14ac:dyDescent="0.3">
+      <c r="C17" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="D17" s="27" t="s">
+        <v>15</v>
+      </c>
+      <c r="E17" s="26">
+        <v>5</v>
+      </c>
+      <c r="F17" s="27">
+        <v>500</v>
+      </c>
+      <c r="G17" s="28">
+        <v>2771.9239499999999</v>
+      </c>
+      <c r="H17" s="49">
+        <v>71.813209999999998</v>
+      </c>
+      <c r="I17" s="49">
+        <v>83.805090000000007</v>
+      </c>
+      <c r="J17" s="30"/>
+      <c r="K17" t="s">
+        <v>69</v>
+      </c>
+      <c r="M17" t="s">
+        <v>2</v>
+      </c>
+      <c r="N17" t="s">
+        <v>20</v>
+      </c>
+      <c r="O17" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="P17" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>37</v>
+      </c>
+      <c r="R17" t="s">
+        <v>38</v>
+      </c>
+      <c r="S17" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="3:21" x14ac:dyDescent="0.3">
+      <c r="C18" s="31"/>
+      <c r="D18" s="32" t="s">
+        <v>17</v>
+      </c>
+      <c r="E18" s="31">
+        <v>5</v>
+      </c>
+      <c r="F18" s="32">
+        <v>500</v>
+      </c>
+      <c r="G18" s="33"/>
+      <c r="H18" s="34"/>
+      <c r="I18" s="33"/>
+      <c r="J18" s="35"/>
+      <c r="P18" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>33</v>
+      </c>
+      <c r="R18" t="s">
+        <v>65</v>
+      </c>
+      <c r="S18" t="s">
+        <v>66</v>
+      </c>
+      <c r="T18" s="6"/>
+      <c r="U18" s="6"/>
+    </row>
+    <row r="19" spans="3:21" x14ac:dyDescent="0.3">
+      <c r="C19" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="D19" t="s">
+        <v>15</v>
+      </c>
+      <c r="E19" s="7">
+        <v>4</v>
+      </c>
+      <c r="F19">
+        <v>500</v>
+      </c>
+      <c r="G19" s="20">
+        <v>4392.4121150000001</v>
+      </c>
+      <c r="H19" s="6">
+        <v>5.1046800000000003E-2</v>
+      </c>
+      <c r="I19" s="6">
+        <v>0.1080306</v>
+      </c>
+      <c r="J19" s="21"/>
+      <c r="M19" t="s">
+        <v>11</v>
+      </c>
+      <c r="N19" t="s">
+        <v>12</v>
+      </c>
+      <c r="O19" t="s">
+        <v>13</v>
+      </c>
+      <c r="R19" s="6"/>
+    </row>
+    <row r="20" spans="3:21" x14ac:dyDescent="0.3">
+      <c r="C20" s="16"/>
+      <c r="D20" s="17"/>
+      <c r="E20" s="16"/>
+      <c r="F20" s="17"/>
+      <c r="G20" s="22"/>
+      <c r="H20" s="24"/>
+      <c r="I20" s="63"/>
+      <c r="J20" s="25"/>
+      <c r="M20" t="s">
+        <v>23</v>
+      </c>
+      <c r="N20" t="s">
+        <v>15</v>
+      </c>
+      <c r="O20">
+        <v>10</v>
+      </c>
+      <c r="P20" s="6">
+        <v>7.9131149999999997E-2</v>
+      </c>
+      <c r="Q20" s="6">
+        <v>0</v>
+      </c>
+      <c r="R20" s="6">
+        <v>5.5976189999999999</v>
+      </c>
+      <c r="S20">
+        <v>5.5976189999999999</v>
+      </c>
+    </row>
+    <row r="21" spans="3:21" x14ac:dyDescent="0.3">
+      <c r="C21" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="D21" s="27" t="s">
+        <v>15</v>
+      </c>
+      <c r="E21" s="26">
+        <v>2</v>
+      </c>
+      <c r="F21" s="27">
+        <v>500</v>
+      </c>
+      <c r="G21" s="28">
+        <v>11605.569545</v>
+      </c>
+      <c r="H21" s="29" t="s">
+        <v>45</v>
+      </c>
+      <c r="I21" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="J21" s="30" t="s">
+        <v>58</v>
+      </c>
+      <c r="K21" t="s">
+        <v>70</v>
+      </c>
+      <c r="M21" t="s">
+        <v>24</v>
+      </c>
+      <c r="N21" t="s">
+        <v>15</v>
+      </c>
+      <c r="O21">
+        <v>3</v>
+      </c>
+      <c r="P21" s="6">
+        <v>4.0780320000000002E-10</v>
+      </c>
+      <c r="Q21" s="6">
+        <v>0</v>
+      </c>
+      <c r="R21" s="6">
+        <v>6.055301</v>
+      </c>
+      <c r="S21">
+        <v>6.055301</v>
+      </c>
+    </row>
+    <row r="22" spans="3:21" x14ac:dyDescent="0.3">
+      <c r="C22" s="31"/>
+      <c r="D22" s="32"/>
+      <c r="E22" s="31"/>
+      <c r="F22" s="32"/>
+      <c r="G22" s="33"/>
+      <c r="H22" s="34"/>
+      <c r="I22" s="33"/>
+      <c r="J22" s="35"/>
+      <c r="M22" t="s">
+        <v>25</v>
+      </c>
+      <c r="N22" t="s">
+        <v>15</v>
+      </c>
+      <c r="O22">
+        <v>5</v>
+      </c>
+      <c r="P22" s="6">
+        <v>2.3976250000000001E-2</v>
+      </c>
+      <c r="Q22" s="6">
+        <v>0</v>
+      </c>
+      <c r="R22" s="6">
+        <v>15.261062000000001</v>
+      </c>
+      <c r="S22">
+        <v>15.261062000000001</v>
+      </c>
+    </row>
+    <row r="23" spans="3:21" x14ac:dyDescent="0.3">
+      <c r="C23" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="D23" t="s">
+        <v>15</v>
+      </c>
+      <c r="E23" s="7">
+        <v>10</v>
+      </c>
+      <c r="F23">
+        <v>500</v>
+      </c>
+      <c r="G23" s="20">
+        <v>5333.496255</v>
+      </c>
+      <c r="H23" s="49">
+        <v>1.0793980000000001E-5</v>
+      </c>
+      <c r="I23" s="6">
+        <v>8.3642960000000002E-3</v>
+      </c>
+      <c r="J23" s="21"/>
+      <c r="K23" t="s">
+        <v>80</v>
+      </c>
+      <c r="M23" t="s">
+        <v>26</v>
+      </c>
+      <c r="N23" t="s">
+        <v>15</v>
+      </c>
+      <c r="O23">
+        <v>6</v>
+      </c>
+      <c r="P23" s="6">
+        <v>29.82807</v>
+      </c>
+      <c r="Q23" s="6">
+        <v>0</v>
+      </c>
+      <c r="R23" s="6">
+        <v>21.234144000000001</v>
+      </c>
+      <c r="S23">
+        <v>21.234144000000001</v>
+      </c>
+    </row>
+    <row r="24" spans="3:21" x14ac:dyDescent="0.3">
+      <c r="C24" s="7"/>
+      <c r="D24" t="s">
+        <v>17</v>
+      </c>
+      <c r="E24" s="7">
+        <v>10</v>
+      </c>
+      <c r="F24">
+        <v>500</v>
+      </c>
+      <c r="G24" s="20"/>
+      <c r="H24" s="6"/>
+      <c r="I24" s="22"/>
+      <c r="J24" s="21"/>
+      <c r="M24" t="s">
+        <v>27</v>
+      </c>
+      <c r="N24" t="s">
+        <v>15</v>
+      </c>
+      <c r="O24">
+        <v>9</v>
+      </c>
+      <c r="P24" s="6">
+        <v>8.2158320000000004E-5</v>
+      </c>
+      <c r="Q24" s="6">
+        <v>0</v>
+      </c>
+      <c r="R24" s="6">
+        <v>5.0288060000000003</v>
+      </c>
+      <c r="S24">
+        <v>4.0947120000000004</v>
+      </c>
+    </row>
+    <row r="25" spans="3:21" x14ac:dyDescent="0.3">
+      <c r="C25" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E25" s="3">
+        <v>2</v>
+      </c>
+      <c r="F25" s="4">
+        <v>500</v>
+      </c>
+      <c r="G25" s="38">
+        <v>1008.424625</v>
+      </c>
+      <c r="H25" s="39">
+        <v>2.4152220000000001E-8</v>
+      </c>
+      <c r="I25" s="6">
+        <v>1.4790490000000001E-7</v>
+      </c>
+      <c r="J25" s="23"/>
+      <c r="M25" t="s">
+        <v>28</v>
+      </c>
+      <c r="N25" t="s">
+        <v>15</v>
+      </c>
+      <c r="O25">
+        <v>15</v>
+      </c>
+      <c r="P25" s="6">
+        <v>83.805090000000007</v>
+      </c>
+      <c r="Q25" s="6">
+        <v>0</v>
+      </c>
+      <c r="R25" s="6">
+        <v>28.226071000000001</v>
+      </c>
+      <c r="S25">
+        <v>28.226071000000001</v>
+      </c>
+    </row>
+    <row r="26" spans="3:21" x14ac:dyDescent="0.3">
+      <c r="C26" s="16"/>
+      <c r="D26" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="E26" s="16">
+        <v>2</v>
+      </c>
+      <c r="F26" s="17">
+        <v>500</v>
+      </c>
+      <c r="G26" s="22"/>
+      <c r="H26" s="24"/>
+      <c r="I26" s="22"/>
+      <c r="J26" s="25"/>
+      <c r="M26" t="s">
+        <v>29</v>
+      </c>
+      <c r="N26" t="s">
+        <v>15</v>
+      </c>
+      <c r="O26">
+        <v>7</v>
+      </c>
+      <c r="P26" s="6">
+        <v>0.1080306</v>
+      </c>
+      <c r="Q26" s="6">
+        <v>3.3382750000000002E-8</v>
+      </c>
+      <c r="R26" s="6">
+        <v>11.520512999999999</v>
+      </c>
+      <c r="S26">
+        <v>12.463725</v>
+      </c>
+    </row>
+    <row r="27" spans="3:21" x14ac:dyDescent="0.3">
+      <c r="C27" t="s">
+        <v>68</v>
+      </c>
+      <c r="M27" t="s">
+        <v>30</v>
+      </c>
+      <c r="N27" t="s">
+        <v>15</v>
+      </c>
+      <c r="O27">
+        <v>22</v>
+      </c>
+      <c r="P27" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q27" s="6">
+        <v>316361500</v>
+      </c>
+      <c r="R27" s="6">
+        <v>28.126895000000001</v>
+      </c>
+      <c r="S27">
+        <v>28.126895000000001</v>
+      </c>
+    </row>
+    <row r="28" spans="3:21" x14ac:dyDescent="0.3">
+      <c r="M28" t="s">
+        <v>31</v>
+      </c>
+      <c r="N28" t="s">
+        <v>15</v>
+      </c>
+      <c r="O28">
+        <v>9</v>
+      </c>
+      <c r="P28" s="6">
+        <v>8.3642960000000002E-3</v>
+      </c>
+      <c r="Q28" s="6">
+        <v>0</v>
+      </c>
+      <c r="R28" s="6">
+        <v>26.532160999999999</v>
+      </c>
+      <c r="S28">
+        <v>26.532160999999999</v>
+      </c>
+    </row>
+    <row r="29" spans="3:21" x14ac:dyDescent="0.3">
+      <c r="M29" t="s">
+        <v>32</v>
+      </c>
+      <c r="N29" t="s">
+        <v>15</v>
+      </c>
+      <c r="O29">
+        <v>2</v>
+      </c>
+      <c r="P29" s="6">
+        <v>1.4790490000000001E-7</v>
+      </c>
+      <c r="Q29" s="6">
+        <v>0</v>
+      </c>
+      <c r="R29" s="6">
+        <v>18.880030999999999</v>
+      </c>
+      <c r="S29">
+        <v>18.819611999999999</v>
+      </c>
+    </row>
+    <row r="30" spans="3:21" x14ac:dyDescent="0.3">
+      <c r="R30" s="6"/>
+    </row>
+    <row r="32" spans="3:21" x14ac:dyDescent="0.3">
+      <c r="M32" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="33" spans="13:22" x14ac:dyDescent="0.3">
+      <c r="N33" t="s">
+        <v>2</v>
+      </c>
+      <c r="O33" t="s">
+        <v>3</v>
+      </c>
+      <c r="P33" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q33" t="s">
+        <v>5</v>
+      </c>
+      <c r="R33" t="s">
+        <v>37</v>
+      </c>
+      <c r="S33" t="s">
+        <v>38</v>
+      </c>
+      <c r="T33" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34" spans="13:22" x14ac:dyDescent="0.3">
+      <c r="Q34" t="s">
+        <v>7</v>
+      </c>
+      <c r="R34" t="s">
+        <v>8</v>
+      </c>
+      <c r="S34" t="s">
+        <v>21</v>
+      </c>
+      <c r="T34" t="s">
+        <v>61</v>
+      </c>
+      <c r="U34" t="s">
+        <v>33</v>
+      </c>
+      <c r="V34" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="35" spans="13:22" x14ac:dyDescent="0.3">
+      <c r="M35" t="s">
+        <v>11</v>
+      </c>
+      <c r="N35" t="s">
+        <v>10</v>
+      </c>
+      <c r="O35" t="s">
+        <v>71</v>
+      </c>
+      <c r="P35" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="36" spans="13:22" x14ac:dyDescent="0.3">
+      <c r="M36" t="s">
+        <v>30</v>
+      </c>
+      <c r="N36">
+        <v>0</v>
+      </c>
+      <c r="O36" s="6">
+        <v>1E-4</v>
+      </c>
+      <c r="P36" t="s">
+        <v>74</v>
+      </c>
+      <c r="Q36">
+        <v>11497.557994999999</v>
+      </c>
+      <c r="R36">
+        <v>1.771E-3</v>
+      </c>
+      <c r="S36">
+        <v>7.3415999999999995E-2</v>
+      </c>
+      <c r="T36">
+        <v>4</v>
+      </c>
+      <c r="U36">
+        <v>0</v>
+      </c>
+      <c r="V36">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="37" spans="13:22" x14ac:dyDescent="0.3">
+      <c r="M37" t="s">
+        <v>30</v>
+      </c>
+      <c r="N37">
+        <v>0</v>
+      </c>
+      <c r="O37" s="6">
+        <v>1E-4</v>
+      </c>
+      <c r="P37" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q37">
+        <v>9021.6708450000006</v>
+      </c>
+      <c r="R37">
+        <v>1.699E-3</v>
+      </c>
+      <c r="S37">
+        <v>1.5568E-2</v>
+      </c>
+      <c r="T37">
+        <v>3</v>
+      </c>
+      <c r="U37">
+        <v>0</v>
+      </c>
+      <c r="V37">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="38" spans="13:22" x14ac:dyDescent="0.3">
+      <c r="M38" t="s">
+        <v>30</v>
+      </c>
+      <c r="N38">
+        <v>0</v>
+      </c>
+      <c r="O38" s="6">
+        <v>1E-4</v>
+      </c>
+      <c r="P38" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q38">
+        <v>16759.19471</v>
+      </c>
+      <c r="R38" t="s">
+        <v>45</v>
+      </c>
+      <c r="S38" t="s">
+        <v>45</v>
+      </c>
+      <c r="T38">
+        <v>4</v>
+      </c>
+      <c r="U38">
+        <v>5.8215999999999997E-2</v>
+      </c>
+      <c r="V38">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="39" spans="13:22" x14ac:dyDescent="0.3">
+      <c r="M39" t="s">
+        <v>30</v>
+      </c>
+      <c r="N39">
+        <v>0</v>
+      </c>
+      <c r="O39" s="6">
+        <v>1E-4</v>
+      </c>
+      <c r="P39" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q39">
+        <v>16759.19471</v>
+      </c>
+      <c r="R39" t="s">
+        <v>45</v>
+      </c>
+      <c r="S39" t="s">
+        <v>45</v>
+      </c>
+      <c r="T39">
+        <v>6</v>
+      </c>
+      <c r="U39">
+        <v>5.8215999999999997E-2</v>
+      </c>
+      <c r="V39">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="40" spans="13:22" x14ac:dyDescent="0.3">
+      <c r="M40" t="s">
+        <v>30</v>
+      </c>
+      <c r="N40">
+        <v>0</v>
+      </c>
+      <c r="O40" s="6">
+        <v>1E-4</v>
+      </c>
+      <c r="P40" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q40">
+        <v>9735.7064549999996</v>
+      </c>
+      <c r="R40">
+        <v>3.3742070000000002</v>
+      </c>
+      <c r="S40">
+        <v>7.3022689999999999</v>
+      </c>
+      <c r="T40">
+        <v>5</v>
+      </c>
+      <c r="U40">
+        <v>5.8215999999999997E-2</v>
+      </c>
+      <c r="V40">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="13:22" x14ac:dyDescent="0.3">
+      <c r="M44" s="2"/>
+    </row>
+    <row r="51" spans="13:21" x14ac:dyDescent="0.3">
+      <c r="M51" s="2"/>
+    </row>
+    <row r="55" spans="13:21" x14ac:dyDescent="0.3">
+      <c r="R55" s="6"/>
+      <c r="U55" s="6"/>
+    </row>
+    <row r="56" spans="13:21" x14ac:dyDescent="0.3">
+      <c r="R56" s="6"/>
+      <c r="U56" s="6"/>
+    </row>
+    <row r="57" spans="13:21" x14ac:dyDescent="0.3">
+      <c r="U57" s="6"/>
+    </row>
+    <row r="62" spans="13:21" x14ac:dyDescent="0.3">
+      <c r="Q62" s="6"/>
+    </row>
+    <row r="63" spans="13:21" x14ac:dyDescent="0.3">
+      <c r="Q63" s="6"/>
+    </row>
+    <row r="64" spans="13:21" x14ac:dyDescent="0.3">
+      <c r="Q64" s="6"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{086DCCED-70F6-45A9-8496-98A0FEEDF10E}">
   <dimension ref="C1:U33"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -5829,7 +7139,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55D91BD8-0048-428B-8029-9C24A623F1BA}">
   <dimension ref="C1:U33"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -6851,7 +8161,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F1827695-A9C0-4BE6-AEFB-B5C1FCB8A6CD}">
   <dimension ref="C1:U33"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>

--- a/test/G14-G24.xlsx
+++ b/test/G14-G24.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wolfgang\Documents\GitHub\SACOBRA_Py\test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC77C04C-78E1-4CDA-9BE2-5ED204A5A8FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B971552E-977C-44E5-8220-C4EA166C1A03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="3" xr2:uid="{6EF9DD2D-A48A-4E61-B7E9-B72FBCB815D4}"/>
   </bookViews>
